--- a/restaurant_analytics/data/mornings.xlsx
+++ b/restaurant_analytics/data/mornings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cardi\Documents\git-repo\swe_dev\restaurant_analytics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393A0407-58DF-4887-91F9-4C54AD79C635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABE66E6-2FEC-4F78-A8CF-27C8B5808296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="1830" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -221,9 +221,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -568,7 +565,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -587,6 +583,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17250,7 +17247,7 @@
         <v>0</v>
       </c>
       <c r="H616" s="9">
-        <v>20.3</v>
+        <v>20.100000000000001</v>
       </c>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
@@ -17325,7 +17322,7 @@
         <v>17</v>
       </c>
       <c r="E619" s="9">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="F619" s="9">
         <v>0.66900000000000004</v>
@@ -17334,7 +17331,7 @@
         <v>9</v>
       </c>
       <c r="H619" s="9">
-        <v>9.6</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
@@ -17438,7 +17435,7 @@
         <v>4.016</v>
       </c>
       <c r="H623" s="9">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.25">
@@ -17542,7 +17539,7 @@
         <v>7.008</v>
       </c>
       <c r="H627" s="9">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
@@ -17620,7 +17617,7 @@
         <v>0.7</v>
       </c>
       <c r="H630" s="9">
-        <v>15.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
@@ -17663,7 +17660,7 @@
         <v>20</v>
       </c>
       <c r="E632" s="9">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="F632" s="9">
         <v>4.0000000000000001E-3</v>
@@ -17698,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="H633" s="9">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
@@ -17828,7 +17825,7 @@
         <v>0</v>
       </c>
       <c r="H638" s="9">
-        <v>17.100000000000001</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
@@ -18004,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="E645" s="9">
-        <v>39.9</v>
+        <v>40.6</v>
       </c>
       <c r="F645" s="9">
         <v>0</v>
@@ -18013,7 +18010,7 @@
         <v>0</v>
       </c>
       <c r="H645" s="9">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="I645" t="s">
         <v>28</v>
@@ -18036,13 +18033,13 @@
         <v>42.3</v>
       </c>
       <c r="F646" s="9">
-        <v>0.23200000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="G646" s="9">
         <v>0</v>
       </c>
       <c r="H646" s="9">
-        <v>8.8000000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I646" s="36" t="s">
         <v>29</v>
@@ -18062,7 +18059,7 @@
         <v>65</v>
       </c>
       <c r="E647" s="9">
-        <v>41.4</v>
+        <v>40.1</v>
       </c>
       <c r="F647" s="9">
         <v>0</v>
@@ -18071,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="H647" s="9">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
@@ -18088,16 +18085,16 @@
         <v>68</v>
       </c>
       <c r="E648" s="9">
-        <v>45.5</v>
+        <v>47.7</v>
       </c>
       <c r="F648" s="9">
-        <v>1.3819999999999999</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="G648" s="9">
         <v>0</v>
       </c>
       <c r="H648" s="9">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
@@ -18114,16 +18111,16 @@
         <v>12</v>
       </c>
       <c r="E649" s="9">
-        <v>18.899999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="F649" s="9">
-        <v>6.7000000000000004E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G649" s="9">
         <v>0.98399999999999999</v>
       </c>
       <c r="H649" s="9">
-        <v>18.899999999999999</v>
+        <v>19</v>
       </c>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.25">
@@ -18140,13 +18137,13 @@
         <v>6</v>
       </c>
       <c r="E650" s="9">
-        <v>17.399999999999999</v>
+        <v>16</v>
       </c>
       <c r="F650" s="9">
-        <v>8.3000000000000004E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G650" s="9">
-        <v>0.2</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H650" s="9">
         <v>9.8000000000000007</v>
@@ -18166,16 +18163,16 @@
         <v>0</v>
       </c>
       <c r="E651" s="9">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="F651" s="9">
-        <v>6.3E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G651" s="9">
-        <v>0.98399999999999999</v>
+        <v>2.008</v>
       </c>
       <c r="H651" s="9">
-        <v>13.1</v>
+        <v>12.3</v>
       </c>
       <c r="I651" s="36" t="s">
         <v>30</v>
@@ -18363,7 +18360,7 @@
         <v>0</v>
       </c>
       <c r="H658" s="9">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.25">
@@ -18389,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="H659" s="9">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
@@ -18406,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="E660" s="9">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="F660" s="9">
         <v>2.4E-2</v>
@@ -18415,7 +18412,7 @@
         <v>0</v>
       </c>
       <c r="H660" s="9">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="661" spans="1:9" x14ac:dyDescent="0.25">
@@ -18432,16 +18429,16 @@
         <v>23</v>
       </c>
       <c r="E661" s="9">
-        <v>35.200000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="F661" s="9">
-        <v>0.20100000000000001</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="G661" s="9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H661" s="9">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
@@ -18458,7 +18455,7 @@
         <v>13</v>
       </c>
       <c r="E662" s="9">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="F662" s="9">
         <v>0</v>
@@ -18467,7 +18464,7 @@
         <v>0</v>
       </c>
       <c r="H662" s="9">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="663" spans="1:9" x14ac:dyDescent="0.25">
@@ -18484,7 +18481,7 @@
         <v>7</v>
       </c>
       <c r="E663" s="9">
-        <v>34.299999999999997</v>
+        <v>31.5</v>
       </c>
       <c r="F663" s="9">
         <v>0</v>
@@ -18493,7 +18490,7 @@
         <v>0</v>
       </c>
       <c r="H663" s="9">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.25">
@@ -18510,7 +18507,7 @@
         <v>2</v>
       </c>
       <c r="E664" s="9">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="F664" s="9">
         <v>0</v>
@@ -18519,7 +18516,7 @@
         <v>0</v>
       </c>
       <c r="H664" s="9">
-        <v>15</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.25">
@@ -18536,13 +18533,13 @@
         <v>21</v>
       </c>
       <c r="E665" s="9">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="F665" s="9">
-        <v>0.05</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G665" s="9">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H665" s="9">
         <v>17</v>
@@ -18562,16 +18559,16 @@
         <v>11</v>
       </c>
       <c r="E666" s="9">
-        <v>21.9</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F666" s="9">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G666" s="9">
-        <v>1.2</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H666" s="9">
-        <v>10</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="667" spans="1:9" x14ac:dyDescent="0.25">
@@ -18588,16 +18585,16 @@
         <v>0</v>
       </c>
       <c r="E667" s="9">
-        <v>25.2</v>
+        <v>28</v>
       </c>
       <c r="F667" s="9">
-        <v>0.26</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="G667" s="9">
-        <v>3.9</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H667" s="9">
-        <v>10.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
@@ -18614,16 +18611,16 @@
         <v>15</v>
       </c>
       <c r="E668" s="9">
-        <v>20.5</v>
+        <v>18.7</v>
       </c>
       <c r="F668" s="9">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G668" s="9">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H668" s="9">
-        <v>11.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
@@ -18640,16 +18637,16 @@
         <v>25</v>
       </c>
       <c r="E669" s="9">
-        <v>16.5</v>
+        <v>12.6</v>
       </c>
       <c r="F669" s="9">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G669" s="9">
         <v>0</v>
       </c>
       <c r="H669" s="9">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
@@ -18666,16 +18663,16 @@
         <v>21</v>
       </c>
       <c r="E670" s="9">
-        <v>14.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F670" s="9">
         <v>0</v>
       </c>
       <c r="G670" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H670" s="9">
-        <v>11.6</v>
+        <v>14.3</v>
       </c>
       <c r="I670" t="s">
         <v>32</v>
@@ -18695,16 +18692,16 @@
         <v>5</v>
       </c>
       <c r="E671" s="9">
-        <v>16.7</v>
+        <v>7.7</v>
       </c>
       <c r="F671" s="9">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G671" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H671" s="9">
-        <v>10.4</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
@@ -18721,19 +18718,19 @@
         <v>18</v>
       </c>
       <c r="E672" s="9">
-        <v>30.5</v>
+        <v>25.7</v>
       </c>
       <c r="F672" s="9">
-        <v>0</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G672" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H672" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" s="6">
         <v>5</v>
       </c>
@@ -18747,19 +18744,19 @@
         <v>12</v>
       </c>
       <c r="E673" s="9">
-        <v>26.5</v>
+        <v>20.8</v>
       </c>
       <c r="F673" s="9">
         <v>0</v>
       </c>
       <c r="G673" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H673" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" s="6">
         <v>6</v>
       </c>
@@ -18773,19 +18770,19 @@
         <v>7</v>
       </c>
       <c r="E674" s="9">
-        <v>24</v>
+        <v>-1.3</v>
       </c>
       <c r="F674" s="9">
         <v>0</v>
       </c>
       <c r="G674" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H674" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" s="6">
         <v>7</v>
       </c>
@@ -18799,19 +18796,19 @@
         <v>26</v>
       </c>
       <c r="E675" s="9">
-        <v>22</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="F675" s="9">
-        <v>0</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G675" s="9">
-        <v>0</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H675" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" s="6">
         <v>1</v>
       </c>
@@ -18825,19 +18822,19 @@
         <v>36</v>
       </c>
       <c r="E676" s="9">
-        <v>15</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F676" s="9">
-        <v>0.02</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="G676" s="9">
-        <v>0.2</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="H676" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" s="6">
         <v>2</v>
       </c>
@@ -18851,19 +18848,19 @@
         <v>11</v>
       </c>
       <c r="E677" s="9">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="F677" s="9">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G677" s="9">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="H677" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" s="6">
         <v>3</v>
       </c>
@@ -18877,19 +18874,19 @@
         <v>9</v>
       </c>
       <c r="E678" s="9">
-        <v>15</v>
+        <v>11.1</v>
       </c>
       <c r="F678" s="9">
         <v>0</v>
       </c>
       <c r="G678" s="9">
-        <v>0</v>
+        <v>2.992</v>
       </c>
       <c r="H678" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="679" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" s="6">
         <v>4</v>
       </c>
@@ -18903,19 +18900,19 @@
         <v>14</v>
       </c>
       <c r="E679" s="9">
-        <v>25</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F679" s="9">
         <v>0</v>
       </c>
       <c r="G679" s="9">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H679" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="680" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" s="6">
         <v>5</v>
       </c>
@@ -18929,19 +18926,19 @@
         <v>10</v>
       </c>
       <c r="E680" s="9">
-        <v>31</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F680" s="9">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="G680" s="9">
-        <v>0.08</v>
+        <v>2.008</v>
       </c>
       <c r="H680" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="681" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" s="6">
         <v>6</v>
       </c>
@@ -18955,19 +18952,19 @@
         <v>19</v>
       </c>
       <c r="E681" s="9">
-        <v>24</v>
+        <v>12.6</v>
       </c>
       <c r="F681" s="9">
-        <v>0</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G681" s="9">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H681" s="9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" s="6">
         <v>7</v>
       </c>
@@ -18981,19 +18978,19 @@
         <v>28</v>
       </c>
       <c r="E682" s="9">
-        <v>14.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="F682" s="9">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G682" s="9">
-        <v>0</v>
+        <v>2.992</v>
       </c>
       <c r="H682" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" s="6">
         <v>1</v>
       </c>
@@ -19007,7 +19004,7 @@
         <v>11</v>
       </c>
       <c r="E683" s="9">
-        <v>22.5</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F683" s="9">
         <v>0</v>
@@ -19016,10 +19013,10 @@
         <v>0</v>
       </c>
       <c r="H683" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" s="6">
         <v>2</v>
       </c>
@@ -19033,19 +19030,19 @@
         <v>4</v>
       </c>
       <c r="E684" s="9">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="F684" s="9">
-        <v>0</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G684" s="9">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H684" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" s="6">
         <v>3</v>
       </c>
@@ -19056,22 +19053,22 @@
         <v>46056</v>
       </c>
       <c r="D685" s="14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E685" s="9">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="F685" s="9">
         <v>0</v>
       </c>
       <c r="G685" s="9">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="H685" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" s="6">
         <v>4</v>
       </c>
@@ -19082,10 +19079,10 @@
         <v>46057</v>
       </c>
       <c r="D686" s="14">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="E686" s="9">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="F686" s="9">
         <v>0</v>
@@ -19094,13 +19091,10 @@
         <v>0</v>
       </c>
       <c r="H686" s="9">
-        <v>14</v>
-      </c>
-      <c r="J686" s="9">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" s="6">
         <v>5</v>
       </c>
@@ -19111,25 +19105,22 @@
         <v>46058</v>
       </c>
       <c r="D687" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E687" s="9">
-        <v>16</v>
+        <v>24.4</v>
       </c>
       <c r="F687" s="9">
-        <v>0</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G687" s="9">
         <v>0</v>
       </c>
       <c r="H687" s="9">
-        <v>8</v>
-      </c>
-      <c r="J687" s="9">
-        <v>5.6099999999999994</v>
-      </c>
-    </row>
-    <row r="688" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" s="6">
         <v>6</v>
       </c>
@@ -19140,22 +19131,19 @@
         <v>46059</v>
       </c>
       <c r="D688" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E688" s="9">
-        <v>18.5</v>
+        <v>31.1</v>
       </c>
       <c r="F688" s="9">
-        <v>0.12</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="G688" s="9">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H688" s="9">
-        <v>6</v>
-      </c>
-      <c r="J688" s="9">
-        <v>6.12</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="689" spans="1:10" x14ac:dyDescent="0.25">
@@ -19169,22 +19157,19 @@
         <v>46060</v>
       </c>
       <c r="D689" s="14">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E689" s="9">
-        <v>17</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="F689" s="9">
-        <v>0.11</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G689" s="9">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H689" s="9">
-        <v>10</v>
-      </c>
-      <c r="J689" s="9">
-        <v>4.4649999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="690" spans="1:10" x14ac:dyDescent="0.25">
@@ -19198,25 +19183,22 @@
         <v>46061</v>
       </c>
       <c r="D690" s="14">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="E690" s="9">
-        <v>15.5</v>
+        <v>25.3</v>
       </c>
       <c r="F690" s="9">
-        <v>0</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G690" s="9">
         <v>0</v>
       </c>
       <c r="H690" s="9">
-        <v>14</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I690" t="s">
         <v>33</v>
-      </c>
-      <c r="J690" s="9">
-        <v>11.95</v>
       </c>
     </row>
     <row r="691" spans="1:10" x14ac:dyDescent="0.25">
@@ -19230,22 +19212,19 @@
         <v>46062</v>
       </c>
       <c r="D691" s="14">
-        <v>22.5</v>
+        <v>2</v>
       </c>
       <c r="E691" s="9">
-        <v>14.5</v>
+        <v>31.3</v>
       </c>
       <c r="F691" s="9">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G691" s="9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H691" s="9">
-        <v>16</v>
-      </c>
-      <c r="J691" s="9">
-        <v>7.9399999999999995</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="692" spans="1:10" x14ac:dyDescent="0.25">
@@ -19259,10 +19238,10 @@
         <v>46063</v>
       </c>
       <c r="D692" s="14">
-        <v>6.5</v>
+        <v>19</v>
       </c>
       <c r="E692" s="9">
-        <v>16.5</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="F692" s="9">
         <v>0</v>
@@ -19271,10 +19250,7 @@
         <v>0</v>
       </c>
       <c r="H692" s="9">
-        <v>13</v>
-      </c>
-      <c r="J692" s="9">
-        <v>4.9350000000000005</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.25">
@@ -19288,10 +19264,10 @@
         <v>46064</v>
       </c>
       <c r="D693" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E693" s="9">
-        <v>16.5</v>
+        <v>31.1</v>
       </c>
       <c r="F693" s="9">
         <v>0</v>
@@ -19300,10 +19276,7 @@
         <v>0</v>
       </c>
       <c r="H693" s="9">
-        <v>6</v>
-      </c>
-      <c r="J693" s="9">
-        <v>4.8250000000000002</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="694" spans="1:10" x14ac:dyDescent="0.25">
@@ -19317,10 +19290,10 @@
         <v>46065</v>
       </c>
       <c r="D694" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E694" s="9">
-        <v>17</v>
+        <v>31.3</v>
       </c>
       <c r="F694" s="9">
         <v>0</v>
@@ -19329,10 +19302,7 @@
         <v>0</v>
       </c>
       <c r="H694" s="9">
-        <v>5</v>
-      </c>
-      <c r="J694" s="9">
-        <v>3.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.25">
@@ -19346,10 +19316,10 @@
         <v>46066</v>
       </c>
       <c r="D695" s="14">
-        <v>12.5</v>
+        <v>31</v>
       </c>
       <c r="E695" s="9">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F695" s="9">
         <v>0</v>
@@ -19358,10 +19328,7 @@
         <v>0</v>
       </c>
       <c r="H695" s="9">
-        <v>6</v>
-      </c>
-      <c r="J695" s="9">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="696" spans="1:10" x14ac:dyDescent="0.25">
@@ -19375,10 +19342,10 @@
         <v>46067</v>
       </c>
       <c r="D696" s="14">
-        <v>18.5</v>
+        <v>78</v>
       </c>
       <c r="E696" s="9">
-        <v>17</v>
+        <v>36.9</v>
       </c>
       <c r="F696" s="9">
         <v>0</v>
@@ -19387,13 +19354,10 @@
         <v>0</v>
       </c>
       <c r="H696" s="9">
-        <v>8</v>
-      </c>
-      <c r="I696" t="s">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I696" s="36" t="s">
         <v>34</v>
-      </c>
-      <c r="J696" s="9">
-        <v>7.91</v>
       </c>
     </row>
     <row r="697" spans="1:10" x14ac:dyDescent="0.25">
@@ -19407,22 +19371,19 @@
         <v>46068</v>
       </c>
       <c r="D697" s="14">
-        <v>23.5</v>
+        <v>43</v>
       </c>
       <c r="E697" s="9">
-        <v>19.5</v>
+        <v>44.2</v>
       </c>
       <c r="F697" s="9">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G697" s="9">
         <v>0</v>
       </c>
       <c r="H697" s="9">
-        <v>12</v>
-      </c>
-      <c r="J697" s="9">
-        <v>8.1349999999999998</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="698" spans="1:10" x14ac:dyDescent="0.25">
@@ -19436,25 +19397,22 @@
         <v>46069</v>
       </c>
       <c r="D698" s="14">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="E698" s="9">
-        <v>23.5</v>
+        <v>48.9</v>
       </c>
       <c r="F698" s="9">
         <v>0</v>
       </c>
       <c r="G698" s="9">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="H698" s="9">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I698" s="36" t="s">
         <v>35</v>
-      </c>
-      <c r="J698" s="9">
-        <v>8.26</v>
       </c>
     </row>
     <row r="699" spans="1:10" x14ac:dyDescent="0.25">
@@ -19468,22 +19426,19 @@
         <v>46070</v>
       </c>
       <c r="D699" s="14">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="E699" s="9">
-        <v>18.5</v>
+        <v>48.4</v>
       </c>
       <c r="F699" s="9">
-        <v>0</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G699" s="9">
         <v>0</v>
       </c>
       <c r="H699" s="9">
-        <v>4</v>
-      </c>
-      <c r="J699" s="9">
-        <v>5.5250000000000004</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="700" spans="1:10" x14ac:dyDescent="0.25">
@@ -19497,25 +19452,25 @@
         <v>46071</v>
       </c>
       <c r="D700" s="14">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="E700" s="9">
-        <v>20</v>
+        <v>53.6</v>
       </c>
       <c r="F700" s="9">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G700" s="9">
-        <v>1.2</v>
+        <v>0.04</v>
       </c>
       <c r="H700" s="9">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I700" s="36" t="s">
         <v>37</v>
       </c>
       <c r="J700" s="9">
-        <v>6</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="701" spans="1:10" x14ac:dyDescent="0.25">
@@ -19529,10 +19484,10 @@
         <v>46072</v>
       </c>
       <c r="D701" s="14">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="E701" s="9">
-        <v>27.5</v>
+        <v>45.3</v>
       </c>
       <c r="F701" s="9">
         <v>0</v>
@@ -19541,10 +19496,10 @@
         <v>0</v>
       </c>
       <c r="H701" s="9">
-        <v>6</v>
+        <v>9.1</v>
       </c>
       <c r="J701" s="9">
-        <v>3.2149999999999999</v>
+        <v>2.915</v>
       </c>
     </row>
     <row r="702" spans="1:10" x14ac:dyDescent="0.25">
@@ -19558,25 +19513,25 @@
         <v>46073</v>
       </c>
       <c r="D702" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E702" s="9">
-        <v>21.5</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="F702" s="9">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G702" s="9">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H702" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I702" s="36" t="s">
         <v>10</v>
       </c>
       <c r="J702" s="9">
-        <v>4.7850000000000001</v>
+        <v>3.9000000000000004</v>
       </c>
     </row>
     <row r="703" spans="1:10" x14ac:dyDescent="0.25">
@@ -19590,10 +19545,10 @@
         <v>46074</v>
       </c>
       <c r="D703" s="14">
-        <v>18.5</v>
+        <v>25.5</v>
       </c>
       <c r="E703" s="9">
-        <v>18.5</v>
+        <v>31.6</v>
       </c>
       <c r="F703" s="9">
         <v>0</v>
@@ -19602,10 +19557,10 @@
         <v>0</v>
       </c>
       <c r="H703" s="9">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="J703" s="9">
-        <v>8.0449999999999999</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="704" spans="1:10" x14ac:dyDescent="0.25">
@@ -19619,22 +19574,22 @@
         <v>46075</v>
       </c>
       <c r="D704" s="14">
-        <v>23.5</v>
+        <v>28.5</v>
       </c>
       <c r="E704" s="9">
-        <v>20</v>
+        <v>28.4</v>
       </c>
       <c r="F704" s="9">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="G704" s="9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H704" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J704" s="9">
-        <v>9.4400000000000013</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="705" spans="1:10" x14ac:dyDescent="0.25">
@@ -19648,10 +19603,10 @@
         <v>46076</v>
       </c>
       <c r="D705" s="14">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="E705" s="9">
-        <v>22.5</v>
+        <v>28.8</v>
       </c>
       <c r="F705" s="9">
         <v>0</v>
@@ -19660,10 +19615,10 @@
         <v>0</v>
       </c>
       <c r="H705" s="9">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="J705" s="9">
-        <v>4.93</v>
+        <v>3.895</v>
       </c>
     </row>
     <row r="706" spans="1:10" x14ac:dyDescent="0.25">
@@ -19677,22 +19632,22 @@
         <v>46077</v>
       </c>
       <c r="D706" s="14">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="E706" s="9">
-        <v>22.5</v>
+        <v>31.8</v>
       </c>
       <c r="F706" s="9">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G706" s="9">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H706" s="9">
-        <v>5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J706" s="9">
-        <v>5.6749999999999998</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="707" spans="1:10" x14ac:dyDescent="0.25">
@@ -19706,22 +19661,22 @@
         <v>46078</v>
       </c>
       <c r="D707" s="14">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="E707" s="9">
-        <v>26.5</v>
+        <v>22</v>
       </c>
       <c r="F707" s="9">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="G707" s="9">
-        <v>0.56000000000000005</v>
+        <v>0.36</v>
       </c>
       <c r="H707" s="9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J707" s="9">
-        <v>4.0200000000000005</v>
+        <v>3.0550000000000002</v>
       </c>
     </row>
     <row r="708" spans="1:10" x14ac:dyDescent="0.25">
@@ -19735,22 +19690,22 @@
         <v>46079</v>
       </c>
       <c r="D708" s="14">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="E708" s="9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F708" s="9">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="G708" s="9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H708" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J708" s="9">
-        <v>5.58</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="709" spans="1:10" x14ac:dyDescent="0.25">
@@ -19764,16 +19719,16 @@
         <v>46080</v>
       </c>
       <c r="D709" s="14">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="E709" s="9">
-        <v>20.5</v>
+        <v>25</v>
       </c>
       <c r="F709" s="9">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G709" s="9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="H709" s="9">
         <v>15</v>
@@ -19782,7 +19737,7 @@
         <v>10</v>
       </c>
       <c r="J709" s="9">
-        <v>6.9350000000000005</v>
+        <v>3.8049999999999997</v>
       </c>
     </row>
     <row r="710" spans="1:10" x14ac:dyDescent="0.25">
@@ -19796,10 +19751,10 @@
         <v>46081</v>
       </c>
       <c r="D710" s="14">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="E710" s="9">
-        <v>25</v>
+        <v>21.5</v>
       </c>
       <c r="F710" s="9">
         <v>0</v>
@@ -19811,7 +19766,7 @@
         <v>7</v>
       </c>
       <c r="J710" s="9">
-        <v>5.97</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="711" spans="1:10" x14ac:dyDescent="0.25">
@@ -19825,22 +19780,22 @@
         <v>46082</v>
       </c>
       <c r="D711" s="14">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="E711" s="9">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F711" s="9">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="G711" s="9">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
       <c r="H711" s="9">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J711" s="9">
-        <v>6.52</v>
+        <v>6</v>
       </c>
     </row>
     <row r="712" spans="1:10" x14ac:dyDescent="0.25">
@@ -19857,19 +19812,19 @@
         <v>20.5</v>
       </c>
       <c r="E712" s="9">
-        <v>30</v>
+        <v>24.5</v>
       </c>
       <c r="F712" s="9">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="G712" s="9">
-        <v>0.12</v>
+        <v>0.73</v>
       </c>
       <c r="H712" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J712" s="9">
-        <v>6.2050000000000001</v>
+        <v>6.8849999999999998</v>
       </c>
     </row>
     <row r="713" spans="1:10" x14ac:dyDescent="0.25">
@@ -19883,22 +19838,22 @@
         <v>46084</v>
       </c>
       <c r="D713" s="14">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="E713" s="9">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F713" s="9">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G713" s="9">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="H713" s="9">
         <v>8</v>
       </c>
       <c r="J713" s="9">
-        <v>4.625</v>
+        <v>3.0149999999999997</v>
       </c>
     </row>
     <row r="714" spans="1:10" x14ac:dyDescent="0.25">
@@ -19912,22 +19867,22 @@
         <v>46085</v>
       </c>
       <c r="D714" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E714" s="9">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F714" s="9">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G714" s="9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H714" s="9">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J714" s="9">
-        <v>4.49</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="715" spans="1:10" x14ac:dyDescent="0.25">
@@ -19941,22 +19896,22 @@
         <v>46086</v>
       </c>
       <c r="D715" s="14">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="E715" s="9">
-        <v>32</v>
+        <v>24.5</v>
       </c>
       <c r="F715" s="9">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G715" s="9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="H715" s="9">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J715" s="9">
-        <v>7.625</v>
+        <v>3.0300000000000002</v>
       </c>
     </row>
     <row r="716" spans="1:10" x14ac:dyDescent="0.25">
@@ -19970,25 +19925,25 @@
         <v>46087</v>
       </c>
       <c r="D716" s="14">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E716" s="9">
-        <v>37.5</v>
+        <v>23</v>
       </c>
       <c r="F716" s="9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G716" s="9">
         <v>0</v>
       </c>
       <c r="H716" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I716" s="36" t="s">
         <v>10</v>
       </c>
       <c r="J716" s="9">
-        <v>3.125</v>
+        <v>3.6149999999999998</v>
       </c>
     </row>
     <row r="717" spans="1:10" x14ac:dyDescent="0.25">
@@ -20002,22 +19957,22 @@
         <v>46088</v>
       </c>
       <c r="D717" s="14">
-        <v>26.5</v>
+        <v>29.5</v>
       </c>
       <c r="E717" s="9">
-        <v>39</v>
+        <v>22.5</v>
       </c>
       <c r="F717" s="9">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G717" s="9">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H717" s="9">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J717" s="9">
-        <v>10.815000000000001</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="718" spans="1:10" x14ac:dyDescent="0.25">
@@ -20054,20 +20009,20 @@
         <v>43</v>
       </c>
       <c r="B1" s="7"/>
-      <c r="C1" s="41">
+      <c r="C1" s="40">
         <v>0.85</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="42"/>
       <c r="O1" s="22" t="s">
         <v>39</v>
       </c>
@@ -27839,7 +27794,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q195" t="e">
-        <f t="shared" ref="Q195:Q219" si="13">O195-A195</f>
+        <f t="shared" ref="Q195:Q233" si="13">O195-A195</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -29271,7 +29226,7 @@
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B219" s="24">
         <v>46056</v>
@@ -29322,7 +29277,7 @@
       </c>
       <c r="Q219">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R219">
         <v>40</v>
@@ -29332,6 +29287,9 @@
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A220" s="14">
+        <v>18</v>
+      </c>
       <c r="B220" s="24">
         <v>46057</v>
       </c>
@@ -29379,6 +29337,10 @@
         <f t="shared" si="15"/>
         <v>5.55</v>
       </c>
+      <c r="Q220">
+        <f t="shared" si="13"/>
+        <v>-5</v>
+      </c>
       <c r="R220">
         <v>28</v>
       </c>
@@ -29387,6 +29349,9 @@
       </c>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A221" s="14">
+        <v>8</v>
+      </c>
       <c r="B221" s="24">
         <v>46058</v>
       </c>
@@ -29434,6 +29399,10 @@
         <f t="shared" si="15"/>
         <v>5.45</v>
       </c>
+      <c r="Q221">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
       <c r="R221">
         <v>31</v>
       </c>
@@ -29442,6 +29411,9 @@
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A222" s="14">
+        <v>17</v>
+      </c>
       <c r="B222" s="24">
         <v>46059</v>
       </c>
@@ -29489,6 +29461,10 @@
         <f t="shared" si="15"/>
         <v>6.69</v>
       </c>
+      <c r="Q222">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
       <c r="R222">
         <v>33</v>
       </c>
@@ -29497,6 +29473,9 @@
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A223" s="14">
+        <v>39</v>
+      </c>
       <c r="B223" s="24">
         <v>46060</v>
       </c>
@@ -29544,6 +29523,10 @@
         <f t="shared" si="15"/>
         <v>3.85</v>
       </c>
+      <c r="Q223">
+        <f t="shared" si="13"/>
+        <v>-24</v>
+      </c>
       <c r="R223">
         <v>24</v>
       </c>
@@ -29552,6 +29535,9 @@
       </c>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A224" s="14">
+        <v>16</v>
+      </c>
       <c r="B224" s="24">
         <v>46061</v>
       </c>
@@ -29599,6 +29585,10 @@
         <f t="shared" si="15"/>
         <v>13.45</v>
       </c>
+      <c r="Q224">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
       <c r="R224">
         <v>44</v>
       </c>
@@ -29606,7 +29596,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A225" s="14">
+        <v>2</v>
+      </c>
       <c r="B225" s="24">
         <v>46062</v>
       </c>
@@ -29654,6 +29647,10 @@
         <f t="shared" si="15"/>
         <v>8.1</v>
       </c>
+      <c r="Q225">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
       <c r="R225">
         <v>52</v>
       </c>
@@ -29661,7 +29658,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="226" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A226" s="14">
+        <v>19</v>
+      </c>
       <c r="B226" s="24">
         <v>46063</v>
       </c>
@@ -29709,6 +29709,10 @@
         <f t="shared" si="15"/>
         <v>6.87</v>
       </c>
+      <c r="Q226">
+        <f t="shared" si="13"/>
+        <v>-11</v>
+      </c>
       <c r="R226">
         <v>29</v>
       </c>
@@ -29716,7 +29720,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A227" s="14">
+        <v>5</v>
+      </c>
       <c r="B227" s="24">
         <v>46064</v>
       </c>
@@ -29764,6 +29771,10 @@
         <f t="shared" si="15"/>
         <v>6.5</v>
       </c>
+      <c r="Q227">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
       <c r="R227">
         <v>30</v>
       </c>
@@ -29771,7 +29782,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A228" s="14">
+        <v>2</v>
+      </c>
       <c r="B228" s="24">
         <v>46065</v>
       </c>
@@ -29819,6 +29833,10 @@
         <f t="shared" si="15"/>
         <v>5.0999999999999996</v>
       </c>
+      <c r="Q228">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
       <c r="R228">
         <v>26</v>
       </c>
@@ -29826,7 +29844,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A229" s="14">
+        <v>31</v>
+      </c>
       <c r="B229" s="24">
         <v>46066</v>
       </c>
@@ -29874,6 +29895,10 @@
         <f t="shared" si="15"/>
         <v>4.46</v>
       </c>
+      <c r="Q229">
+        <f t="shared" si="13"/>
+        <v>-18</v>
+      </c>
       <c r="R229">
         <v>22</v>
       </c>
@@ -29881,7 +29906,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="230" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A230" s="14">
+        <v>78</v>
+      </c>
       <c r="B230" s="24">
         <v>46067</v>
       </c>
@@ -29929,6 +29957,10 @@
         <f t="shared" si="15"/>
         <v>7.31</v>
       </c>
+      <c r="Q230">
+        <f t="shared" si="13"/>
+        <v>-58</v>
+      </c>
       <c r="R230">
         <v>28</v>
       </c>
@@ -29936,7 +29968,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A231" s="14">
+        <v>43</v>
+      </c>
       <c r="B231" s="24">
         <v>46068</v>
       </c>
@@ -29984,6 +30019,10 @@
         <f t="shared" si="15"/>
         <v>9.18</v>
       </c>
+      <c r="Q231">
+        <f t="shared" si="13"/>
+        <v>-15</v>
+      </c>
       <c r="R231">
         <v>56</v>
       </c>
@@ -29991,7 +30030,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A232" s="14">
+        <v>20</v>
+      </c>
       <c r="B232" s="24">
         <v>46069</v>
       </c>
@@ -30039,6 +30081,10 @@
         <f t="shared" si="15"/>
         <v>10.78</v>
       </c>
+      <c r="Q232">
+        <f t="shared" si="13"/>
+        <v>-5</v>
+      </c>
       <c r="R232">
         <v>40</v>
       </c>
@@ -30046,7 +30092,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="233" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A233" s="14">
+        <v>12</v>
+      </c>
       <c r="B233" s="24">
         <v>46070</v>
       </c>
@@ -30094,6 +30143,10 @@
         <f t="shared" si="15"/>
         <v>7.84</v>
       </c>
+      <c r="Q233">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
       <c r="R233">
         <v>39</v>
       </c>
@@ -30101,192 +30154,192 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B234" s="24">
         <v>46071</v>
       </c>
       <c r="C234">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D234">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E234">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F234">
         <v>16</v>
       </c>
       <c r="G234">
+        <v>26</v>
+      </c>
+      <c r="H234">
+        <v>29</v>
+      </c>
+      <c r="I234">
+        <v>21</v>
+      </c>
+      <c r="J234">
+        <v>15</v>
+      </c>
+      <c r="K234">
         <v>13</v>
       </c>
-      <c r="H234">
-        <v>10</v>
-      </c>
-      <c r="I234">
+      <c r="L234">
         <v>16</v>
       </c>
-      <c r="J234">
-        <v>9</v>
-      </c>
-      <c r="K234">
-        <v>10</v>
-      </c>
-      <c r="L234">
-        <v>12</v>
-      </c>
       <c r="M234">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N234">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O234" s="23">
         <f t="shared" si="14"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P234" s="23">
         <f t="shared" si="15"/>
-        <v>6.94</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="R234">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="S234">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="235" spans="2:19" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B235" s="24">
         <v>46072</v>
       </c>
       <c r="C235">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D235">
         <v>15</v>
       </c>
       <c r="E235">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F235">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G235">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H235">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I235">
         <v>17</v>
       </c>
       <c r="J235">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K235">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L235">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M235">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N235">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O235" s="23">
         <f t="shared" si="14"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P235" s="23">
         <f t="shared" si="15"/>
-        <v>3.78</v>
+        <v>2.46</v>
       </c>
       <c r="R235">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="S235">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="236" spans="2:19" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B236" s="24">
         <v>46073</v>
       </c>
       <c r="C236">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D236">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E236">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F236">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G236">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H236">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I236">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J236">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K236">
         <v>12</v>
       </c>
       <c r="L236">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M236">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N236">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O236" s="23">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P236" s="23">
         <f t="shared" si="15"/>
-        <v>5.01</v>
+        <v>3.23</v>
       </c>
       <c r="R236">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="S236">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="237" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B237" s="24">
         <v>46074</v>
       </c>
       <c r="C237">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D237">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E237">
+        <v>27</v>
+      </c>
+      <c r="F237">
+        <v>25</v>
+      </c>
+      <c r="G237">
         <v>15</v>
       </c>
-      <c r="F237">
-        <v>20</v>
-      </c>
-      <c r="G237">
-        <v>0</v>
-      </c>
       <c r="H237">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I237">
         <v>21</v>
@@ -30295,195 +30348,195 @@
         <v>18</v>
       </c>
       <c r="K237">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L237">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M237">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="N237">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O237" s="23">
         <f t="shared" si="14"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P237" s="23">
         <f t="shared" si="15"/>
-        <v>7.49</v>
+        <v>9.1</v>
       </c>
       <c r="R237">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="S237">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="238" spans="2:19" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B238" s="24">
         <v>46075</v>
       </c>
       <c r="C238">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D238">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E238">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F238">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G238">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H238">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="I238">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J238">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K238">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L238">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M238">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N238">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O238" s="23">
         <f t="shared" si="14"/>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P238" s="23">
         <f t="shared" si="15"/>
-        <v>13.98</v>
+        <v>11.87</v>
       </c>
       <c r="R238">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="S238">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="239" spans="2:19" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B239" s="24">
         <v>46076</v>
       </c>
       <c r="C239">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D239">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E239">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F239">
         <v>16</v>
       </c>
       <c r="G239">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H239">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I239">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J239">
         <v>16</v>
       </c>
       <c r="K239">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L239">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M239">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N239">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O239" s="23">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P239" s="23">
         <f t="shared" si="15"/>
-        <v>7.24</v>
+        <v>3.99</v>
       </c>
       <c r="R239">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="S239">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="240" spans="2:19" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B240" s="24">
         <v>46077</v>
       </c>
       <c r="C240">
+        <v>14</v>
+      </c>
+      <c r="D240">
+        <v>14</v>
+      </c>
+      <c r="E240">
+        <v>23</v>
+      </c>
+      <c r="F240">
         <v>19</v>
       </c>
-      <c r="D240">
-        <v>11</v>
-      </c>
-      <c r="E240">
-        <v>14</v>
-      </c>
-      <c r="F240">
+      <c r="G240">
+        <v>24</v>
+      </c>
+      <c r="H240">
+        <v>35</v>
+      </c>
+      <c r="I240">
         <v>21</v>
-      </c>
-      <c r="G240">
-        <v>17</v>
-      </c>
-      <c r="H240">
-        <v>19</v>
-      </c>
-      <c r="I240">
-        <v>26</v>
       </c>
       <c r="J240">
         <v>17</v>
       </c>
       <c r="K240">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L240">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M240">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N240">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O240" s="23">
         <f t="shared" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P240" s="23">
         <f t="shared" si="15"/>
-        <v>7.34</v>
+        <v>5.54</v>
       </c>
       <c r="R240">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="S240">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241" spans="2:19" x14ac:dyDescent="0.25">
@@ -30491,54 +30544,54 @@
         <v>46078</v>
       </c>
       <c r="C241">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D241">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F241">
         <v>10</v>
       </c>
       <c r="G241">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H241">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I241">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J241">
         <v>10</v>
       </c>
       <c r="K241">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L241">
         <v>10</v>
       </c>
       <c r="M241">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N241">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O241" s="23">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P241" s="23">
         <f t="shared" si="15"/>
-        <v>4.6100000000000003</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="R241">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="S241">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="242" spans="2:19" x14ac:dyDescent="0.25">
@@ -30546,37 +30599,37 @@
         <v>46079</v>
       </c>
       <c r="C242">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D242">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E242">
+        <v>20</v>
+      </c>
+      <c r="F242">
+        <v>14</v>
+      </c>
+      <c r="G242">
         <v>16</v>
       </c>
-      <c r="F242">
+      <c r="H242">
+        <v>14</v>
+      </c>
+      <c r="I242">
+        <v>20</v>
+      </c>
+      <c r="J242">
         <v>16</v>
       </c>
-      <c r="G242">
-        <v>3</v>
-      </c>
-      <c r="H242">
-        <v>13</v>
-      </c>
-      <c r="I242">
-        <v>18</v>
-      </c>
-      <c r="J242">
+      <c r="K242">
+        <v>12</v>
+      </c>
+      <c r="L242">
         <v>15</v>
       </c>
-      <c r="K242">
-        <v>18</v>
-      </c>
-      <c r="L242">
-        <v>21</v>
-      </c>
       <c r="M242">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N242">
         <v>16</v>
@@ -30587,13 +30640,13 @@
       </c>
       <c r="P242" s="23">
         <f t="shared" si="15"/>
-        <v>5.23</v>
+        <v>3.78</v>
       </c>
       <c r="R242">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="S242">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243" spans="2:19" x14ac:dyDescent="0.25">
@@ -30601,54 +30654,54 @@
         <v>46080</v>
       </c>
       <c r="C243">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D243">
+        <v>22</v>
+      </c>
+      <c r="E243">
+        <v>25</v>
+      </c>
+      <c r="F243">
+        <v>20</v>
+      </c>
+      <c r="G243">
+        <v>15</v>
+      </c>
+      <c r="H243">
+        <v>22</v>
+      </c>
+      <c r="I243">
+        <v>17</v>
+      </c>
+      <c r="J243">
         <v>16</v>
       </c>
-      <c r="E243">
-        <v>13</v>
-      </c>
-      <c r="F243">
-        <v>19</v>
-      </c>
-      <c r="G243">
-        <v>2</v>
-      </c>
-      <c r="H243">
-        <v>6</v>
-      </c>
-      <c r="I243">
+      <c r="K243">
+        <v>15</v>
+      </c>
+      <c r="L243">
+        <v>15</v>
+      </c>
+      <c r="M243">
         <v>22</v>
       </c>
-      <c r="J243">
-        <v>13</v>
-      </c>
-      <c r="K243">
-        <v>26</v>
-      </c>
-      <c r="L243">
-        <v>20</v>
-      </c>
-      <c r="M243">
-        <v>12</v>
-      </c>
       <c r="N243">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O243" s="23">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P243" s="23">
         <f t="shared" si="15"/>
-        <v>6.53</v>
+        <v>3.27</v>
       </c>
       <c r="R243">
         <v>23</v>
       </c>
       <c r="S243">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="244" spans="2:19" x14ac:dyDescent="0.25">
@@ -30656,54 +30709,54 @@
         <v>46081</v>
       </c>
       <c r="C244">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D244">
+        <v>24</v>
+      </c>
+      <c r="E244">
+        <v>23</v>
+      </c>
+      <c r="F244">
+        <v>21</v>
+      </c>
+      <c r="G244">
         <v>19</v>
       </c>
-      <c r="E244">
-        <v>17</v>
-      </c>
-      <c r="F244">
-        <v>13</v>
-      </c>
-      <c r="G244">
-        <v>10</v>
-      </c>
       <c r="H244">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I244">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J244">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K244">
+        <v>15</v>
+      </c>
+      <c r="L244">
+        <v>21</v>
+      </c>
+      <c r="M244">
         <v>18</v>
       </c>
-      <c r="L244">
+      <c r="N244">
         <v>23</v>
-      </c>
-      <c r="M244">
-        <v>25</v>
-      </c>
-      <c r="N244">
-        <v>24</v>
       </c>
       <c r="O244" s="23">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P244" s="23">
         <f t="shared" si="15"/>
-        <v>5.6</v>
+        <v>6.19</v>
       </c>
       <c r="R244">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="S244">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="2:19" x14ac:dyDescent="0.25">
@@ -30711,54 +30764,54 @@
         <v>46082</v>
       </c>
       <c r="C245">
+        <v>19</v>
+      </c>
+      <c r="D245">
+        <v>20</v>
+      </c>
+      <c r="E245">
+        <v>26</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245">
+        <v>29</v>
+      </c>
+      <c r="H245">
+        <v>29</v>
+      </c>
+      <c r="I245">
+        <v>28</v>
+      </c>
+      <c r="J245">
         <v>22</v>
       </c>
-      <c r="D245">
+      <c r="K245">
+        <v>17</v>
+      </c>
+      <c r="L245">
+        <v>19</v>
+      </c>
+      <c r="M245">
+        <v>14</v>
+      </c>
+      <c r="N245">
         <v>22</v>
-      </c>
-      <c r="E245">
-        <v>21</v>
-      </c>
-      <c r="F245">
-        <v>24</v>
-      </c>
-      <c r="G245">
-        <v>20</v>
-      </c>
-      <c r="H245">
-        <v>36</v>
-      </c>
-      <c r="I245">
-        <v>20</v>
-      </c>
-      <c r="J245">
-        <v>26</v>
-      </c>
-      <c r="K245">
-        <v>19</v>
-      </c>
-      <c r="L245">
-        <v>20</v>
-      </c>
-      <c r="M245">
-        <v>22</v>
-      </c>
-      <c r="N245">
-        <v>23</v>
       </c>
       <c r="O245" s="23">
         <f t="shared" si="14"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P245" s="23">
         <f t="shared" si="15"/>
-        <v>7.19</v>
+        <v>4.47</v>
       </c>
       <c r="R245">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="S245">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="246" spans="2:19" x14ac:dyDescent="0.25">
@@ -30766,54 +30819,54 @@
         <v>46083</v>
       </c>
       <c r="C246">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D246">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E246">
+        <v>24</v>
+      </c>
+      <c r="F246">
+        <v>19</v>
+      </c>
+      <c r="G246">
+        <v>16</v>
+      </c>
+      <c r="H246">
+        <v>32</v>
+      </c>
+      <c r="I246">
+        <v>14</v>
+      </c>
+      <c r="J246">
+        <v>21</v>
+      </c>
+      <c r="K246">
         <v>23</v>
       </c>
-      <c r="F246">
-        <v>25</v>
-      </c>
-      <c r="G246">
+      <c r="L246">
+        <v>16</v>
+      </c>
+      <c r="M246">
+        <v>34</v>
+      </c>
+      <c r="N246">
         <v>17</v>
-      </c>
-      <c r="H246">
-        <v>27</v>
-      </c>
-      <c r="I246">
-        <v>25</v>
-      </c>
-      <c r="J246">
-        <v>28</v>
-      </c>
-      <c r="K246">
-        <v>18</v>
-      </c>
-      <c r="L246">
-        <v>21</v>
-      </c>
-      <c r="M246">
-        <v>18</v>
-      </c>
-      <c r="N246">
-        <v>24</v>
       </c>
       <c r="O246" s="23">
         <f t="shared" si="14"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P246" s="23">
         <f t="shared" si="15"/>
-        <v>6.64</v>
+        <v>6.36</v>
       </c>
       <c r="R246">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="S246">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="2:19" x14ac:dyDescent="0.25">
@@ -30821,54 +30874,54 @@
         <v>46084</v>
       </c>
       <c r="C247">
+        <v>15</v>
+      </c>
+      <c r="D247">
+        <v>10</v>
+      </c>
+      <c r="E247">
+        <v>19</v>
+      </c>
+      <c r="F247">
+        <v>14</v>
+      </c>
+      <c r="G247">
+        <v>15</v>
+      </c>
+      <c r="H247">
+        <v>21</v>
+      </c>
+      <c r="I247">
+        <v>11</v>
+      </c>
+      <c r="J247">
+        <v>13</v>
+      </c>
+      <c r="K247">
+        <v>13</v>
+      </c>
+      <c r="L247">
         <v>12</v>
       </c>
-      <c r="D247">
-        <v>13</v>
-      </c>
-      <c r="E247">
+      <c r="M247">
+        <v>12</v>
+      </c>
+      <c r="N247">
         <v>11</v>
-      </c>
-      <c r="F247">
-        <v>16</v>
-      </c>
-      <c r="G247">
-        <v>14</v>
-      </c>
-      <c r="H247">
-        <v>18</v>
-      </c>
-      <c r="I247">
-        <v>22</v>
-      </c>
-      <c r="J247">
-        <v>16</v>
-      </c>
-      <c r="K247">
-        <v>20</v>
-      </c>
-      <c r="L247">
-        <v>13</v>
-      </c>
-      <c r="M247">
-        <v>16</v>
-      </c>
-      <c r="N247">
-        <v>13</v>
       </c>
       <c r="O247" s="23">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P247" s="23">
         <f t="shared" si="15"/>
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="R247">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S247">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="248" spans="2:19" x14ac:dyDescent="0.25">
@@ -30876,54 +30929,54 @@
         <v>46085</v>
       </c>
       <c r="C248">
+        <v>11</v>
+      </c>
+      <c r="D248">
+        <v>16</v>
+      </c>
+      <c r="E248">
+        <v>23</v>
+      </c>
+      <c r="F248">
+        <v>17</v>
+      </c>
+      <c r="G248">
+        <v>16</v>
+      </c>
+      <c r="H248">
+        <v>23</v>
+      </c>
+      <c r="I248">
         <v>12</v>
       </c>
-      <c r="D248">
+      <c r="J248">
+        <v>17</v>
+      </c>
+      <c r="K248">
+        <v>20</v>
+      </c>
+      <c r="L248">
         <v>12</v>
       </c>
-      <c r="E248">
-        <v>13</v>
-      </c>
-      <c r="F248">
-        <v>19</v>
-      </c>
-      <c r="G248">
-        <v>9</v>
-      </c>
-      <c r="H248">
-        <v>19</v>
-      </c>
-      <c r="I248">
-        <v>17</v>
-      </c>
-      <c r="J248">
-        <v>12</v>
-      </c>
-      <c r="K248">
-        <v>12</v>
-      </c>
-      <c r="L248">
+      <c r="M248">
         <v>10</v>
       </c>
-      <c r="M248">
-        <v>11</v>
-      </c>
       <c r="N248">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O248" s="23">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P248" s="23">
         <f t="shared" si="15"/>
-        <v>3.84</v>
+        <v>4.08</v>
       </c>
       <c r="R248">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S248">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="249" spans="2:19" x14ac:dyDescent="0.25">
@@ -30931,54 +30984,54 @@
         <v>46086</v>
       </c>
       <c r="C249">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D249">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E249">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F249">
         <v>17</v>
       </c>
       <c r="G249">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H249">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I249">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J249">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K249">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L249">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M249">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N249">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O249" s="23">
         <f t="shared" si="14"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P249" s="23">
         <f t="shared" si="15"/>
-        <v>7.03</v>
+        <v>2.4</v>
       </c>
       <c r="R249">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="S249">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250" spans="2:19" x14ac:dyDescent="0.25">
@@ -30986,54 +31039,54 @@
         <v>46087</v>
       </c>
       <c r="C250">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D250">
         <v>12</v>
       </c>
       <c r="E250">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F250">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G250">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H250">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I250">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J250">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K250">
+        <v>20</v>
+      </c>
+      <c r="L250">
         <v>12</v>
       </c>
-      <c r="L250">
-        <v>9</v>
-      </c>
       <c r="M250">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N250">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O250" s="23">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P250" s="23">
         <f t="shared" si="15"/>
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="R250">
         <v>13</v>
       </c>
       <c r="S250">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="251" spans="2:19" x14ac:dyDescent="0.25">
@@ -31041,54 +31094,54 @@
         <v>46088</v>
       </c>
       <c r="C251">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D251">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E251">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F251">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G251">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H251">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I251">
+        <v>17</v>
+      </c>
+      <c r="J251">
         <v>31</v>
       </c>
-      <c r="J251">
-        <v>20</v>
-      </c>
       <c r="K251">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L251">
         <v>31</v>
       </c>
       <c r="M251">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N251">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="O251" s="23">
         <f t="shared" si="14"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P251" s="23">
         <f t="shared" si="15"/>
-        <v>9.58</v>
+        <v>5.31</v>
       </c>
       <c r="R251">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S251">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="252" spans="2:19" x14ac:dyDescent="0.25">
@@ -31096,54 +31149,54 @@
         <v>41</v>
       </c>
       <c r="C252" s="32">
-        <v>29.36</v>
+        <v>34.42</v>
       </c>
       <c r="D252" s="32">
-        <v>26.14</v>
+        <v>30.07</v>
       </c>
       <c r="E252" s="32">
-        <v>21.18</v>
+        <v>27.96</v>
       </c>
       <c r="F252" s="32">
-        <v>18.86</v>
+        <v>27.09</v>
       </c>
       <c r="G252" s="32">
-        <v>19.850000000000001</v>
+        <v>29.35</v>
       </c>
       <c r="H252" s="32">
-        <v>16.97</v>
+        <v>20</v>
       </c>
       <c r="I252" s="32">
-        <v>23.97</v>
+        <v>28.58</v>
       </c>
       <c r="J252" s="32">
-        <v>21.55</v>
+        <v>28.01</v>
       </c>
       <c r="K252" s="32">
-        <v>28.46</v>
+        <v>31.54</v>
       </c>
       <c r="L252" s="32">
-        <v>27.05</v>
+        <v>30</v>
       </c>
       <c r="M252" s="32">
-        <v>26.12</v>
+        <v>30.62</v>
       </c>
       <c r="N252" s="33">
-        <v>30.92</v>
+        <v>31.05</v>
       </c>
       <c r="O252" s="34">
         <f>ROUND(AVERAGE(C252:N252,R252,S252),2)</f>
-        <v>24.2</v>
+        <v>29.1</v>
       </c>
       <c r="P252" s="34">
         <f>ROUND(_xlfn.STDEV.P(C252:N252,R252,S252),2)</f>
-        <v>3.98</v>
+        <v>3.09</v>
       </c>
       <c r="R252">
-        <v>24.06</v>
+        <v>28.34</v>
       </c>
       <c r="S252">
-        <v>24.36</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="253" spans="2:19" x14ac:dyDescent="0.25">
@@ -31151,86 +31204,86 @@
         <v>42</v>
       </c>
       <c r="C253" s="16">
-        <v>13.2</v>
+        <v>11.84</v>
       </c>
       <c r="D253" s="16">
-        <v>13.95</v>
+        <v>13.92</v>
       </c>
       <c r="E253" s="16">
-        <v>16.850000000000001</v>
+        <v>18.37</v>
       </c>
       <c r="F253" s="16">
-        <v>24.84</v>
+        <v>14.94</v>
       </c>
       <c r="G253" s="16">
-        <v>19.05</v>
+        <v>14.51</v>
       </c>
       <c r="H253" s="16">
-        <v>30.27</v>
+        <v>18.7</v>
       </c>
       <c r="I253" s="16">
-        <v>16.43</v>
+        <v>13.99</v>
       </c>
       <c r="J253" s="16">
-        <v>20.76</v>
+        <v>14.47</v>
       </c>
       <c r="K253" s="16">
-        <v>13.1</v>
+        <v>11.76</v>
       </c>
       <c r="L253" s="16">
-        <v>13.72</v>
+        <v>12.07</v>
       </c>
       <c r="M253" s="16">
-        <v>13.37</v>
+        <v>12.25</v>
       </c>
       <c r="N253" s="17">
-        <v>13.29</v>
+        <v>12.32</v>
       </c>
       <c r="O253" s="34">
         <f>ROUND(AVERAGE(C253:N253,R253,S253),2)</f>
-        <v>17.45</v>
+        <v>14.08</v>
       </c>
       <c r="P253" s="34">
         <f>ROUND(_xlfn.STDEV.P(C253:N253,R253,S253),2)</f>
-        <v>4.95</v>
+        <v>2.1</v>
       </c>
       <c r="R253">
-        <v>20.170000000000002</v>
+        <v>13.79</v>
       </c>
       <c r="S253">
-        <v>15.25</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="254" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B254" s="24"/>
-      <c r="C254" s="40" t="s">
+      <c r="C254" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D254" s="40"/>
-      <c r="E254" s="40" t="s">
+      <c r="D254" s="39"/>
+      <c r="E254" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F254" s="40"/>
-      <c r="G254" s="40" t="s">
+      <c r="F254" s="39"/>
+      <c r="G254" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H254" s="40"/>
-      <c r="I254" s="40" t="s">
+      <c r="H254" s="39"/>
+      <c r="I254" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="J254" s="40"/>
-      <c r="K254" s="44" t="s">
+      <c r="J254" s="39"/>
+      <c r="K254" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="L254" s="44"/>
-      <c r="M254" s="44" t="s">
+      <c r="L254" s="43"/>
+      <c r="M254" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="N254" s="44"/>
-      <c r="R254" s="40" t="s">
+      <c r="N254" s="43"/>
+      <c r="R254" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="S254" s="40"/>
+      <c r="S254" s="39"/>
     </row>
     <row r="255" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
@@ -31270,10 +31323,10 @@
         <v>56</v>
       </c>
       <c r="R255" t="s">
+        <v>55</v>
+      </c>
+      <c r="S255" t="s">
         <v>56</v>
-      </c>
-      <c r="S255" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="256" spans="2:19" x14ac:dyDescent="0.25">
@@ -31281,46 +31334,46 @@
         <v>57</v>
       </c>
       <c r="C256">
-        <v>78.900000000000006</v>
+        <v>72.492999999999995</v>
       </c>
       <c r="D256">
-        <v>75.400000000000006</v>
+        <v>71.766999999999996</v>
       </c>
       <c r="E256">
-        <v>112.1</v>
+        <v>85.573999999999998</v>
       </c>
       <c r="F256">
-        <v>96.2</v>
+        <v>73.179000000000002</v>
       </c>
       <c r="G256">
-        <v>35.9</v>
+        <v>24.437999999999999</v>
       </c>
       <c r="H256">
-        <v>22.2</v>
+        <v>12.88</v>
       </c>
       <c r="I256">
-        <v>129.1</v>
+        <v>121.943</v>
       </c>
       <c r="J256">
-        <v>127.3</v>
+        <v>124.828</v>
       </c>
       <c r="K256">
-        <v>106</v>
+        <v>86.710999999999999</v>
       </c>
       <c r="L256">
-        <v>98.9</v>
+        <v>89.936999999999998</v>
       </c>
       <c r="M256">
-        <v>182.2</v>
+        <v>148.298</v>
       </c>
       <c r="N256">
-        <v>190.5</v>
+        <v>146.03</v>
       </c>
       <c r="R256">
-        <v>198.3</v>
+        <v>191.82900000000001</v>
       </c>
       <c r="S256">
-        <v>205.6</v>
+        <v>183.238</v>
       </c>
     </row>
     <row r="257" spans="2:19" x14ac:dyDescent="0.25">
@@ -31333,29 +31386,29 @@
       <c r="F257" s="38"/>
       <c r="G257" s="38"/>
       <c r="H257" s="38"/>
-      <c r="I257" s="39">
-        <v>0.80600000000000005</v>
-      </c>
-      <c r="J257" s="39">
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="K257" s="39">
-        <v>0.80300000000000005</v>
-      </c>
-      <c r="L257" s="39">
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="M257" s="39">
-        <v>0.80300000000000005</v>
-      </c>
-      <c r="N257" s="39">
-        <v>0.85699999999999998</v>
-      </c>
-      <c r="R257" s="39">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="S257" s="39">
-        <v>0.74099999999999999</v>
+      <c r="I257" s="45">
+        <v>0.83809999999999996</v>
+      </c>
+      <c r="J257" s="45">
+        <v>0.85819999999999996</v>
+      </c>
+      <c r="K257" s="45">
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="L257" s="45">
+        <v>0.67910000000000004</v>
+      </c>
+      <c r="M257" s="45">
+        <v>0.75929999999999997</v>
+      </c>
+      <c r="N257" s="45">
+        <v>0.75360000000000005</v>
+      </c>
+      <c r="R257" s="45">
+        <v>0.72350000000000003</v>
+      </c>
+      <c r="S257" s="45">
+        <v>0.78800000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -31380,7 +31433,7 @@
       <formula>ABS(C116-$A116)&lt;=10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q219">
+  <conditionalFormatting sqref="Q1:Q233">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -31405,20 +31458,20 @@
         <v>43</v>
       </c>
       <c r="B1" s="7"/>
-      <c r="C1" s="41">
+      <c r="C1" s="40">
         <v>0.85</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="42"/>
       <c r="O1" s="22" t="s">
         <v>39</v>
       </c>
@@ -39083,7 +39136,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q195" t="e">
-        <f t="shared" ref="Q195:Q219" si="12">O195-A195</f>
+        <f t="shared" ref="Q195:Q233" si="12">O195-A195</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -40515,7 +40568,7 @@
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B219" s="24">
         <v>46056</v>
@@ -40566,7 +40619,7 @@
       </c>
       <c r="Q219">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="R219">
         <v>11</v>
@@ -40576,6 +40629,9 @@
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A220" s="14">
+        <v>18</v>
+      </c>
       <c r="B220" s="24">
         <v>46057</v>
       </c>
@@ -40623,6 +40679,10 @@
         <f t="shared" si="14"/>
         <v>4.53</v>
       </c>
+      <c r="Q220">
+        <f t="shared" si="12"/>
+        <v>-8</v>
+      </c>
       <c r="R220">
         <v>8</v>
       </c>
@@ -40631,6 +40691,9 @@
       </c>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A221" s="14">
+        <v>8</v>
+      </c>
       <c r="B221" s="24">
         <v>46058</v>
       </c>
@@ -40678,6 +40741,10 @@
         <f t="shared" si="14"/>
         <v>5.77</v>
       </c>
+      <c r="Q221">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
       <c r="R221">
         <v>10</v>
       </c>
@@ -40686,6 +40753,9 @@
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A222" s="14">
+        <v>17</v>
+      </c>
       <c r="B222" s="24">
         <v>46059</v>
       </c>
@@ -40733,6 +40803,10 @@
         <f t="shared" si="14"/>
         <v>5.55</v>
       </c>
+      <c r="Q222">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="R222">
         <v>15</v>
       </c>
@@ -40741,6 +40815,9 @@
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A223" s="14">
+        <v>39</v>
+      </c>
       <c r="B223" s="24">
         <v>46060</v>
       </c>
@@ -40788,6 +40865,10 @@
         <f t="shared" si="14"/>
         <v>5.08</v>
       </c>
+      <c r="Q223">
+        <f t="shared" si="12"/>
+        <v>-26</v>
+      </c>
       <c r="R223">
         <v>10</v>
       </c>
@@ -40796,6 +40877,9 @@
       </c>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A224" s="14">
+        <v>16</v>
+      </c>
       <c r="B224" s="24">
         <v>46061</v>
       </c>
@@ -40843,6 +40927,10 @@
         <f t="shared" si="14"/>
         <v>10.45</v>
       </c>
+      <c r="Q224">
+        <f t="shared" si="12"/>
+        <v>-6</v>
+      </c>
       <c r="R224">
         <v>12</v>
       </c>
@@ -40850,7 +40938,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A225" s="14">
+        <v>2</v>
+      </c>
       <c r="B225" s="24">
         <v>46062</v>
       </c>
@@ -40898,6 +40989,10 @@
         <f t="shared" si="14"/>
         <v>7.78</v>
       </c>
+      <c r="Q225">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
       <c r="R225">
         <v>15</v>
       </c>
@@ -40905,7 +41000,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A226" s="14">
+        <v>19</v>
+      </c>
       <c r="B226" s="24">
         <v>46063</v>
       </c>
@@ -40953,6 +41051,10 @@
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
+      <c r="Q226">
+        <f t="shared" si="12"/>
+        <v>-14</v>
+      </c>
       <c r="R226">
         <v>4</v>
       </c>
@@ -40960,7 +41062,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A227" s="14">
+        <v>5</v>
+      </c>
       <c r="B227" s="24">
         <v>46064</v>
       </c>
@@ -41008,6 +41113,10 @@
         <f t="shared" si="14"/>
         <v>3.15</v>
       </c>
+      <c r="Q227">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
       <c r="R227">
         <v>9</v>
       </c>
@@ -41015,7 +41124,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A228" s="14">
+        <v>2</v>
+      </c>
       <c r="B228" s="24">
         <v>46065</v>
       </c>
@@ -41063,6 +41175,10 @@
         <f t="shared" si="14"/>
         <v>2.82</v>
       </c>
+      <c r="Q228">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
       <c r="R228">
         <v>13</v>
       </c>
@@ -41070,7 +41186,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="229" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A229" s="14">
+        <v>31</v>
+      </c>
       <c r="B229" s="24">
         <v>46066</v>
       </c>
@@ -41118,6 +41237,10 @@
         <f t="shared" si="14"/>
         <v>3.34</v>
       </c>
+      <c r="Q229">
+        <f t="shared" si="12"/>
+        <v>-19</v>
+      </c>
       <c r="R229">
         <v>10</v>
       </c>
@@ -41125,7 +41248,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A230" s="14">
+        <v>78</v>
+      </c>
       <c r="B230" s="24">
         <v>46067</v>
       </c>
@@ -41173,6 +41299,10 @@
         <f t="shared" si="14"/>
         <v>8.51</v>
       </c>
+      <c r="Q230">
+        <f t="shared" si="12"/>
+        <v>-61</v>
+      </c>
       <c r="R230">
         <v>14</v>
       </c>
@@ -41180,7 +41310,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A231" s="14">
+        <v>43</v>
+      </c>
       <c r="B231" s="24">
         <v>46068</v>
       </c>
@@ -41228,6 +41361,10 @@
         <f t="shared" si="14"/>
         <v>7.09</v>
       </c>
+      <c r="Q231">
+        <f t="shared" si="12"/>
+        <v>-24</v>
+      </c>
       <c r="R231">
         <v>17</v>
       </c>
@@ -41235,7 +41372,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="232" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A232" s="14">
+        <v>20</v>
+      </c>
       <c r="B232" s="24">
         <v>46069</v>
       </c>
@@ -41283,6 +41423,10 @@
         <f t="shared" si="14"/>
         <v>5.74</v>
       </c>
+      <c r="Q232">
+        <f t="shared" si="12"/>
+        <v>-10</v>
+      </c>
       <c r="R232">
         <v>7</v>
       </c>
@@ -41290,7 +41434,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A233" s="14">
+        <v>12</v>
+      </c>
       <c r="B233" s="24">
         <v>46070</v>
       </c>
@@ -41338,6 +41485,10 @@
         <f t="shared" si="14"/>
         <v>3.21</v>
       </c>
+      <c r="Q233">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
       <c r="R233">
         <v>16</v>
       </c>
@@ -41345,389 +41496,389 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B234" s="24">
         <v>46071</v>
       </c>
       <c r="C234">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D234">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E234">
+        <v>20</v>
+      </c>
+      <c r="F234">
+        <v>13</v>
+      </c>
+      <c r="G234">
         <v>19</v>
       </c>
-      <c r="F234">
-        <v>9</v>
-      </c>
-      <c r="G234">
-        <v>14</v>
-      </c>
       <c r="H234">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I234">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J234">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K234">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L234">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M234">
         <v>23</v>
       </c>
       <c r="N234">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O234" s="23">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P234" s="23">
         <f t="shared" si="14"/>
-        <v>5.0599999999999996</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="R234">
         <v>16</v>
       </c>
       <c r="S234">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="235" spans="2:19" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B235" s="24">
         <v>46072</v>
       </c>
       <c r="C235">
+        <v>12</v>
+      </c>
+      <c r="D235">
+        <v>15</v>
+      </c>
+      <c r="E235">
+        <v>16</v>
+      </c>
+      <c r="F235">
+        <v>14</v>
+      </c>
+      <c r="G235">
+        <v>19</v>
+      </c>
+      <c r="H235">
+        <v>22</v>
+      </c>
+      <c r="I235">
+        <v>13</v>
+      </c>
+      <c r="J235">
+        <v>23</v>
+      </c>
+      <c r="K235">
+        <v>14</v>
+      </c>
+      <c r="L235">
         <v>17</v>
       </c>
-      <c r="D235">
+      <c r="M235">
+        <v>15</v>
+      </c>
+      <c r="N235">
         <v>16</v>
-      </c>
-      <c r="E235">
-        <v>15</v>
-      </c>
-      <c r="F235">
-        <v>11</v>
-      </c>
-      <c r="G235">
-        <v>14</v>
-      </c>
-      <c r="H235">
-        <v>10</v>
-      </c>
-      <c r="I235">
-        <v>16</v>
-      </c>
-      <c r="J235">
-        <v>9</v>
-      </c>
-      <c r="K235">
-        <v>13</v>
-      </c>
-      <c r="L235">
-        <v>14</v>
-      </c>
-      <c r="M235">
-        <v>19</v>
-      </c>
-      <c r="N235">
-        <v>14</v>
       </c>
       <c r="O235" s="23">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P235" s="23">
         <f t="shared" si="14"/>
-        <v>2.65</v>
+        <v>3.37</v>
       </c>
       <c r="R235">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S235">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="236" spans="2:19" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B236" s="24">
         <v>46073</v>
       </c>
       <c r="C236">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D236">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E236">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F236">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G236">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I236">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J236">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K236">
         <v>12</v>
       </c>
       <c r="L236">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M236">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N236">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O236" s="23">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P236" s="23">
         <f t="shared" si="14"/>
-        <v>4.5599999999999996</v>
+        <v>4.57</v>
       </c>
       <c r="R236">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S236">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="237" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B237" s="24">
         <v>46074</v>
       </c>
       <c r="C237">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D237">
+        <v>32</v>
+      </c>
+      <c r="E237">
+        <v>26</v>
+      </c>
+      <c r="F237">
+        <v>25</v>
+      </c>
+      <c r="G237">
+        <v>19</v>
+      </c>
+      <c r="H237">
+        <v>24</v>
+      </c>
+      <c r="I237">
+        <v>15</v>
+      </c>
+      <c r="J237">
+        <v>17</v>
+      </c>
+      <c r="K237">
+        <v>15</v>
+      </c>
+      <c r="L237">
         <v>23</v>
       </c>
-      <c r="E237">
-        <v>19</v>
-      </c>
-      <c r="F237">
-        <v>12</v>
-      </c>
-      <c r="G237">
-        <v>0</v>
-      </c>
-      <c r="H237">
-        <v>1</v>
-      </c>
-      <c r="I237">
-        <v>17</v>
-      </c>
-      <c r="J237">
-        <v>10</v>
-      </c>
-      <c r="K237">
+      <c r="M237">
+        <v>46</v>
+      </c>
+      <c r="N237">
         <v>29</v>
-      </c>
-      <c r="L237">
-        <v>24</v>
-      </c>
-      <c r="M237">
-        <v>27</v>
-      </c>
-      <c r="N237">
-        <v>25</v>
       </c>
       <c r="O237" s="23">
         <f t="shared" si="13"/>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="P237" s="23">
         <f t="shared" si="14"/>
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="R237">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="S237">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="238" spans="2:19" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B238" s="24">
         <v>46075</v>
       </c>
       <c r="C238">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D238">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E238">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F238">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G238">
         <v>19</v>
       </c>
       <c r="H238">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="I238">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J238">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K238">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L238">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M238">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="N238">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O238" s="23">
         <f t="shared" si="13"/>
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P238" s="23">
         <f t="shared" si="14"/>
-        <v>4.9000000000000004</v>
+        <v>13.77</v>
       </c>
       <c r="R238">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="S238">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="239" spans="2:19" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B239" s="24">
         <v>46076</v>
       </c>
       <c r="C239">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E239">
+        <v>16</v>
+      </c>
+      <c r="F239">
+        <v>11</v>
+      </c>
+      <c r="G239">
+        <v>19</v>
+      </c>
+      <c r="H239">
         <v>6</v>
       </c>
-      <c r="F239">
-        <v>5</v>
-      </c>
-      <c r="G239">
-        <v>6</v>
-      </c>
-      <c r="H239">
-        <v>1</v>
-      </c>
       <c r="I239">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J239">
         <v>6</v>
       </c>
       <c r="K239">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L239">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M239">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N239">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O239" s="23">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P239" s="23">
         <f t="shared" si="14"/>
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="R239">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="S239">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="240" spans="2:19" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B240" s="24">
         <v>46077</v>
       </c>
       <c r="C240">
+        <v>15</v>
+      </c>
+      <c r="D240">
+        <v>14</v>
+      </c>
+      <c r="E240">
         <v>19</v>
       </c>
-      <c r="D240">
-        <v>11</v>
-      </c>
-      <c r="E240">
+      <c r="F240">
+        <v>15</v>
+      </c>
+      <c r="G240">
+        <v>19</v>
+      </c>
+      <c r="H240">
+        <v>29</v>
+      </c>
+      <c r="I240">
+        <v>16</v>
+      </c>
+      <c r="J240">
+        <v>20</v>
+      </c>
+      <c r="K240">
+        <v>16</v>
+      </c>
+      <c r="L240">
+        <v>15</v>
+      </c>
+      <c r="M240">
         <v>17</v>
       </c>
-      <c r="F240">
-        <v>9</v>
-      </c>
-      <c r="G240">
-        <v>15</v>
-      </c>
-      <c r="H240">
-        <v>5</v>
-      </c>
-      <c r="I240">
-        <v>14</v>
-      </c>
-      <c r="J240">
-        <v>9</v>
-      </c>
-      <c r="K240">
-        <v>10</v>
-      </c>
-      <c r="L240">
-        <v>12</v>
-      </c>
-      <c r="M240">
-        <v>20</v>
-      </c>
       <c r="N240">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O240" s="23">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P240" s="23">
         <f t="shared" si="14"/>
-        <v>4.01</v>
+        <v>4.54</v>
       </c>
       <c r="R240">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S240">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="241" spans="2:19" x14ac:dyDescent="0.25">
@@ -41735,54 +41886,54 @@
         <v>46078</v>
       </c>
       <c r="C241">
+        <v>17</v>
+      </c>
+      <c r="D241">
+        <v>11</v>
+      </c>
+      <c r="E241">
+        <v>13</v>
+      </c>
+      <c r="F241">
+        <v>11</v>
+      </c>
+      <c r="G241">
+        <v>19</v>
+      </c>
+      <c r="H241">
+        <v>6</v>
+      </c>
+      <c r="I241">
         <v>12</v>
-      </c>
-      <c r="D241">
-        <v>8</v>
-      </c>
-      <c r="E241">
-        <v>7</v>
-      </c>
-      <c r="F241">
-        <v>4</v>
-      </c>
-      <c r="G241">
-        <v>7</v>
-      </c>
-      <c r="H241">
-        <v>1</v>
-      </c>
-      <c r="I241">
-        <v>13</v>
       </c>
       <c r="J241">
         <v>6</v>
       </c>
       <c r="K241">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L241">
+        <v>11</v>
+      </c>
+      <c r="M241">
+        <v>17</v>
+      </c>
+      <c r="N241">
         <v>10</v>
-      </c>
-      <c r="M241">
-        <v>1</v>
-      </c>
-      <c r="N241">
-        <v>8</v>
       </c>
       <c r="O241" s="23">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P241" s="23">
         <f t="shared" si="14"/>
-        <v>3.43</v>
+        <v>3.68</v>
       </c>
       <c r="R241">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S241">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="242" spans="2:19" x14ac:dyDescent="0.25">
@@ -41790,51 +41941,51 @@
         <v>46079</v>
       </c>
       <c r="C242">
+        <v>25</v>
+      </c>
+      <c r="D242">
+        <v>17</v>
+      </c>
+      <c r="E242">
         <v>21</v>
       </c>
-      <c r="D242">
-        <v>19</v>
-      </c>
-      <c r="E242">
-        <v>18</v>
-      </c>
       <c r="F242">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G242">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H242">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I242">
+        <v>14</v>
+      </c>
+      <c r="J242">
+        <v>17</v>
+      </c>
+      <c r="K242">
+        <v>12</v>
+      </c>
+      <c r="L242">
         <v>15</v>
       </c>
-      <c r="J242">
-        <v>8</v>
-      </c>
-      <c r="K242">
-        <v>17</v>
-      </c>
-      <c r="L242">
-        <v>21</v>
-      </c>
       <c r="M242">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N242">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O242" s="23">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P242" s="23">
         <f t="shared" si="14"/>
-        <v>5.93</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="R242">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S242">
         <v>11</v>
@@ -41845,54 +41996,54 @@
         <v>46080</v>
       </c>
       <c r="C243">
+        <v>16</v>
+      </c>
+      <c r="D243">
+        <v>22</v>
+      </c>
+      <c r="E243">
+        <v>22</v>
+      </c>
+      <c r="F243">
+        <v>29</v>
+      </c>
+      <c r="G243">
         <v>19</v>
       </c>
-      <c r="D243">
-        <v>17</v>
-      </c>
-      <c r="E243">
+      <c r="H243">
+        <v>18</v>
+      </c>
+      <c r="I243">
         <v>14</v>
       </c>
-      <c r="F243">
-        <v>10</v>
-      </c>
-      <c r="G243">
-        <v>0</v>
-      </c>
-      <c r="H243">
-        <v>0</v>
-      </c>
-      <c r="I243">
+      <c r="J243">
+        <v>11</v>
+      </c>
+      <c r="K243">
+        <v>15</v>
+      </c>
+      <c r="L243">
+        <v>15</v>
+      </c>
+      <c r="M243">
         <v>20</v>
       </c>
-      <c r="J243">
-        <v>8</v>
-      </c>
-      <c r="K243">
-        <v>25</v>
-      </c>
-      <c r="L243">
-        <v>20</v>
-      </c>
-      <c r="M243">
-        <v>13</v>
-      </c>
       <c r="N243">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O243" s="23">
         <f t="shared" si="13"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P243" s="23">
         <f t="shared" si="14"/>
-        <v>7.34</v>
+        <v>4.34</v>
       </c>
       <c r="R243">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="S243">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244" spans="2:19" x14ac:dyDescent="0.25">
@@ -41900,54 +42051,54 @@
         <v>46081</v>
       </c>
       <c r="C244">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D244">
+        <v>24</v>
+      </c>
+      <c r="E244">
+        <v>23</v>
+      </c>
+      <c r="F244">
         <v>18</v>
       </c>
-      <c r="E244">
-        <v>18</v>
-      </c>
-      <c r="F244">
-        <v>14</v>
-      </c>
       <c r="G244">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H244">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I244">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J244">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K244">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L244">
+        <v>21</v>
+      </c>
+      <c r="M244">
+        <v>16</v>
+      </c>
+      <c r="N244">
         <v>23</v>
-      </c>
-      <c r="M244">
-        <v>25</v>
-      </c>
-      <c r="N244">
-        <v>25</v>
       </c>
       <c r="O244" s="23">
         <f t="shared" si="13"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P244" s="23">
         <f t="shared" si="14"/>
-        <v>6.34</v>
+        <v>4.05</v>
       </c>
       <c r="R244">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="S244">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="2:19" x14ac:dyDescent="0.25">
@@ -41955,54 +42106,54 @@
         <v>46082</v>
       </c>
       <c r="C245">
+        <v>17</v>
+      </c>
+      <c r="D245">
+        <v>20</v>
+      </c>
+      <c r="E245">
+        <v>19</v>
+      </c>
+      <c r="F245">
+        <v>17</v>
+      </c>
+      <c r="G245">
         <v>22</v>
       </c>
-      <c r="D245">
-        <v>22</v>
-      </c>
-      <c r="E245">
-        <v>13</v>
-      </c>
-      <c r="F245">
+      <c r="H245">
+        <v>8</v>
+      </c>
+      <c r="I245">
+        <v>18</v>
+      </c>
+      <c r="J245">
+        <v>8</v>
+      </c>
+      <c r="K245">
+        <v>17</v>
+      </c>
+      <c r="L245">
+        <v>19</v>
+      </c>
+      <c r="M245">
         <v>14</v>
-      </c>
-      <c r="G245">
-        <v>21</v>
-      </c>
-      <c r="H245">
-        <v>3</v>
-      </c>
-      <c r="I245">
-        <v>15</v>
-      </c>
-      <c r="J245">
-        <v>10</v>
-      </c>
-      <c r="K245">
-        <v>19</v>
-      </c>
-      <c r="L245">
-        <v>20</v>
-      </c>
-      <c r="M245">
-        <v>23</v>
       </c>
       <c r="N245">
         <v>22</v>
       </c>
       <c r="O245" s="23">
         <f t="shared" si="13"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P245" s="23">
         <f t="shared" si="14"/>
-        <v>5.85</v>
+        <v>7.53</v>
       </c>
       <c r="R245">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="S245">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="2:19" x14ac:dyDescent="0.25">
@@ -42010,54 +42161,54 @@
         <v>46083</v>
       </c>
       <c r="C246">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D246">
+        <v>18</v>
+      </c>
+      <c r="E246">
+        <v>18</v>
+      </c>
+      <c r="F246">
+        <v>14</v>
+      </c>
+      <c r="G246">
         <v>20</v>
       </c>
-      <c r="E246">
-        <v>21</v>
-      </c>
-      <c r="F246">
-        <v>11</v>
-      </c>
-      <c r="G246">
+      <c r="H246">
         <v>12</v>
       </c>
-      <c r="H246">
-        <v>5</v>
-      </c>
       <c r="I246">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J246">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K246">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L246">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M246">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="N246">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O246" s="23">
         <f t="shared" si="13"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P246" s="23">
         <f t="shared" si="14"/>
-        <v>5.77</v>
+        <v>7.41</v>
       </c>
       <c r="R246">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="S246">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247" spans="2:19" x14ac:dyDescent="0.25">
@@ -42065,40 +42216,40 @@
         <v>46084</v>
       </c>
       <c r="C247">
+        <v>15</v>
+      </c>
+      <c r="D247">
+        <v>10</v>
+      </c>
+      <c r="E247">
+        <v>18</v>
+      </c>
+      <c r="F247">
+        <v>10</v>
+      </c>
+      <c r="G247">
+        <v>19</v>
+      </c>
+      <c r="H247">
+        <v>10</v>
+      </c>
+      <c r="I247">
         <v>12</v>
       </c>
-      <c r="D247">
+      <c r="J247">
+        <v>8</v>
+      </c>
+      <c r="K247">
         <v>13</v>
       </c>
-      <c r="E247">
+      <c r="L247">
+        <v>12</v>
+      </c>
+      <c r="M247">
+        <v>12</v>
+      </c>
+      <c r="N247">
         <v>11</v>
-      </c>
-      <c r="F247">
-        <v>9</v>
-      </c>
-      <c r="G247">
-        <v>8</v>
-      </c>
-      <c r="H247">
-        <v>7</v>
-      </c>
-      <c r="I247">
-        <v>22</v>
-      </c>
-      <c r="J247">
-        <v>9</v>
-      </c>
-      <c r="K247">
-        <v>19</v>
-      </c>
-      <c r="L247">
-        <v>13</v>
-      </c>
-      <c r="M247">
-        <v>15</v>
-      </c>
-      <c r="N247">
-        <v>13</v>
       </c>
       <c r="O247" s="23">
         <f t="shared" si="13"/>
@@ -42106,13 +42257,13 @@
       </c>
       <c r="P247" s="23">
         <f t="shared" si="14"/>
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="R247">
+        <v>14</v>
+      </c>
+      <c r="S247">
         <v>9</v>
-      </c>
-      <c r="S247">
-        <v>13</v>
       </c>
     </row>
     <row r="248" spans="2:19" x14ac:dyDescent="0.25">
@@ -42120,54 +42271,54 @@
         <v>46085</v>
       </c>
       <c r="C248">
+        <v>11</v>
+      </c>
+      <c r="D248">
+        <v>17</v>
+      </c>
+      <c r="E248">
+        <v>18</v>
+      </c>
+      <c r="F248">
+        <v>26</v>
+      </c>
+      <c r="G248">
+        <v>21</v>
+      </c>
+      <c r="H248">
+        <v>20</v>
+      </c>
+      <c r="I248">
         <v>12</v>
-      </c>
-      <c r="D248">
-        <v>11</v>
-      </c>
-      <c r="E248">
-        <v>0</v>
-      </c>
-      <c r="F248">
-        <v>7</v>
-      </c>
-      <c r="G248">
-        <v>13</v>
-      </c>
-      <c r="H248">
-        <v>0</v>
-      </c>
-      <c r="I248">
-        <v>11</v>
       </c>
       <c r="J248">
         <v>7</v>
       </c>
       <c r="K248">
+        <v>20</v>
+      </c>
+      <c r="L248">
         <v>12</v>
       </c>
-      <c r="L248">
+      <c r="M248">
         <v>10</v>
       </c>
-      <c r="M248">
-        <v>12</v>
-      </c>
       <c r="N248">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O248" s="23">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P248" s="23">
         <f t="shared" si="14"/>
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="R248">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="S248">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="2:19" x14ac:dyDescent="0.25">
@@ -42175,54 +42326,54 @@
         <v>46086</v>
       </c>
       <c r="C249">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D249">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E249">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F249">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G249">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H249">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I249">
+        <v>14</v>
+      </c>
+      <c r="J249">
         <v>19</v>
       </c>
-      <c r="J249">
-        <v>10</v>
-      </c>
       <c r="K249">
+        <v>14</v>
+      </c>
+      <c r="L249">
+        <v>21</v>
+      </c>
+      <c r="M249">
         <v>25</v>
       </c>
-      <c r="L249">
-        <v>27</v>
-      </c>
-      <c r="M249">
+      <c r="N249">
         <v>18</v>
-      </c>
-      <c r="N249">
-        <v>22</v>
       </c>
       <c r="O249" s="23">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P249" s="23">
         <f t="shared" si="14"/>
-        <v>8.2200000000000006</v>
+        <v>3.66</v>
       </c>
       <c r="R249">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S249">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="250" spans="2:19" x14ac:dyDescent="0.25">
@@ -42230,54 +42381,54 @@
         <v>46087</v>
       </c>
       <c r="C250">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D250">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E250">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F250">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G250">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I250">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J250">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K250">
+        <v>20</v>
+      </c>
+      <c r="L250">
         <v>12</v>
       </c>
-      <c r="L250">
-        <v>9</v>
-      </c>
       <c r="M250">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N250">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O250" s="23">
         <f t="shared" si="13"/>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P250" s="23">
         <f t="shared" si="14"/>
-        <v>3.56</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="R250">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S250">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="251" spans="2:19" x14ac:dyDescent="0.25">
@@ -42285,89 +42436,89 @@
         <v>46088</v>
       </c>
       <c r="C251">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D251">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E251">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F251">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G251">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I251">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J251">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K251">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L251">
         <v>31</v>
       </c>
       <c r="M251">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N251">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O251" s="23">
         <f t="shared" si="13"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P251" s="23">
         <f t="shared" si="14"/>
-        <v>12.05</v>
+        <v>4.55</v>
       </c>
       <c r="R251">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="S251">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="252" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B252" s="32"/>
-      <c r="C252" s="45" t="s">
+      <c r="C252" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D252" s="45"/>
-      <c r="E252" s="45" t="s">
+      <c r="D252" s="44"/>
+      <c r="E252" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="F252" s="45"/>
-      <c r="G252" s="45" t="s">
+      <c r="F252" s="44"/>
+      <c r="G252" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="H252" s="45"/>
-      <c r="I252" s="45" t="s">
+      <c r="H252" s="44"/>
+      <c r="I252" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="J252" s="45"/>
-      <c r="K252" s="45" t="s">
+      <c r="J252" s="44"/>
+      <c r="K252" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="L252" s="45"/>
-      <c r="M252" s="45" t="s">
+      <c r="L252" s="44"/>
+      <c r="M252" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="N252" s="45"/>
+      <c r="N252" s="44"/>
       <c r="O252" s="32"/>
       <c r="P252" s="32"/>
       <c r="Q252" s="32"/>
-      <c r="R252" s="45" t="s">
+      <c r="R252" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="S252" s="45"/>
+      <c r="S252" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -42388,7 +42539,7 @@
       <formula>ABS(C116-$A116)&lt;=10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q219">
+  <conditionalFormatting sqref="Q1:Q233">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/restaurant_analytics/data/mornings.xlsx
+++ b/restaurant_analytics/data/mornings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cardi\Documents\git-repo\swe_dev\restaurant_analytics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABE66E6-2FEC-4F78-A8CF-27C8B5808296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4834C399-6143-4688-83AC-4395B7F424CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
     <t>day</t>
   </si>
@@ -216,6 +216,9 @@
   <si>
     <t>trn %</t>
   </si>
+  <si>
+    <t>lent Friday</t>
+  </si>
 </sst>
 </file>
 
@@ -268,7 +271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -483,11 +486,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -565,7 +605,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -577,13 +622,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,7 +1015,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K722"/>
+  <dimension ref="A1:K759"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
@@ -19146,7 +19193,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="689" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" s="6">
         <v>7</v>
       </c>
@@ -19172,7 +19219,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="690" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" s="6">
         <v>1</v>
       </c>
@@ -19201,7 +19248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="691" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" s="6">
         <v>2</v>
       </c>
@@ -19227,7 +19274,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="692" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" s="6">
         <v>3</v>
       </c>
@@ -19253,7 +19300,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="693" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" s="6">
         <v>4</v>
       </c>
@@ -19279,7 +19326,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="694" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" s="6">
         <v>5</v>
       </c>
@@ -19305,7 +19352,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="695" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" s="6">
         <v>6</v>
       </c>
@@ -19319,7 +19366,7 @@
         <v>31</v>
       </c>
       <c r="E695" s="9">
-        <v>34</v>
+        <v>36.1</v>
       </c>
       <c r="F695" s="9">
         <v>0</v>
@@ -19328,10 +19375,10 @@
         <v>0</v>
       </c>
       <c r="H695" s="9">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="696" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" s="6">
         <v>7</v>
       </c>
@@ -19345,7 +19392,7 @@
         <v>78</v>
       </c>
       <c r="E696" s="9">
-        <v>36.9</v>
+        <v>41.2</v>
       </c>
       <c r="F696" s="9">
         <v>0</v>
@@ -19354,13 +19401,13 @@
         <v>0</v>
       </c>
       <c r="H696" s="9">
-        <v>8.1999999999999993</v>
+        <v>3.4</v>
       </c>
       <c r="I696" s="36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="697" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" s="6">
         <v>1</v>
       </c>
@@ -19374,19 +19421,19 @@
         <v>43</v>
       </c>
       <c r="E697" s="9">
-        <v>44.2</v>
+        <v>42.8</v>
       </c>
       <c r="F697" s="9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G697" s="9">
         <v>0</v>
       </c>
       <c r="H697" s="9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="698" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" s="6">
         <v>2</v>
       </c>
@@ -19400,22 +19447,22 @@
         <v>20</v>
       </c>
       <c r="E698" s="9">
-        <v>48.9</v>
+        <v>47.7</v>
       </c>
       <c r="F698" s="9">
         <v>0</v>
       </c>
       <c r="G698" s="9">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="H698" s="9">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="I698" s="36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="699" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" s="6">
         <v>3</v>
       </c>
@@ -19429,19 +19476,19 @@
         <v>12</v>
       </c>
       <c r="E699" s="9">
-        <v>48.4</v>
+        <v>50.2</v>
       </c>
       <c r="F699" s="9">
-        <v>5.0999999999999997E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G699" s="9">
         <v>0</v>
       </c>
       <c r="H699" s="9">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="700" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" s="6">
         <v>4</v>
       </c>
@@ -19452,28 +19499,25 @@
         <v>46071</v>
       </c>
       <c r="D700" s="14">
-        <v>18.5</v>
+        <v>3</v>
       </c>
       <c r="E700" s="9">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="F700" s="9">
-        <v>0</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G700" s="9">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H700" s="9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="I700" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="J700" s="9">
-        <v>4.7699999999999996</v>
-      </c>
-    </row>
-    <row r="701" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" s="6">
         <v>5</v>
       </c>
@@ -19484,25 +19528,22 @@
         <v>46072</v>
       </c>
       <c r="D701" s="14">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="E701" s="9">
-        <v>45.3</v>
+        <v>47.5</v>
       </c>
       <c r="F701" s="9">
-        <v>0</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="G701" s="9">
         <v>0</v>
       </c>
       <c r="H701" s="9">
-        <v>9.1</v>
-      </c>
-      <c r="J701" s="9">
-        <v>2.915</v>
-      </c>
-    </row>
-    <row r="702" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" s="6">
         <v>6</v>
       </c>
@@ -19513,28 +19554,25 @@
         <v>46073</v>
       </c>
       <c r="D702" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E702" s="9">
-        <v>38.299999999999997</v>
+        <v>35.4</v>
       </c>
       <c r="F702" s="9">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G702" s="9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H702" s="9">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="I702" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="J702" s="9">
-        <v>3.9000000000000004</v>
-      </c>
-    </row>
-    <row r="703" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" s="6">
         <v>7</v>
       </c>
@@ -19545,25 +19583,22 @@
         <v>46074</v>
       </c>
       <c r="D703" s="14">
-        <v>25.5</v>
+        <v>19</v>
       </c>
       <c r="E703" s="9">
-        <v>31.6</v>
+        <v>27.1</v>
       </c>
       <c r="F703" s="9">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G703" s="9">
         <v>0</v>
       </c>
       <c r="H703" s="9">
-        <v>11.7</v>
-      </c>
-      <c r="J703" s="9">
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="704" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" s="6">
         <v>1</v>
       </c>
@@ -19574,10 +19609,10 @@
         <v>46075</v>
       </c>
       <c r="D704" s="14">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="E704" s="9">
-        <v>28.4</v>
+        <v>24.4</v>
       </c>
       <c r="F704" s="9">
         <v>0</v>
@@ -19586,13 +19621,10 @@
         <v>0</v>
       </c>
       <c r="H704" s="9">
-        <v>10</v>
-      </c>
-      <c r="J704" s="9">
-        <v>12.82</v>
-      </c>
-    </row>
-    <row r="705" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" s="6">
         <v>2</v>
       </c>
@@ -19603,10 +19635,10 @@
         <v>46076</v>
       </c>
       <c r="D705" s="14">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="E705" s="9">
-        <v>28.8</v>
+        <v>21.9</v>
       </c>
       <c r="F705" s="9">
         <v>0</v>
@@ -19615,13 +19647,10 @@
         <v>0</v>
       </c>
       <c r="H705" s="9">
-        <v>10.4</v>
-      </c>
-      <c r="J705" s="9">
-        <v>3.895</v>
-      </c>
-    </row>
-    <row r="706" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" s="6">
         <v>3</v>
       </c>
@@ -19632,10 +19661,10 @@
         <v>46077</v>
       </c>
       <c r="D706" s="14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E706" s="9">
-        <v>31.8</v>
+        <v>25.7</v>
       </c>
       <c r="F706" s="9">
         <v>0</v>
@@ -19644,13 +19673,10 @@
         <v>0</v>
       </c>
       <c r="H706" s="9">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="J706" s="9">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="707" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" s="6">
         <v>4</v>
       </c>
@@ -19661,25 +19687,22 @@
         <v>46078</v>
       </c>
       <c r="D707" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E707" s="9">
-        <v>22</v>
+        <v>32.5</v>
       </c>
       <c r="F707" s="9">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G707" s="9">
         <v>0.36</v>
       </c>
       <c r="H707" s="9">
-        <v>9</v>
-      </c>
-      <c r="J707" s="9">
-        <v>3.0550000000000002</v>
-      </c>
-    </row>
-    <row r="708" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" s="6">
         <v>5</v>
       </c>
@@ -19690,25 +19713,22 @@
         <v>46079</v>
       </c>
       <c r="D708" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E708" s="9">
-        <v>28</v>
+        <v>30.2</v>
       </c>
       <c r="F708" s="9">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="G708" s="9">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H708" s="9">
-        <v>6</v>
-      </c>
-      <c r="J708" s="9">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="709" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" s="6">
         <v>6</v>
       </c>
@@ -19719,28 +19739,25 @@
         <v>46080</v>
       </c>
       <c r="D709" s="14">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="E709" s="9">
-        <v>25</v>
+        <v>43.2</v>
       </c>
       <c r="F709" s="9">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G709" s="9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="H709" s="9">
-        <v>15</v>
+        <v>10.3</v>
       </c>
       <c r="I709" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="J709" s="9">
-        <v>3.8049999999999997</v>
-      </c>
-    </row>
-    <row r="710" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" s="6">
         <v>7</v>
       </c>
@@ -19751,10 +19768,10 @@
         <v>46081</v>
       </c>
       <c r="D710" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E710" s="9">
-        <v>21.5</v>
+        <v>39.9</v>
       </c>
       <c r="F710" s="9">
         <v>0</v>
@@ -19763,13 +19780,10 @@
         <v>0</v>
       </c>
       <c r="H710" s="9">
-        <v>7</v>
-      </c>
-      <c r="J710" s="9">
-        <v>5.12</v>
-      </c>
-    </row>
-    <row r="711" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" s="6">
         <v>1</v>
       </c>
@@ -19780,25 +19794,22 @@
         <v>46082</v>
       </c>
       <c r="D711" s="14">
-        <v>20.5</v>
+        <v>70</v>
       </c>
       <c r="E711" s="9">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="F711" s="9">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G711" s="9">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="H711" s="9">
-        <v>4</v>
-      </c>
-      <c r="J711" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="712" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" s="6">
         <v>2</v>
       </c>
@@ -19809,25 +19820,22 @@
         <v>46083</v>
       </c>
       <c r="D712" s="14">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="E712" s="9">
-        <v>24.5</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="F712" s="9">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G712" s="9">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="H712" s="9">
-        <v>7</v>
-      </c>
-      <c r="J712" s="9">
-        <v>6.8849999999999998</v>
-      </c>
-    </row>
-    <row r="713" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" s="6">
         <v>3</v>
       </c>
@@ -19838,25 +19846,22 @@
         <v>46084</v>
       </c>
       <c r="D713" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E713" s="9">
-        <v>23</v>
+        <v>36.5</v>
       </c>
       <c r="F713" s="9">
-        <v>0</v>
+        <v>3.1E-2</v>
       </c>
       <c r="G713" s="9">
         <v>0</v>
       </c>
       <c r="H713" s="9">
-        <v>8</v>
-      </c>
-      <c r="J713" s="9">
-        <v>3.0149999999999997</v>
-      </c>
-    </row>
-    <row r="714" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" s="6">
         <v>4</v>
       </c>
@@ -19867,25 +19872,22 @@
         <v>46085</v>
       </c>
       <c r="D714" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E714" s="9">
-        <v>23</v>
+        <v>37.9</v>
       </c>
       <c r="F714" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G714" s="9">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H714" s="9">
-        <v>6</v>
-      </c>
-      <c r="J714" s="9">
-        <v>4.665</v>
-      </c>
-    </row>
-    <row r="715" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" s="6">
         <v>5</v>
       </c>
@@ -19896,25 +19898,22 @@
         <v>46086</v>
       </c>
       <c r="D715" s="14">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="E715" s="9">
-        <v>24.5</v>
+        <v>43.3</v>
       </c>
       <c r="F715" s="9">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="G715" s="9">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="H715" s="9">
-        <v>23</v>
-      </c>
-      <c r="J715" s="9">
-        <v>3.0300000000000002</v>
-      </c>
-    </row>
-    <row r="716" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" s="6">
         <v>6</v>
       </c>
@@ -19925,28 +19924,25 @@
         <v>46087</v>
       </c>
       <c r="D716" s="14">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="E716" s="9">
-        <v>23</v>
+        <v>54.5</v>
       </c>
       <c r="F716" s="9">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="G716" s="9">
         <v>0</v>
       </c>
       <c r="H716" s="9">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="I716" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="J716" s="9">
-        <v>3.6149999999999998</v>
-      </c>
-    </row>
-    <row r="717" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" s="6">
         <v>7</v>
       </c>
@@ -19957,38 +19953,1203 @@
         <v>46088</v>
       </c>
       <c r="D717" s="14">
+        <v>13</v>
+      </c>
+      <c r="E717" s="9">
+        <v>52.3</v>
+      </c>
+      <c r="F717" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="G717" s="9">
+        <v>0</v>
+      </c>
+      <c r="H717" s="9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A718" s="6">
+        <v>1</v>
+      </c>
+      <c r="B718" s="6">
+        <v>717</v>
+      </c>
+      <c r="C718" s="7">
+        <v>46089</v>
+      </c>
+      <c r="D718" s="14">
+        <v>73</v>
+      </c>
+      <c r="E718" s="9">
+        <v>48.6</v>
+      </c>
+      <c r="F718" s="9">
+        <v>0</v>
+      </c>
+      <c r="G718" s="9">
+        <v>0</v>
+      </c>
+      <c r="H718" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="I718" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A719" s="6">
+        <v>2</v>
+      </c>
+      <c r="B719" s="6">
+        <v>718</v>
+      </c>
+      <c r="C719" s="7">
+        <v>46090</v>
+      </c>
+      <c r="D719" s="14">
+        <v>12</v>
+      </c>
+      <c r="E719" s="9">
+        <v>59.4</v>
+      </c>
+      <c r="F719" s="9">
+        <v>0</v>
+      </c>
+      <c r="G719" s="9">
+        <v>0</v>
+      </c>
+      <c r="H719" s="9">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A720" s="6">
+        <v>3</v>
+      </c>
+      <c r="B720" s="6">
+        <v>719</v>
+      </c>
+      <c r="C720" s="7">
+        <v>46091</v>
+      </c>
+      <c r="D720" s="14">
+        <v>27</v>
+      </c>
+      <c r="E720" s="9">
+        <v>51.8</v>
+      </c>
+      <c r="F720" s="9">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="G720" s="9">
+        <v>0</v>
+      </c>
+      <c r="H720" s="9">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A721" s="6">
+        <v>4</v>
+      </c>
+      <c r="B721" s="6">
+        <v>720</v>
+      </c>
+      <c r="C721" s="7">
+        <v>46092</v>
+      </c>
+      <c r="D721" s="14">
+        <v>24</v>
+      </c>
+      <c r="E721" s="9">
+        <v>40.5</v>
+      </c>
+      <c r="F721" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="G721" s="9">
+        <v>0</v>
+      </c>
+      <c r="H721" s="9">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A722" s="6">
+        <v>5</v>
+      </c>
+      <c r="B722" s="6">
+        <v>721</v>
+      </c>
+      <c r="C722" s="7">
+        <v>46093</v>
+      </c>
+      <c r="D722" s="14">
+        <v>4</v>
+      </c>
+      <c r="E722" s="9">
+        <v>39.9</v>
+      </c>
+      <c r="F722" s="9">
+        <v>0</v>
+      </c>
+      <c r="G722" s="9">
+        <v>0</v>
+      </c>
+      <c r="H722" s="9">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A723" s="6">
+        <v>6</v>
+      </c>
+      <c r="B723" s="6">
+        <v>722</v>
+      </c>
+      <c r="C723" s="7">
+        <v>46094</v>
+      </c>
+      <c r="D723" s="14">
+        <v>28</v>
+      </c>
+      <c r="E723" s="9">
+        <v>44.1</v>
+      </c>
+      <c r="F723" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="G723" s="9">
+        <v>0</v>
+      </c>
+      <c r="H723" s="9">
+        <v>17</v>
+      </c>
+      <c r="I723" s="36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="724" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A724" s="6">
+        <v>7</v>
+      </c>
+      <c r="B724" s="6">
+        <v>723</v>
+      </c>
+      <c r="C724" s="7">
+        <v>46095</v>
+      </c>
+      <c r="D724" s="14">
+        <v>17</v>
+      </c>
+      <c r="E724" s="9">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="F724" s="9">
+        <v>0</v>
+      </c>
+      <c r="G724" s="9">
+        <v>0</v>
+      </c>
+      <c r="H724" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="725" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A725" s="6">
+        <v>1</v>
+      </c>
+      <c r="B725" s="6">
+        <v>724</v>
+      </c>
+      <c r="C725" s="7">
+        <v>46096</v>
+      </c>
+      <c r="D725" s="14">
+        <v>66</v>
+      </c>
+      <c r="E725" s="9">
+        <v>38.1</v>
+      </c>
+      <c r="F725" s="9">
+        <v>1.42</v>
+      </c>
+      <c r="G725" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H725" s="9">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="726" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A726" s="6">
+        <v>2</v>
+      </c>
+      <c r="B726" s="6">
+        <v>725</v>
+      </c>
+      <c r="C726" s="7">
+        <v>46097</v>
+      </c>
+      <c r="D726" s="14">
+        <v>7</v>
+      </c>
+      <c r="E726" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F726" s="9">
+        <v>0</v>
+      </c>
+      <c r="G726" s="9">
+        <v>0</v>
+      </c>
+      <c r="H726" s="9">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A727" s="6">
+        <v>3</v>
+      </c>
+      <c r="B727" s="6">
+        <v>726</v>
+      </c>
+      <c r="C727" s="7">
+        <v>46098</v>
+      </c>
+      <c r="D727" s="14">
+        <v>13</v>
+      </c>
+      <c r="E727" s="9">
         <v>29.5</v>
       </c>
-      <c r="E717" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F717" s="9">
-        <v>0</v>
-      </c>
-      <c r="G717" s="9">
-        <v>0</v>
-      </c>
-      <c r="H717" s="9">
+      <c r="F727" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="G727" s="9">
+        <v>0</v>
+      </c>
+      <c r="H727" s="9">
+        <v>10.4</v>
+      </c>
+      <c r="I727" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="J727" s="9">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A728" s="6">
+        <v>4</v>
+      </c>
+      <c r="B728" s="6">
+        <v>727</v>
+      </c>
+      <c r="C728" s="7">
+        <v>46099</v>
+      </c>
+      <c r="D728" s="14">
+        <v>14.5</v>
+      </c>
+      <c r="E728" s="9">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F728" s="9">
+        <v>0</v>
+      </c>
+      <c r="G728" s="9">
+        <v>0</v>
+      </c>
+      <c r="H728" s="9">
+        <v>10.3</v>
+      </c>
+      <c r="J728" s="9">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A729" s="6">
+        <v>5</v>
+      </c>
+      <c r="B729" s="6">
+        <v>728</v>
+      </c>
+      <c r="C729" s="7">
+        <v>46100</v>
+      </c>
+      <c r="D729" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="E729" s="9">
+        <v>38.5</v>
+      </c>
+      <c r="F729" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="G729" s="9">
+        <v>0</v>
+      </c>
+      <c r="H729" s="9">
+        <v>10.7</v>
+      </c>
+      <c r="J729" s="9">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A730" s="6">
         <v>6</v>
       </c>
-      <c r="J717" s="9">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="718" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A718" s="6"/>
-    </row>
-    <row r="719" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A719" s="6"/>
-    </row>
-    <row r="720" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A720" s="6"/>
-    </row>
-    <row r="721" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A721" s="6"/>
-    </row>
-    <row r="722" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A722" s="6"/>
+      <c r="B730" s="6">
+        <v>729</v>
+      </c>
+      <c r="C730" s="7">
+        <v>46101</v>
+      </c>
+      <c r="D730" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="E730" s="9">
+        <v>49</v>
+      </c>
+      <c r="F730" s="9">
+        <v>0</v>
+      </c>
+      <c r="G730" s="9">
+        <v>0</v>
+      </c>
+      <c r="H730" s="9">
+        <v>9</v>
+      </c>
+      <c r="J730" s="9">
+        <v>7.0750000000000002</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A731" s="6">
+        <v>7</v>
+      </c>
+      <c r="B731" s="6">
+        <v>730</v>
+      </c>
+      <c r="C731" s="7">
+        <v>46102</v>
+      </c>
+      <c r="D731" s="14">
+        <v>35.5</v>
+      </c>
+      <c r="E731" s="9">
+        <v>58</v>
+      </c>
+      <c r="F731" s="9">
+        <v>0</v>
+      </c>
+      <c r="G731" s="9">
+        <v>0</v>
+      </c>
+      <c r="H731" s="9">
+        <v>8</v>
+      </c>
+      <c r="J731" s="9">
+        <v>15.074999999999999</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A732" s="6">
+        <v>1</v>
+      </c>
+      <c r="B732" s="6">
+        <v>731</v>
+      </c>
+      <c r="C732" s="7">
+        <v>46103</v>
+      </c>
+      <c r="D732" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="E732" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="F732" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="G732" s="9">
+        <v>0</v>
+      </c>
+      <c r="H732" s="9">
+        <v>17</v>
+      </c>
+      <c r="J732" s="9">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="733" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A733" s="6">
+        <v>2</v>
+      </c>
+      <c r="B733" s="6">
+        <v>732</v>
+      </c>
+      <c r="C733" s="7">
+        <v>46104</v>
+      </c>
+      <c r="D733" s="14">
+        <v>21</v>
+      </c>
+      <c r="E733" s="9">
+        <v>34</v>
+      </c>
+      <c r="F733" s="9">
+        <v>0</v>
+      </c>
+      <c r="G733" s="9">
+        <v>0</v>
+      </c>
+      <c r="H733" s="9">
+        <v>8</v>
+      </c>
+      <c r="J733" s="9">
+        <v>6.375</v>
+      </c>
+    </row>
+    <row r="734" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A734" s="6">
+        <v>3</v>
+      </c>
+      <c r="B734" s="6">
+        <v>733</v>
+      </c>
+      <c r="C734" s="7">
+        <v>46105</v>
+      </c>
+      <c r="D734" s="14">
+        <v>17</v>
+      </c>
+      <c r="E734" s="9">
+        <v>39.5</v>
+      </c>
+      <c r="F734" s="9">
+        <v>0</v>
+      </c>
+      <c r="G734" s="9">
+        <v>0</v>
+      </c>
+      <c r="H734" s="9">
+        <v>5</v>
+      </c>
+      <c r="J734" s="9">
+        <v>3.4450000000000003</v>
+      </c>
+    </row>
+    <row r="735" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A735" s="6">
+        <v>4</v>
+      </c>
+      <c r="B735" s="6">
+        <v>734</v>
+      </c>
+      <c r="C735" s="7">
+        <v>46106</v>
+      </c>
+      <c r="D735" s="14">
+        <v>18.5</v>
+      </c>
+      <c r="E735" s="9">
+        <v>47.5</v>
+      </c>
+      <c r="F735" s="9">
+        <v>0</v>
+      </c>
+      <c r="G735" s="9">
+        <v>0</v>
+      </c>
+      <c r="H735" s="9">
+        <v>6</v>
+      </c>
+      <c r="J735" s="9">
+        <v>4.0150000000000006</v>
+      </c>
+    </row>
+    <row r="736" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A736" s="6">
+        <v>5</v>
+      </c>
+      <c r="B736" s="6">
+        <v>735</v>
+      </c>
+      <c r="C736" s="7">
+        <v>46107</v>
+      </c>
+      <c r="D736" s="14">
+        <v>20.5</v>
+      </c>
+      <c r="E736" s="9">
+        <v>42.5</v>
+      </c>
+      <c r="F736" s="9">
+        <v>0</v>
+      </c>
+      <c r="G736" s="9">
+        <v>0</v>
+      </c>
+      <c r="H736" s="9">
+        <v>8</v>
+      </c>
+      <c r="J736" s="9">
+        <v>4.6199999999999992</v>
+      </c>
+    </row>
+    <row r="737" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A737" s="6">
+        <v>6</v>
+      </c>
+      <c r="B737" s="6">
+        <v>736</v>
+      </c>
+      <c r="C737" s="7">
+        <v>46108</v>
+      </c>
+      <c r="D737" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="E737" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="F737" s="9">
+        <v>0</v>
+      </c>
+      <c r="G737" s="9">
+        <v>0</v>
+      </c>
+      <c r="H737" s="9">
+        <v>8</v>
+      </c>
+      <c r="I737" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J737" s="9">
+        <v>3.0550000000000002</v>
+      </c>
+    </row>
+    <row r="738" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A738" s="6">
+        <v>7</v>
+      </c>
+      <c r="B738" s="6">
+        <v>737</v>
+      </c>
+      <c r="C738" s="7">
+        <v>46109</v>
+      </c>
+      <c r="D738" s="14">
+        <v>21</v>
+      </c>
+      <c r="E738" s="9">
+        <v>42</v>
+      </c>
+      <c r="F738" s="9">
+        <v>0</v>
+      </c>
+      <c r="G738" s="9">
+        <v>0</v>
+      </c>
+      <c r="H738" s="9">
+        <v>4</v>
+      </c>
+      <c r="J738" s="9">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="739" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A739" s="6">
+        <v>1</v>
+      </c>
+      <c r="B739" s="6">
+        <v>738</v>
+      </c>
+      <c r="C739" s="7">
+        <v>46110</v>
+      </c>
+      <c r="D739" s="14">
+        <v>38.5</v>
+      </c>
+      <c r="E739" s="9">
+        <v>47</v>
+      </c>
+      <c r="F739" s="9">
+        <v>0</v>
+      </c>
+      <c r="G739" s="9">
+        <v>0</v>
+      </c>
+      <c r="H739" s="9">
+        <v>6</v>
+      </c>
+      <c r="J739" s="9">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="740" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A740" s="6">
+        <v>2</v>
+      </c>
+      <c r="B740" s="6">
+        <v>739</v>
+      </c>
+      <c r="C740" s="7">
+        <v>46111</v>
+      </c>
+      <c r="D740" s="14">
+        <v>15</v>
+      </c>
+      <c r="E740" s="9">
+        <v>45.5</v>
+      </c>
+      <c r="F740" s="9">
+        <v>0</v>
+      </c>
+      <c r="G740" s="9">
+        <v>0</v>
+      </c>
+      <c r="H740" s="9">
+        <v>13</v>
+      </c>
+      <c r="J740" s="9">
+        <v>3.0550000000000002</v>
+      </c>
+    </row>
+    <row r="741" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A741" s="6">
+        <v>3</v>
+      </c>
+      <c r="B741" s="6">
+        <v>740</v>
+      </c>
+      <c r="C741" s="7">
+        <v>46112</v>
+      </c>
+      <c r="D741" s="14">
+        <v>12</v>
+      </c>
+      <c r="E741" s="9">
+        <v>42</v>
+      </c>
+      <c r="F741" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="G741" s="9">
+        <v>0</v>
+      </c>
+      <c r="H741" s="9">
+        <v>9</v>
+      </c>
+      <c r="J741" s="9">
+        <v>2.3149999999999999</v>
+      </c>
+    </row>
+    <row r="742" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A742" s="6">
+        <v>4</v>
+      </c>
+      <c r="B742" s="6">
+        <v>741</v>
+      </c>
+      <c r="C742" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D742" s="14">
+        <v>16</v>
+      </c>
+      <c r="E742" s="9">
+        <v>49.5</v>
+      </c>
+      <c r="F742" s="9">
+        <v>0</v>
+      </c>
+      <c r="G742" s="9">
+        <v>0</v>
+      </c>
+      <c r="H742" s="9">
+        <v>14</v>
+      </c>
+      <c r="J742" s="9">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="743" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A743" s="6">
+        <v>5</v>
+      </c>
+      <c r="B743" s="6">
+        <v>742</v>
+      </c>
+      <c r="C743" s="7">
+        <v>46114</v>
+      </c>
+      <c r="D743" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="E743" s="9">
+        <v>51</v>
+      </c>
+      <c r="F743" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="G743" s="9">
+        <v>0</v>
+      </c>
+      <c r="H743" s="9">
+        <v>12</v>
+      </c>
+      <c r="J743" s="9">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="744" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A744" s="6">
+        <v>6</v>
+      </c>
+      <c r="B744" s="6">
+        <v>743</v>
+      </c>
+      <c r="C744" s="7">
+        <v>46115</v>
+      </c>
+      <c r="D744" s="14">
+        <v>14</v>
+      </c>
+      <c r="E744" s="9">
+        <v>50</v>
+      </c>
+      <c r="F744" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="G744" s="9">
+        <v>0</v>
+      </c>
+      <c r="H744" s="9">
+        <v>12</v>
+      </c>
+      <c r="I744" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J744" s="9">
+        <v>3.5049999999999999</v>
+      </c>
+    </row>
+    <row r="745" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A745" s="6">
+        <v>7</v>
+      </c>
+      <c r="B745" s="6">
+        <v>744</v>
+      </c>
+      <c r="C745" s="7">
+        <v>46116</v>
+      </c>
+      <c r="D745" s="14">
+        <v>17</v>
+      </c>
+      <c r="E745" s="9">
+        <v>49.5</v>
+      </c>
+      <c r="F745" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="G745" s="9">
+        <v>0</v>
+      </c>
+      <c r="H745" s="9">
+        <v>7</v>
+      </c>
+      <c r="J745" s="9">
+        <v>5.6750000000000007</v>
+      </c>
+    </row>
+    <row r="746" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A746" s="6">
+        <v>1</v>
+      </c>
+      <c r="B746" s="6">
+        <v>745</v>
+      </c>
+      <c r="C746" s="7">
+        <v>46117</v>
+      </c>
+      <c r="D746" s="14">
+        <v>78</v>
+      </c>
+      <c r="E746" s="9">
+        <v>50.5</v>
+      </c>
+      <c r="F746" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="G746" s="9">
+        <v>0</v>
+      </c>
+      <c r="H746" s="9">
+        <v>12</v>
+      </c>
+      <c r="I746" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="J746" s="9">
+        <v>18.61</v>
+      </c>
+    </row>
+    <row r="747" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A747" s="6">
+        <v>2</v>
+      </c>
+      <c r="B747" s="6">
+        <v>746</v>
+      </c>
+      <c r="C747" s="7">
+        <v>46118</v>
+      </c>
+      <c r="D747" s="14">
+        <v>13.5</v>
+      </c>
+      <c r="E747" s="9">
+        <v>51</v>
+      </c>
+      <c r="F747" s="9">
+        <v>0</v>
+      </c>
+      <c r="G747" s="9">
+        <v>0</v>
+      </c>
+      <c r="H747" s="9">
+        <v>10</v>
+      </c>
+      <c r="J747" s="9">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="748" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A748" s="6">
+        <v>3</v>
+      </c>
+      <c r="B748" s="6">
+        <v>747</v>
+      </c>
+      <c r="C748" s="7">
+        <v>46119</v>
+      </c>
+      <c r="D748" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="E748" s="9">
+        <v>52.5</v>
+      </c>
+      <c r="F748" s="9">
+        <v>0</v>
+      </c>
+      <c r="G748" s="9">
+        <v>0</v>
+      </c>
+      <c r="H748" s="9">
+        <v>10</v>
+      </c>
+      <c r="J748" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="749" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A749" s="6">
+        <v>4</v>
+      </c>
+      <c r="B749" s="6">
+        <v>748</v>
+      </c>
+      <c r="C749" s="7">
+        <v>46120</v>
+      </c>
+      <c r="D749" s="14">
+        <v>19</v>
+      </c>
+      <c r="E749" s="9">
+        <v>52</v>
+      </c>
+      <c r="F749" s="9">
+        <v>0.66</v>
+      </c>
+      <c r="G749" s="9">
+        <v>0</v>
+      </c>
+      <c r="H749" s="9">
+        <v>4</v>
+      </c>
+      <c r="J749" s="9">
+        <v>5.1400000000000006</v>
+      </c>
+    </row>
+    <row r="750" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A750" s="6">
+        <v>5</v>
+      </c>
+      <c r="B750" s="6">
+        <v>749</v>
+      </c>
+      <c r="C750" s="7">
+        <v>46121</v>
+      </c>
+      <c r="D750" s="14">
+        <v>15</v>
+      </c>
+      <c r="E750" s="9">
+        <v>52</v>
+      </c>
+      <c r="F750" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="G750" s="9">
+        <v>0</v>
+      </c>
+      <c r="H750" s="9">
+        <v>7</v>
+      </c>
+      <c r="J750" s="9">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="751" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A751" s="6">
+        <v>6</v>
+      </c>
+      <c r="B751" s="6">
+        <v>750</v>
+      </c>
+      <c r="C751" s="7">
+        <v>46122</v>
+      </c>
+      <c r="D751" s="14">
+        <v>15</v>
+      </c>
+      <c r="E751" s="9">
+        <v>51</v>
+      </c>
+      <c r="F751" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="G751" s="9">
+        <v>0</v>
+      </c>
+      <c r="H751" s="9">
+        <v>8</v>
+      </c>
+      <c r="J751" s="9">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="752" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A752" s="6">
+        <v>7</v>
+      </c>
+      <c r="B752" s="6">
+        <v>751</v>
+      </c>
+      <c r="C752" s="7">
+        <v>46123</v>
+      </c>
+      <c r="D752" s="14">
+        <v>25</v>
+      </c>
+      <c r="E752" s="9">
+        <v>47.5</v>
+      </c>
+      <c r="F752" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G752" s="9">
+        <v>0</v>
+      </c>
+      <c r="H752" s="9">
+        <v>15</v>
+      </c>
+      <c r="J752" s="9">
+        <v>7.0449999999999999</v>
+      </c>
+    </row>
+    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A753" s="6">
+        <v>1</v>
+      </c>
+      <c r="B753" s="6">
+        <v>752</v>
+      </c>
+      <c r="C753" s="7">
+        <v>46124</v>
+      </c>
+      <c r="D753" s="14">
+        <v>29.5</v>
+      </c>
+      <c r="E753" s="9">
+        <v>46.5</v>
+      </c>
+      <c r="F753" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="G753" s="9">
+        <v>0</v>
+      </c>
+      <c r="H753" s="9">
+        <v>10</v>
+      </c>
+      <c r="J753" s="9">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="754" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A754" s="6">
+        <v>2</v>
+      </c>
+      <c r="B754" s="6">
+        <v>753</v>
+      </c>
+      <c r="C754" s="7">
+        <v>46125</v>
+      </c>
+      <c r="D754" s="14">
+        <v>26</v>
+      </c>
+      <c r="E754" s="9">
+        <v>48.5</v>
+      </c>
+      <c r="F754" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="G754" s="9">
+        <v>0</v>
+      </c>
+      <c r="H754" s="9">
+        <v>4</v>
+      </c>
+      <c r="J754" s="9">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A755" s="6">
+        <v>3</v>
+      </c>
+      <c r="B755" s="6">
+        <v>754</v>
+      </c>
+      <c r="C755" s="7">
+        <v>46126</v>
+      </c>
+      <c r="D755" s="14">
+        <v>10.5</v>
+      </c>
+      <c r="E755" s="9">
+        <v>53.5</v>
+      </c>
+      <c r="F755" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="G755" s="9">
+        <v>0</v>
+      </c>
+      <c r="H755" s="9">
+        <v>9</v>
+      </c>
+      <c r="J755" s="9">
+        <v>2.4950000000000001</v>
+      </c>
+    </row>
+    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A756" s="6">
+        <v>4</v>
+      </c>
+      <c r="B756" s="6">
+        <v>755</v>
+      </c>
+      <c r="C756" s="7">
+        <v>46127</v>
+      </c>
+      <c r="D756" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="E756" s="9">
+        <v>52.5</v>
+      </c>
+      <c r="F756" s="9">
+        <v>0</v>
+      </c>
+      <c r="G756" s="9">
+        <v>0</v>
+      </c>
+      <c r="H756" s="9">
+        <v>9</v>
+      </c>
+      <c r="J756" s="9">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="757" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A757" s="6">
+        <v>5</v>
+      </c>
+      <c r="B757" s="6">
+        <v>756</v>
+      </c>
+      <c r="C757" s="7">
+        <v>46128</v>
+      </c>
+      <c r="D757" s="14">
+        <v>14</v>
+      </c>
+      <c r="E757" s="9">
+        <v>48.5</v>
+      </c>
+      <c r="F757" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="G757" s="9">
+        <v>0</v>
+      </c>
+      <c r="H757" s="9">
+        <v>8</v>
+      </c>
+      <c r="J757" s="9">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A758" s="6">
+        <v>6</v>
+      </c>
+      <c r="B758" s="6">
+        <v>757</v>
+      </c>
+      <c r="C758" s="7">
+        <v>46129</v>
+      </c>
+      <c r="D758" s="14">
+        <v>16.5</v>
+      </c>
+      <c r="E758" s="9">
+        <v>46</v>
+      </c>
+      <c r="F758" s="9">
+        <v>0</v>
+      </c>
+      <c r="G758" s="9">
+        <v>0</v>
+      </c>
+      <c r="H758" s="9">
+        <v>10</v>
+      </c>
+      <c r="J758" s="9">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A759" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19998,7 +21159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6638D5E3-C858-457D-8856-EE1DEA6B94D7}">
-  <dimension ref="A1:S257"/>
+  <dimension ref="A1:S298"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -20009,20 +21170,20 @@
         <v>43</v>
       </c>
       <c r="B1" s="7"/>
-      <c r="C1" s="40">
+      <c r="C1" s="43">
         <v>0.85</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="45"/>
       <c r="O1" s="22" t="s">
         <v>39</v>
       </c>
@@ -27794,7 +28955,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q195" t="e">
-        <f t="shared" ref="Q195:Q233" si="13">O195-A195</f>
+        <f t="shared" ref="Q195:Q258" si="13">O195-A195</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -30155,6 +31316,9 @@
       </c>
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A234" s="14">
+        <v>3</v>
+      </c>
       <c r="B234" s="24">
         <v>46071</v>
       </c>
@@ -30162,19 +31326,19 @@
         <v>21</v>
       </c>
       <c r="D234">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E234">
         <v>23</v>
       </c>
       <c r="F234">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G234">
         <v>26</v>
       </c>
       <c r="H234">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I234">
         <v>21</v>
@@ -30186,21 +31350,25 @@
         <v>13</v>
       </c>
       <c r="L234">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M234">
         <v>20</v>
       </c>
       <c r="N234">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O234" s="23">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P234" s="23">
         <f t="shared" si="15"/>
-        <v>4.6500000000000004</v>
+        <v>3.5</v>
+      </c>
+      <c r="Q234">
+        <f t="shared" si="13"/>
+        <v>15</v>
       </c>
       <c r="R234">
         <v>15</v>
@@ -30210,6 +31378,9 @@
       </c>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A235" s="14">
+        <v>10</v>
+      </c>
       <c r="B235" s="24">
         <v>46072</v>
       </c>
@@ -30217,7 +31388,7 @@
         <v>12</v>
       </c>
       <c r="D235">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E235">
         <v>19</v>
@@ -30229,25 +31400,25 @@
         <v>22</v>
       </c>
       <c r="H235">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I235">
         <v>17</v>
       </c>
       <c r="J235">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K235">
         <v>14</v>
       </c>
       <c r="L235">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M235">
         <v>15</v>
       </c>
       <c r="N235">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O235" s="23">
         <f t="shared" si="14"/>
@@ -30255,16 +31426,23 @@
       </c>
       <c r="P235" s="23">
         <f t="shared" si="15"/>
-        <v>2.46</v>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Q235">
+        <f t="shared" si="13"/>
+        <v>7</v>
       </c>
       <c r="R235">
         <v>20</v>
       </c>
       <c r="S235">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A236" s="14">
+        <v>18</v>
+      </c>
       <c r="B236" s="24">
         <v>46073</v>
       </c>
@@ -30272,54 +31450,61 @@
         <v>10</v>
       </c>
       <c r="D236">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E236">
         <v>20</v>
       </c>
       <c r="F236">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G236">
         <v>15</v>
       </c>
       <c r="H236">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I236">
         <v>12</v>
       </c>
       <c r="J236">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K236">
         <v>12</v>
       </c>
       <c r="L236">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M236">
         <v>14</v>
       </c>
       <c r="N236">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O236" s="23">
         <f t="shared" si="14"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P236" s="23">
         <f t="shared" si="15"/>
-        <v>3.23</v>
+        <v>4.95</v>
+      </c>
+      <c r="Q236">
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="R236">
         <v>20</v>
       </c>
       <c r="S236">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A237" s="14">
+        <v>19</v>
+      </c>
       <c r="B237" s="24">
         <v>46074</v>
       </c>
@@ -30327,54 +31512,61 @@
         <v>44</v>
       </c>
       <c r="D237">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E237">
         <v>27</v>
       </c>
       <c r="F237">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G237">
         <v>15</v>
       </c>
       <c r="H237">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I237">
         <v>21</v>
       </c>
       <c r="J237">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K237">
         <v>15</v>
       </c>
       <c r="L237">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M237">
         <v>47</v>
       </c>
       <c r="N237">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O237" s="23">
         <f t="shared" si="14"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P237" s="23">
         <f t="shared" si="15"/>
-        <v>9.1</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q237">
+        <f t="shared" si="13"/>
+        <v>6</v>
       </c>
       <c r="R237">
         <v>22</v>
       </c>
       <c r="S237">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A238" s="14">
+        <v>29</v>
+      </c>
       <c r="B238" s="24">
         <v>46075</v>
       </c>
@@ -30382,7 +31574,7 @@
         <v>37</v>
       </c>
       <c r="D238">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E238">
         <v>32</v>
@@ -30394,25 +31586,25 @@
         <v>37</v>
       </c>
       <c r="H238">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I238">
         <v>22</v>
       </c>
       <c r="J238">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K238">
         <v>16</v>
       </c>
       <c r="L238">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="M238">
         <v>22</v>
       </c>
       <c r="N238">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O238" s="23">
         <f t="shared" si="14"/>
@@ -30420,16 +31612,23 @@
       </c>
       <c r="P238" s="23">
         <f t="shared" si="15"/>
-        <v>11.87</v>
+        <v>7.55</v>
+      </c>
+      <c r="Q238">
+        <f t="shared" si="13"/>
+        <v>-2</v>
       </c>
       <c r="R238">
         <v>18</v>
       </c>
       <c r="S238">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A239" s="14">
+        <v>12</v>
+      </c>
       <c r="B239" s="24">
         <v>46076</v>
       </c>
@@ -30437,54 +31636,61 @@
         <v>10</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E239">
         <v>19</v>
       </c>
       <c r="F239">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G239">
         <v>15</v>
       </c>
       <c r="H239">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I239">
         <v>11</v>
       </c>
       <c r="J239">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K239">
         <v>18</v>
       </c>
       <c r="L239">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M239">
         <v>12</v>
       </c>
       <c r="N239">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O239" s="23">
         <f t="shared" si="14"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P239" s="23">
         <f t="shared" si="15"/>
-        <v>3.99</v>
+        <v>5.23</v>
+      </c>
+      <c r="Q239">
+        <f t="shared" si="13"/>
+        <v>5</v>
       </c>
       <c r="R239">
         <v>19</v>
       </c>
       <c r="S239">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A240" s="14">
+        <v>8</v>
+      </c>
       <c r="B240" s="24">
         <v>46077</v>
       </c>
@@ -30498,48 +31704,55 @@
         <v>23</v>
       </c>
       <c r="F240">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G240">
         <v>24</v>
       </c>
       <c r="H240">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I240">
         <v>21</v>
       </c>
       <c r="J240">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K240">
         <v>16</v>
       </c>
       <c r="L240">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M240">
         <v>16</v>
       </c>
       <c r="N240">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O240" s="23">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P240" s="23">
         <f t="shared" si="15"/>
-        <v>5.54</v>
+        <v>3.97</v>
+      </c>
+      <c r="Q240">
+        <f t="shared" si="13"/>
+        <v>8</v>
       </c>
       <c r="R240">
         <v>16</v>
       </c>
       <c r="S240">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A241" s="14">
         <v>16</v>
       </c>
-    </row>
-    <row r="241" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B241" s="24">
         <v>46078</v>
       </c>
@@ -30547,54 +31760,61 @@
         <v>16</v>
       </c>
       <c r="D241">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E241">
         <v>14</v>
       </c>
       <c r="F241">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G241">
         <v>15</v>
       </c>
       <c r="H241">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I241">
         <v>11</v>
       </c>
       <c r="J241">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K241">
         <v>11</v>
       </c>
       <c r="L241">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M241">
         <v>18</v>
       </c>
       <c r="N241">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O241" s="23">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P241" s="23">
         <f t="shared" si="15"/>
-        <v>2.4300000000000002</v>
+        <v>2.15</v>
+      </c>
+      <c r="Q241">
+        <f t="shared" si="13"/>
+        <v>-2</v>
       </c>
       <c r="R241">
         <v>12</v>
       </c>
       <c r="S241">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="242" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A242" s="14">
+        <v>15</v>
+      </c>
       <c r="B242" s="24">
         <v>46079</v>
       </c>
@@ -30602,7 +31822,7 @@
         <v>25</v>
       </c>
       <c r="D242">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E242">
         <v>20</v>
@@ -30614,42 +31834,49 @@
         <v>16</v>
       </c>
       <c r="H242">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I242">
         <v>20</v>
       </c>
       <c r="J242">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K242">
         <v>12</v>
       </c>
       <c r="L242">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M242">
         <v>25</v>
       </c>
       <c r="N242">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O242" s="23">
         <f t="shared" si="14"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P242" s="23">
         <f t="shared" si="15"/>
-        <v>3.78</v>
+        <v>3.65</v>
+      </c>
+      <c r="Q242">
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="R242">
         <v>15</v>
       </c>
       <c r="S242">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="243" spans="2:19" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A243" s="14">
+        <v>28</v>
+      </c>
       <c r="B243" s="24">
         <v>46080</v>
       </c>
@@ -30657,54 +31884,61 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E243">
         <v>25</v>
       </c>
       <c r="F243">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G243">
         <v>15</v>
       </c>
       <c r="H243">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I243">
         <v>17</v>
       </c>
       <c r="J243">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K243">
         <v>15</v>
       </c>
       <c r="L243">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M243">
         <v>22</v>
       </c>
       <c r="N243">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O243" s="23">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P243" s="23">
         <f t="shared" si="15"/>
-        <v>3.27</v>
+        <v>3.94</v>
+      </c>
+      <c r="Q243">
+        <f t="shared" si="13"/>
+        <v>-7</v>
       </c>
       <c r="R243">
         <v>23</v>
       </c>
       <c r="S243">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="244" spans="2:19" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A244" s="14">
+        <v>17</v>
+      </c>
       <c r="B244" s="24">
         <v>46081</v>
       </c>
@@ -30712,54 +31946,61 @@
         <v>17</v>
       </c>
       <c r="D244">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E244">
         <v>23</v>
       </c>
       <c r="F244">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G244">
         <v>19</v>
       </c>
       <c r="H244">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I244">
         <v>38</v>
       </c>
       <c r="J244">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K244">
         <v>15</v>
       </c>
       <c r="L244">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="M244">
         <v>18</v>
       </c>
       <c r="N244">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O244" s="23">
         <f t="shared" si="14"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P244" s="23">
         <f t="shared" si="15"/>
-        <v>6.19</v>
+        <v>6.65</v>
+      </c>
+      <c r="Q244">
+        <f t="shared" si="13"/>
+        <v>8</v>
       </c>
       <c r="R244">
         <v>35</v>
       </c>
       <c r="S244">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="245" spans="2:19" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A245" s="14">
+        <v>70</v>
+      </c>
       <c r="B245" s="24">
         <v>46082</v>
       </c>
@@ -30767,54 +32008,61 @@
         <v>19</v>
       </c>
       <c r="D245">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E245">
         <v>26</v>
       </c>
       <c r="F245">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G245">
         <v>29</v>
       </c>
       <c r="H245">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I245">
         <v>28</v>
       </c>
       <c r="J245">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K245">
         <v>17</v>
       </c>
       <c r="L245">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M245">
         <v>14</v>
       </c>
       <c r="N245">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O245" s="23">
         <f t="shared" si="14"/>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P245" s="23">
         <f t="shared" si="15"/>
-        <v>4.47</v>
+        <v>7.06</v>
+      </c>
+      <c r="Q245">
+        <f t="shared" si="13"/>
+        <v>-43</v>
       </c>
       <c r="R245">
         <v>26</v>
       </c>
       <c r="S245">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="246" spans="2:19" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A246" s="14">
+        <v>21</v>
+      </c>
       <c r="B246" s="24">
         <v>46083</v>
       </c>
@@ -30822,54 +32070,61 @@
         <v>30</v>
       </c>
       <c r="D246">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E246">
         <v>24</v>
       </c>
       <c r="F246">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G246">
         <v>16</v>
       </c>
       <c r="H246">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I246">
         <v>14</v>
       </c>
       <c r="J246">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K246">
         <v>23</v>
       </c>
       <c r="L246">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M246">
         <v>34</v>
       </c>
       <c r="N246">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O246" s="23">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P246" s="23">
         <f t="shared" si="15"/>
-        <v>6.36</v>
+        <v>6.03</v>
+      </c>
+      <c r="Q246">
+        <f t="shared" si="13"/>
+        <v>5</v>
       </c>
       <c r="R246">
         <v>30</v>
       </c>
       <c r="S246">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="247" spans="2:19" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A247" s="14">
+        <v>9</v>
+      </c>
       <c r="B247" s="24">
         <v>46084</v>
       </c>
@@ -30877,54 +32132,61 @@
         <v>15</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E247">
         <v>19</v>
       </c>
       <c r="F247">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G247">
         <v>15</v>
       </c>
       <c r="H247">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I247">
         <v>11</v>
       </c>
       <c r="J247">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K247">
         <v>13</v>
       </c>
       <c r="L247">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M247">
         <v>12</v>
       </c>
       <c r="N247">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O247" s="23">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P247" s="23">
         <f t="shared" si="15"/>
-        <v>2.92</v>
+        <v>3.83</v>
+      </c>
+      <c r="Q247">
+        <f t="shared" si="13"/>
+        <v>6</v>
       </c>
       <c r="R247">
         <v>14</v>
       </c>
       <c r="S247">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="248" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A248" s="14">
+        <v>18</v>
+      </c>
       <c r="B248" s="24">
         <v>46085</v>
       </c>
@@ -30932,31 +32194,31 @@
         <v>11</v>
       </c>
       <c r="D248">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E248">
         <v>23</v>
       </c>
       <c r="F248">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G248">
         <v>16</v>
       </c>
       <c r="H248">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I248">
         <v>12</v>
       </c>
       <c r="J248">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K248">
         <v>20</v>
       </c>
       <c r="L248">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M248">
         <v>10</v>
@@ -30966,20 +32228,27 @@
       </c>
       <c r="O248" s="23">
         <f t="shared" si="14"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P248" s="23">
         <f t="shared" si="15"/>
-        <v>4.08</v>
+        <v>3.71</v>
+      </c>
+      <c r="Q248">
+        <f t="shared" si="13"/>
+        <v>-3</v>
       </c>
       <c r="R248">
         <v>21</v>
       </c>
       <c r="S248">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="249" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A249" s="14">
+        <v>7</v>
+      </c>
       <c r="B249" s="24">
         <v>46086</v>
       </c>
@@ -30987,54 +32256,61 @@
         <v>19</v>
       </c>
       <c r="D249">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E249">
         <v>20</v>
       </c>
       <c r="F249">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G249">
         <v>19</v>
       </c>
       <c r="H249">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I249">
         <v>20</v>
       </c>
       <c r="J249">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K249">
         <v>14</v>
       </c>
       <c r="L249">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M249">
         <v>24</v>
       </c>
       <c r="N249">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O249" s="23">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P249" s="23">
         <f t="shared" si="15"/>
-        <v>2.4</v>
+        <v>2.82</v>
+      </c>
+      <c r="Q249">
+        <f t="shared" si="13"/>
+        <v>11</v>
       </c>
       <c r="R249">
         <v>22</v>
       </c>
       <c r="S249">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="250" spans="2:19" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A250" s="14">
+        <v>6</v>
+      </c>
       <c r="B250" s="24">
         <v>46087</v>
       </c>
@@ -31042,13 +32318,13 @@
         <v>10</v>
       </c>
       <c r="D250">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E250">
         <v>16</v>
       </c>
       <c r="F250">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G250">
         <v>15</v>
@@ -31060,7 +32336,7 @@
         <v>12</v>
       </c>
       <c r="J250">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K250">
         <v>20</v>
@@ -31072,15 +32348,19 @@
         <v>11</v>
       </c>
       <c r="N250">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O250" s="23">
         <f t="shared" si="14"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P250" s="23">
         <f t="shared" si="15"/>
-        <v>2.59</v>
+        <v>2.38</v>
+      </c>
+      <c r="Q250">
+        <f t="shared" si="13"/>
+        <v>8</v>
       </c>
       <c r="R250">
         <v>13</v>
@@ -31089,7 +32369,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A251" s="14">
+        <v>13</v>
+      </c>
       <c r="B251" s="24">
         <v>46088</v>
       </c>
@@ -31097,332 +32380,2467 @@
         <v>34</v>
       </c>
       <c r="D251">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E251">
         <v>26</v>
       </c>
       <c r="F251">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G251">
         <v>20</v>
       </c>
       <c r="H251">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I251">
         <v>17</v>
       </c>
       <c r="J251">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K251">
         <v>30</v>
       </c>
       <c r="L251">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M251">
         <v>33</v>
       </c>
       <c r="N251">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O251" s="23">
         <f t="shared" si="14"/>
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P251" s="23">
         <f t="shared" si="15"/>
-        <v>5.31</v>
+        <v>5.36</v>
+      </c>
+      <c r="Q251">
+        <f t="shared" si="13"/>
+        <v>12</v>
       </c>
       <c r="R251">
         <v>32</v>
       </c>
       <c r="S251">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A252" s="14">
+        <v>73</v>
+      </c>
+      <c r="B252" s="24">
+        <v>46089</v>
+      </c>
+      <c r="D252">
+        <v>23</v>
+      </c>
+      <c r="F252">
+        <v>30</v>
+      </c>
+      <c r="H252">
+        <v>46</v>
+      </c>
+      <c r="J252">
+        <v>26</v>
+      </c>
+      <c r="L252">
+        <v>19</v>
+      </c>
+      <c r="N252">
+        <v>24</v>
+      </c>
+      <c r="O252" s="23">
+        <f t="shared" ref="O252:O292" si="16">ROUND(AVERAGE(C252:N252,R252,S252),0)</f>
+        <v>29</v>
+      </c>
+      <c r="P252" s="23">
+        <f t="shared" ref="P252:P292" si="17">ROUND(_xlfn.STDEV.P(C252:N252,R252,S252),2)</f>
+        <v>8.24</v>
+      </c>
+      <c r="Q252">
+        <f t="shared" si="13"/>
+        <v>-44</v>
+      </c>
+      <c r="S252">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A253" s="14">
+        <v>12</v>
+      </c>
+      <c r="B253" s="24">
+        <v>46090</v>
+      </c>
+      <c r="D253">
+        <v>14</v>
+      </c>
+      <c r="F253">
+        <v>14</v>
+      </c>
+      <c r="H253">
+        <v>23</v>
+      </c>
+      <c r="J253">
+        <v>16</v>
+      </c>
+      <c r="L253">
+        <v>15</v>
+      </c>
+      <c r="N253">
+        <v>12</v>
+      </c>
+      <c r="O253" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P253" s="23">
+        <f t="shared" si="17"/>
+        <v>3.37</v>
+      </c>
+      <c r="Q253">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="S253">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A254" s="14">
+        <v>27</v>
+      </c>
+      <c r="B254" s="24">
+        <v>46091</v>
+      </c>
+      <c r="D254">
+        <v>17</v>
+      </c>
+      <c r="F254">
+        <v>13</v>
+      </c>
+      <c r="H254">
+        <v>15</v>
+      </c>
+      <c r="J254">
+        <v>15</v>
+      </c>
+      <c r="L254">
+        <v>13</v>
+      </c>
+      <c r="N254">
+        <v>14</v>
+      </c>
+      <c r="O254" s="23">
+        <f t="shared" si="16"/>
+        <v>14</v>
+      </c>
+      <c r="P254" s="23">
+        <f t="shared" si="17"/>
+        <v>1.29</v>
+      </c>
+      <c r="Q254">
+        <f t="shared" si="13"/>
+        <v>-13</v>
+      </c>
+      <c r="S254">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A255" s="14">
+        <v>24</v>
+      </c>
+      <c r="B255" s="24">
+        <v>46092</v>
+      </c>
+      <c r="D255">
+        <v>12</v>
+      </c>
+      <c r="F255">
+        <v>9</v>
+      </c>
+      <c r="H255">
+        <v>11</v>
+      </c>
+      <c r="J255">
+        <v>12</v>
+      </c>
+      <c r="L255">
+        <v>12</v>
+      </c>
+      <c r="N255">
+        <v>11</v>
+      </c>
+      <c r="O255" s="23">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="P255" s="23">
+        <f t="shared" si="17"/>
+        <v>0.99</v>
+      </c>
+      <c r="Q255">
+        <f t="shared" si="13"/>
+        <v>-13</v>
+      </c>
+      <c r="S255">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A256" s="14">
+        <v>4</v>
+      </c>
+      <c r="B256" s="24">
+        <v>46093</v>
+      </c>
+      <c r="D256">
+        <v>14</v>
+      </c>
+      <c r="F256">
+        <v>14</v>
+      </c>
+      <c r="H256">
+        <v>13</v>
+      </c>
+      <c r="J256">
+        <v>13</v>
+      </c>
+      <c r="L256">
+        <v>13</v>
+      </c>
+      <c r="N256">
+        <v>13</v>
+      </c>
+      <c r="O256" s="23">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P256" s="23">
+        <f t="shared" si="17"/>
+        <v>0.64</v>
+      </c>
+      <c r="Q256">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="S256">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A257" s="14">
+        <v>28</v>
+      </c>
+      <c r="B257" s="24">
+        <v>46094</v>
+      </c>
+      <c r="D257">
+        <v>22</v>
+      </c>
+      <c r="F257">
+        <v>20</v>
+      </c>
+      <c r="H257">
+        <v>22</v>
+      </c>
+      <c r="J257">
+        <v>23</v>
+      </c>
+      <c r="L257">
+        <v>24</v>
+      </c>
+      <c r="N257">
+        <v>25</v>
+      </c>
+      <c r="O257" s="23">
+        <f t="shared" si="16"/>
+        <v>23</v>
+      </c>
+      <c r="P257" s="23">
+        <f t="shared" si="17"/>
+        <v>1.55</v>
+      </c>
+      <c r="Q257">
+        <f t="shared" si="13"/>
+        <v>-5</v>
+      </c>
+      <c r="S257">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A258" s="14">
+        <v>17</v>
+      </c>
+      <c r="B258" s="24">
+        <v>46095</v>
+      </c>
+      <c r="D258">
+        <v>23</v>
+      </c>
+      <c r="F258">
+        <v>18</v>
+      </c>
+      <c r="H258">
+        <v>17</v>
+      </c>
+      <c r="J258">
+        <v>21</v>
+      </c>
+      <c r="L258">
+        <v>24</v>
+      </c>
+      <c r="N258">
+        <v>21</v>
+      </c>
+      <c r="O258" s="23">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="P258" s="23">
+        <f t="shared" si="17"/>
+        <v>2.31</v>
+      </c>
+      <c r="Q258">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="S258">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A259" s="14">
+        <v>66</v>
+      </c>
+      <c r="B259" s="24">
+        <v>46096</v>
+      </c>
+      <c r="D259">
+        <v>23</v>
+      </c>
+      <c r="F259">
+        <v>26</v>
+      </c>
+      <c r="H259">
+        <v>34</v>
+      </c>
+      <c r="J259">
+        <v>24</v>
+      </c>
+      <c r="L259">
+        <v>17</v>
+      </c>
+      <c r="N259">
+        <v>25</v>
+      </c>
+      <c r="O259" s="23">
+        <f t="shared" si="16"/>
+        <v>25</v>
+      </c>
+      <c r="P259" s="23">
+        <f t="shared" si="17"/>
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="Q259">
+        <f t="shared" ref="Q259:Q260" si="18">O259-A259</f>
+        <v>-41</v>
+      </c>
+      <c r="S259">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A260" s="14">
+        <v>7</v>
+      </c>
+      <c r="B260" s="24">
+        <v>46097</v>
+      </c>
+      <c r="D260">
+        <v>13</v>
+      </c>
+      <c r="F260">
+        <v>14</v>
+      </c>
+      <c r="H260">
+        <v>23</v>
+      </c>
+      <c r="J260">
+        <v>15</v>
+      </c>
+      <c r="L260">
+        <v>13</v>
+      </c>
+      <c r="N260">
+        <v>13</v>
+      </c>
+      <c r="O260" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P260" s="23">
+        <f t="shared" si="17"/>
+        <v>3.34</v>
+      </c>
+      <c r="Q260">
+        <f t="shared" si="18"/>
+        <v>8</v>
+      </c>
+      <c r="S260">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A261" s="26"/>
+      <c r="B261" s="27">
+        <v>46098</v>
+      </c>
+      <c r="C261" s="26">
+        <v>11</v>
+      </c>
+      <c r="D261" s="26">
+        <v>15</v>
+      </c>
+      <c r="E261" s="26">
+        <v>14</v>
+      </c>
+      <c r="F261" s="26">
+        <v>13</v>
+      </c>
+      <c r="G261" s="26">
+        <v>22</v>
+      </c>
+      <c r="H261" s="26">
+        <v>15</v>
+      </c>
+      <c r="I261" s="26">
+        <v>13</v>
+      </c>
+      <c r="J261" s="26">
+        <v>13</v>
+      </c>
+      <c r="K261" s="26">
+        <v>12</v>
+      </c>
+      <c r="L261" s="26">
+        <v>14</v>
+      </c>
+      <c r="M261" s="26">
+        <v>15</v>
+      </c>
+      <c r="N261" s="26">
+        <v>12</v>
+      </c>
+      <c r="O261" s="28">
+        <f t="shared" si="16"/>
+        <v>14</v>
+      </c>
+      <c r="P261" s="28">
+        <f t="shared" si="17"/>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="Q261" s="26"/>
+      <c r="R261" s="26">
+        <v>14</v>
+      </c>
+      <c r="S261" s="26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B262" s="24">
+        <v>46099</v>
+      </c>
+      <c r="C262">
+        <v>19</v>
+      </c>
+      <c r="D262">
+        <v>14</v>
+      </c>
+      <c r="E262">
+        <v>13</v>
+      </c>
+      <c r="F262">
+        <v>14</v>
+      </c>
+      <c r="G262">
+        <v>17</v>
+      </c>
+      <c r="H262">
+        <v>13</v>
+      </c>
+      <c r="I262">
+        <v>14</v>
+      </c>
+      <c r="J262">
+        <v>14</v>
+      </c>
+      <c r="K262">
+        <v>21</v>
+      </c>
+      <c r="L262">
+        <v>14</v>
+      </c>
+      <c r="M262">
+        <v>16</v>
+      </c>
+      <c r="N262">
+        <v>15</v>
+      </c>
+      <c r="O262" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P262" s="23">
+        <f t="shared" si="17"/>
+        <v>2.34</v>
+      </c>
+      <c r="R262">
+        <v>13</v>
+      </c>
+      <c r="S262">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B263" s="24">
+        <v>46100</v>
+      </c>
+      <c r="C263">
+        <v>12</v>
+      </c>
+      <c r="D263">
+        <v>10</v>
+      </c>
+      <c r="E263">
+        <v>13</v>
+      </c>
+      <c r="F263">
+        <v>12</v>
+      </c>
+      <c r="G263">
+        <v>13</v>
+      </c>
+      <c r="H263">
+        <v>11</v>
+      </c>
+      <c r="I263">
+        <v>14</v>
+      </c>
+      <c r="J263">
+        <v>12</v>
+      </c>
+      <c r="K263">
+        <v>14</v>
+      </c>
+      <c r="L263">
+        <v>14</v>
+      </c>
+      <c r="M263">
+        <v>16</v>
+      </c>
+      <c r="N263">
+        <v>12</v>
+      </c>
+      <c r="O263" s="23">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P263" s="23">
+        <f t="shared" si="17"/>
+        <v>1.44</v>
+      </c>
+      <c r="R263">
+        <v>12</v>
+      </c>
+      <c r="S263">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B264" s="24">
+        <v>46101</v>
+      </c>
+      <c r="C264">
+        <v>21</v>
+      </c>
+      <c r="D264">
+        <v>17</v>
+      </c>
+      <c r="E264">
+        <v>30</v>
+      </c>
+      <c r="F264">
+        <v>19</v>
+      </c>
+      <c r="G264">
+        <v>16</v>
+      </c>
+      <c r="H264">
+        <v>18</v>
+      </c>
+      <c r="I264">
+        <v>25</v>
+      </c>
+      <c r="J264">
+        <v>18</v>
+      </c>
+      <c r="K264">
+        <v>30</v>
+      </c>
+      <c r="L264">
+        <v>18</v>
+      </c>
+      <c r="M264">
+        <v>19</v>
+      </c>
+      <c r="N264">
+        <v>17</v>
+      </c>
+      <c r="O264" s="23">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="P264" s="23">
+        <f t="shared" si="17"/>
+        <v>7.48</v>
+      </c>
+      <c r="R264">
+        <v>44</v>
+      </c>
+      <c r="S264">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B265" s="24">
+        <v>46102</v>
+      </c>
+      <c r="C265">
+        <v>41</v>
+      </c>
+      <c r="D265">
+        <v>28</v>
+      </c>
+      <c r="E265">
+        <v>57</v>
+      </c>
+      <c r="F265">
+        <v>25</v>
+      </c>
+      <c r="G265">
+        <v>28</v>
+      </c>
+      <c r="H265">
+        <v>26</v>
+      </c>
+      <c r="I265">
+        <v>47</v>
+      </c>
+      <c r="J265">
+        <v>26</v>
+      </c>
+      <c r="K265">
+        <v>62</v>
+      </c>
+      <c r="L265">
+        <v>25</v>
+      </c>
+      <c r="M265">
+        <v>32</v>
+      </c>
+      <c r="N265">
+        <v>25</v>
+      </c>
+      <c r="O265" s="23">
+        <f t="shared" si="16"/>
+        <v>38</v>
+      </c>
+      <c r="P265" s="23">
+        <f t="shared" si="17"/>
+        <v>15.66</v>
+      </c>
+      <c r="R265">
+        <v>74</v>
+      </c>
+      <c r="S265">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B266" s="24">
+        <v>46103</v>
+      </c>
+      <c r="C266">
+        <v>35</v>
+      </c>
+      <c r="D266">
+        <v>25</v>
+      </c>
+      <c r="E266">
+        <v>36</v>
+      </c>
+      <c r="F266">
+        <v>23</v>
+      </c>
+      <c r="G266">
+        <v>29</v>
+      </c>
+      <c r="H266">
+        <v>26</v>
+      </c>
+      <c r="I266">
+        <v>56</v>
+      </c>
+      <c r="J266">
+        <v>26</v>
+      </c>
+      <c r="K266">
+        <v>27</v>
+      </c>
+      <c r="L266">
+        <v>24</v>
+      </c>
+      <c r="M266">
+        <v>36</v>
+      </c>
+      <c r="N266">
+        <v>25</v>
+      </c>
+      <c r="O266" s="23">
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="252" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B252" s="31" t="s">
+      <c r="P266" s="23">
+        <f t="shared" si="17"/>
+        <v>8.39</v>
+      </c>
+      <c r="R266">
+        <v>35</v>
+      </c>
+      <c r="S266">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B267" s="24">
+        <v>46104</v>
+      </c>
+      <c r="C267">
+        <v>17</v>
+      </c>
+      <c r="D267">
+        <v>19</v>
+      </c>
+      <c r="E267">
+        <v>29</v>
+      </c>
+      <c r="F267">
+        <v>23</v>
+      </c>
+      <c r="G267">
+        <v>34</v>
+      </c>
+      <c r="H267">
+        <v>25</v>
+      </c>
+      <c r="I267">
+        <v>24</v>
+      </c>
+      <c r="J267">
+        <v>20</v>
+      </c>
+      <c r="K267">
+        <v>12</v>
+      </c>
+      <c r="L267">
+        <v>20</v>
+      </c>
+      <c r="M267">
+        <v>23</v>
+      </c>
+      <c r="N267">
+        <v>24</v>
+      </c>
+      <c r="O267" s="23">
+        <f t="shared" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="P267" s="23">
+        <f t="shared" si="17"/>
+        <v>5.83</v>
+      </c>
+      <c r="R267">
+        <v>34</v>
+      </c>
+      <c r="S267">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B268" s="24">
+        <v>46105</v>
+      </c>
+      <c r="C268">
+        <v>16</v>
+      </c>
+      <c r="D268">
+        <v>16</v>
+      </c>
+      <c r="E268">
+        <v>17</v>
+      </c>
+      <c r="F268">
+        <v>19</v>
+      </c>
+      <c r="G268">
+        <v>26</v>
+      </c>
+      <c r="H268">
+        <v>23</v>
+      </c>
+      <c r="I268">
+        <v>17</v>
+      </c>
+      <c r="J268">
+        <v>18</v>
+      </c>
+      <c r="K268">
+        <v>16</v>
+      </c>
+      <c r="L268">
+        <v>15</v>
+      </c>
+      <c r="M268">
+        <v>16</v>
+      </c>
+      <c r="N268">
+        <v>17</v>
+      </c>
+      <c r="O268" s="23">
+        <f t="shared" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="P268" s="23">
+        <f t="shared" si="17"/>
+        <v>3.56</v>
+      </c>
+      <c r="R268">
+        <v>26</v>
+      </c>
+      <c r="S268">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B269" s="24">
+        <v>46106</v>
+      </c>
+      <c r="C269">
+        <v>20</v>
+      </c>
+      <c r="D269">
+        <v>20</v>
+      </c>
+      <c r="E269">
+        <v>14</v>
+      </c>
+      <c r="F269">
+        <v>18</v>
+      </c>
+      <c r="G269">
+        <v>19</v>
+      </c>
+      <c r="H269">
+        <v>22</v>
+      </c>
+      <c r="I269">
+        <v>29</v>
+      </c>
+      <c r="J269">
+        <v>19</v>
+      </c>
+      <c r="K269">
+        <v>20</v>
+      </c>
+      <c r="L269">
+        <v>18</v>
+      </c>
+      <c r="M269">
+        <v>22</v>
+      </c>
+      <c r="N269">
+        <v>21</v>
+      </c>
+      <c r="O269" s="23">
+        <f t="shared" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="P269" s="23">
+        <f t="shared" si="17"/>
+        <v>3.13</v>
+      </c>
+      <c r="R269">
+        <v>21</v>
+      </c>
+      <c r="S269">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B270" s="24">
+        <v>46107</v>
+      </c>
+      <c r="C270">
+        <v>28</v>
+      </c>
+      <c r="D270">
+        <v>17</v>
+      </c>
+      <c r="E270">
+        <v>18</v>
+      </c>
+      <c r="F270">
+        <v>16</v>
+      </c>
+      <c r="G270">
+        <v>21</v>
+      </c>
+      <c r="H270">
+        <v>20</v>
+      </c>
+      <c r="I270">
+        <v>28</v>
+      </c>
+      <c r="J270">
+        <v>19</v>
+      </c>
+      <c r="K270">
+        <v>28</v>
+      </c>
+      <c r="L270">
+        <v>17</v>
+      </c>
+      <c r="M270">
+        <v>25</v>
+      </c>
+      <c r="N270">
+        <v>21</v>
+      </c>
+      <c r="O270" s="23">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="P270" s="23">
+        <f t="shared" si="17"/>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="R270">
+        <v>24</v>
+      </c>
+      <c r="S270">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B271" s="24">
+        <v>46108</v>
+      </c>
+      <c r="C271">
+        <v>26</v>
+      </c>
+      <c r="D271">
+        <v>18</v>
+      </c>
+      <c r="E271">
+        <v>22</v>
+      </c>
+      <c r="F271">
+        <v>22</v>
+      </c>
+      <c r="G271">
+        <v>18</v>
+      </c>
+      <c r="H271">
+        <v>18</v>
+      </c>
+      <c r="I271">
+        <v>25</v>
+      </c>
+      <c r="J271">
+        <v>21</v>
+      </c>
+      <c r="K271">
+        <v>23</v>
+      </c>
+      <c r="L271">
+        <v>24</v>
+      </c>
+      <c r="M271">
+        <v>23</v>
+      </c>
+      <c r="N271">
+        <v>20</v>
+      </c>
+      <c r="O271" s="23">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="P271" s="23">
+        <f t="shared" si="17"/>
+        <v>3.47</v>
+      </c>
+      <c r="R271">
+        <v>31</v>
+      </c>
+      <c r="S271">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B272" s="24">
+        <v>46109</v>
+      </c>
+      <c r="C272">
+        <v>15</v>
+      </c>
+      <c r="D272">
+        <v>23</v>
+      </c>
+      <c r="E272">
+        <v>37</v>
+      </c>
+      <c r="F272">
+        <v>26</v>
+      </c>
+      <c r="G272">
+        <v>19</v>
+      </c>
+      <c r="H272">
+        <v>30</v>
+      </c>
+      <c r="I272">
+        <v>24</v>
+      </c>
+      <c r="J272">
+        <v>20</v>
+      </c>
+      <c r="K272">
+        <v>12</v>
+      </c>
+      <c r="L272">
+        <v>24</v>
+      </c>
+      <c r="M272">
+        <v>17</v>
+      </c>
+      <c r="N272">
+        <v>19</v>
+      </c>
+      <c r="O272" s="23">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="P272" s="23">
+        <f t="shared" si="17"/>
+        <v>6.11</v>
+      </c>
+      <c r="R272">
+        <v>26</v>
+      </c>
+      <c r="S272">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B273" s="24">
+        <v>46110</v>
+      </c>
+      <c r="C273">
+        <v>44</v>
+      </c>
+      <c r="D273">
+        <v>44</v>
+      </c>
+      <c r="E273">
+        <v>32</v>
+      </c>
+      <c r="F273">
+        <v>40</v>
+      </c>
+      <c r="G273">
+        <v>49</v>
+      </c>
+      <c r="H273">
+        <v>38</v>
+      </c>
+      <c r="I273">
+        <v>35</v>
+      </c>
+      <c r="J273">
+        <v>40</v>
+      </c>
+      <c r="K273">
+        <v>37</v>
+      </c>
+      <c r="L273">
+        <v>40</v>
+      </c>
+      <c r="M273">
         <v>41</v>
       </c>
-      <c r="C252" s="32">
-        <v>34.42</v>
-      </c>
-      <c r="D252" s="32">
-        <v>30.07</v>
-      </c>
-      <c r="E252" s="32">
-        <v>27.96</v>
-      </c>
-      <c r="F252" s="32">
-        <v>27.09</v>
-      </c>
-      <c r="G252" s="32">
-        <v>29.35</v>
-      </c>
-      <c r="H252" s="32">
+      <c r="N273">
+        <v>41</v>
+      </c>
+      <c r="O273" s="23">
+        <f t="shared" si="16"/>
+        <v>41</v>
+      </c>
+      <c r="P273" s="23">
+        <f t="shared" si="17"/>
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="R273">
+        <v>46</v>
+      </c>
+      <c r="S273">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="274" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B274" s="24">
+        <v>46111</v>
+      </c>
+      <c r="C274">
+        <v>12</v>
+      </c>
+      <c r="D274">
+        <v>15</v>
+      </c>
+      <c r="E274">
+        <v>24</v>
+      </c>
+      <c r="F274">
+        <v>13</v>
+      </c>
+      <c r="G274">
         <v>20</v>
       </c>
-      <c r="I252" s="32">
-        <v>28.58</v>
-      </c>
-      <c r="J252" s="32">
-        <v>28.01</v>
-      </c>
-      <c r="K252" s="32">
-        <v>31.54</v>
-      </c>
-      <c r="L252" s="32">
+      <c r="H274">
+        <v>15</v>
+      </c>
+      <c r="I274">
+        <v>14</v>
+      </c>
+      <c r="J274">
+        <v>14</v>
+      </c>
+      <c r="K274">
+        <v>12</v>
+      </c>
+      <c r="L274">
+        <v>13</v>
+      </c>
+      <c r="M274">
+        <v>16</v>
+      </c>
+      <c r="N274">
+        <v>16</v>
+      </c>
+      <c r="O274" s="23">
+        <f t="shared" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="P274" s="23">
+        <f t="shared" si="17"/>
+        <v>3.24</v>
+      </c>
+      <c r="R274">
+        <v>19</v>
+      </c>
+      <c r="S274">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="275" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B275" s="24">
+        <v>46112</v>
+      </c>
+      <c r="C275">
+        <v>11</v>
+      </c>
+      <c r="D275">
+        <v>10</v>
+      </c>
+      <c r="E275">
+        <v>14</v>
+      </c>
+      <c r="F275">
+        <v>11</v>
+      </c>
+      <c r="G275">
+        <v>20</v>
+      </c>
+      <c r="H275">
+        <v>15</v>
+      </c>
+      <c r="I275">
+        <v>10</v>
+      </c>
+      <c r="J275">
+        <v>11</v>
+      </c>
+      <c r="K275">
+        <v>12</v>
+      </c>
+      <c r="L275">
+        <v>12</v>
+      </c>
+      <c r="M275">
+        <v>15</v>
+      </c>
+      <c r="N275">
+        <v>11</v>
+      </c>
+      <c r="O275" s="23">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P275" s="23">
+        <f t="shared" si="17"/>
+        <v>2.58</v>
+      </c>
+      <c r="R275">
+        <v>12</v>
+      </c>
+      <c r="S275">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="276" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B276" s="24">
+        <v>46113</v>
+      </c>
+      <c r="C276">
+        <v>25</v>
+      </c>
+      <c r="D276">
+        <v>15</v>
+      </c>
+      <c r="E276">
+        <v>21</v>
+      </c>
+      <c r="F276">
+        <v>14</v>
+      </c>
+      <c r="G276">
+        <v>14</v>
+      </c>
+      <c r="H276">
+        <v>12</v>
+      </c>
+      <c r="I276">
+        <v>14</v>
+      </c>
+      <c r="J276">
+        <v>14</v>
+      </c>
+      <c r="K276">
+        <v>24</v>
+      </c>
+      <c r="L276">
+        <v>15</v>
+      </c>
+      <c r="M276">
+        <v>17</v>
+      </c>
+      <c r="N276">
+        <v>18</v>
+      </c>
+      <c r="O276" s="23">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="P276" s="23">
+        <f t="shared" si="17"/>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="R276">
+        <v>21</v>
+      </c>
+      <c r="S276">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B277" s="24">
+        <v>46114</v>
+      </c>
+      <c r="C277">
+        <v>11</v>
+      </c>
+      <c r="D277">
+        <v>10</v>
+      </c>
+      <c r="E277">
+        <v>14</v>
+      </c>
+      <c r="F277">
+        <v>11</v>
+      </c>
+      <c r="G277">
+        <v>11</v>
+      </c>
+      <c r="H277">
+        <v>16</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <v>11</v>
+      </c>
+      <c r="K277">
+        <v>15</v>
+      </c>
+      <c r="L277">
+        <v>12</v>
+      </c>
+      <c r="M277">
+        <v>10</v>
+      </c>
+      <c r="N277">
+        <v>11</v>
+      </c>
+      <c r="O277" s="23">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="P277" s="23">
+        <f t="shared" si="17"/>
+        <v>3.33</v>
+      </c>
+      <c r="R277">
+        <v>12</v>
+      </c>
+      <c r="S277">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B278" s="24">
+        <v>46115</v>
+      </c>
+      <c r="C278">
+        <v>13</v>
+      </c>
+      <c r="D278">
+        <v>13</v>
+      </c>
+      <c r="E278">
+        <v>17</v>
+      </c>
+      <c r="F278">
+        <v>16</v>
+      </c>
+      <c r="G278">
+        <v>14</v>
+      </c>
+      <c r="H278">
+        <v>12</v>
+      </c>
+      <c r="I278">
+        <v>11</v>
+      </c>
+      <c r="J278">
+        <v>16</v>
+      </c>
+      <c r="K278">
+        <v>12</v>
+      </c>
+      <c r="L278">
+        <v>14</v>
+      </c>
+      <c r="M278">
+        <v>18</v>
+      </c>
+      <c r="N278">
+        <v>17</v>
+      </c>
+      <c r="O278" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P278" s="23">
+        <f t="shared" si="17"/>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="R278">
+        <v>20</v>
+      </c>
+      <c r="S278">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="279" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B279" s="24">
+        <v>46116</v>
+      </c>
+      <c r="C279">
+        <v>16</v>
+      </c>
+      <c r="D279">
+        <v>11</v>
+      </c>
+      <c r="E279">
+        <v>22</v>
+      </c>
+      <c r="F279">
+        <v>19</v>
+      </c>
+      <c r="G279">
+        <v>18</v>
+      </c>
+      <c r="H279">
+        <v>26</v>
+      </c>
+      <c r="I279">
+        <v>18</v>
+      </c>
+      <c r="J279">
+        <v>16</v>
+      </c>
+      <c r="K279">
+        <v>13</v>
+      </c>
+      <c r="L279">
+        <v>16</v>
+      </c>
+      <c r="M279">
+        <v>18</v>
+      </c>
+      <c r="N279">
+        <v>13</v>
+      </c>
+      <c r="O279" s="23">
+        <f t="shared" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="P279" s="23">
+        <f t="shared" si="17"/>
+        <v>5.48</v>
+      </c>
+      <c r="R279">
+        <v>33</v>
+      </c>
+      <c r="S279">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="280" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B280" s="24">
+        <v>46117</v>
+      </c>
+      <c r="C280">
+        <v>100</v>
+      </c>
+      <c r="D280">
+        <v>92</v>
+      </c>
+      <c r="E280">
+        <v>67</v>
+      </c>
+      <c r="F280">
+        <v>65</v>
+      </c>
+      <c r="G280">
+        <v>64</v>
+      </c>
+      <c r="H280">
+        <v>58</v>
+      </c>
+      <c r="I280">
+        <v>89</v>
+      </c>
+      <c r="J280">
+        <v>81</v>
+      </c>
+      <c r="K280">
+        <v>108</v>
+      </c>
+      <c r="L280">
+        <v>94</v>
+      </c>
+      <c r="M280">
+        <v>91</v>
+      </c>
+      <c r="N280">
+        <v>89</v>
+      </c>
+      <c r="O280" s="23">
+        <f t="shared" si="16"/>
+        <v>83</v>
+      </c>
+      <c r="P280" s="23">
+        <f t="shared" si="17"/>
+        <v>14.23</v>
+      </c>
+      <c r="R280">
+        <v>87</v>
+      </c>
+      <c r="S280">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="281" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B281" s="24">
+        <v>46118</v>
+      </c>
+      <c r="C281">
+        <v>12</v>
+      </c>
+      <c r="D281">
+        <v>13</v>
+      </c>
+      <c r="E281">
+        <v>15</v>
+      </c>
+      <c r="F281">
+        <v>13</v>
+      </c>
+      <c r="G281">
+        <v>20</v>
+      </c>
+      <c r="H281">
+        <v>18</v>
+      </c>
+      <c r="I281">
+        <v>14</v>
+      </c>
+      <c r="J281">
+        <v>14</v>
+      </c>
+      <c r="K281">
+        <v>14</v>
+      </c>
+      <c r="L281">
+        <v>15</v>
+      </c>
+      <c r="M281">
+        <v>15</v>
+      </c>
+      <c r="N281">
+        <v>14</v>
+      </c>
+      <c r="O281" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P281" s="23">
+        <f t="shared" si="17"/>
+        <v>1.99</v>
+      </c>
+      <c r="R281">
+        <v>16</v>
+      </c>
+      <c r="S281">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B282" s="24">
+        <v>46119</v>
+      </c>
+      <c r="C282">
+        <v>14</v>
+      </c>
+      <c r="D282">
+        <v>15</v>
+      </c>
+      <c r="E282">
+        <v>13</v>
+      </c>
+      <c r="F282">
+        <v>12</v>
+      </c>
+      <c r="G282">
+        <v>15</v>
+      </c>
+      <c r="H282">
+        <v>15</v>
+      </c>
+      <c r="I282">
+        <v>10</v>
+      </c>
+      <c r="J282">
+        <v>14</v>
+      </c>
+      <c r="K282">
+        <v>12</v>
+      </c>
+      <c r="L282">
+        <v>14</v>
+      </c>
+      <c r="M282">
+        <v>14</v>
+      </c>
+      <c r="N282">
+        <v>12</v>
+      </c>
+      <c r="O282" s="23">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="P282" s="23">
+        <f t="shared" si="17"/>
+        <v>1.4</v>
+      </c>
+      <c r="R282">
+        <v>14</v>
+      </c>
+      <c r="S282">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="283" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B283" s="24">
+        <v>46120</v>
+      </c>
+      <c r="C283">
+        <v>19</v>
+      </c>
+      <c r="D283">
+        <v>21</v>
+      </c>
+      <c r="E283">
+        <v>21</v>
+      </c>
+      <c r="F283">
+        <v>21</v>
+      </c>
+      <c r="G283">
+        <v>34</v>
+      </c>
+      <c r="H283">
+        <v>25</v>
+      </c>
+      <c r="I283">
+        <v>22</v>
+      </c>
+      <c r="J283">
+        <v>17</v>
+      </c>
+      <c r="K283">
+        <v>12</v>
+      </c>
+      <c r="L283">
+        <v>13</v>
+      </c>
+      <c r="M283">
+        <v>20</v>
+      </c>
+      <c r="N283">
+        <v>20</v>
+      </c>
+      <c r="O283" s="23">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="P283" s="23">
+        <f t="shared" si="17"/>
+        <v>5.25</v>
+      </c>
+      <c r="R283">
+        <v>26</v>
+      </c>
+      <c r="S283">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="284" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B284" s="24">
+        <v>46121</v>
+      </c>
+      <c r="C284">
+        <v>12</v>
+      </c>
+      <c r="D284">
+        <v>14</v>
+      </c>
+      <c r="E284">
+        <v>16</v>
+      </c>
+      <c r="F284">
+        <v>16</v>
+      </c>
+      <c r="G284">
+        <v>14</v>
+      </c>
+      <c r="H284">
+        <v>21</v>
+      </c>
+      <c r="I284">
+        <v>17</v>
+      </c>
+      <c r="J284">
+        <v>15</v>
+      </c>
+      <c r="K284">
+        <v>12</v>
+      </c>
+      <c r="L284">
+        <v>14</v>
+      </c>
+      <c r="M284">
+        <v>16</v>
+      </c>
+      <c r="N284">
+        <v>14</v>
+      </c>
+      <c r="O284" s="23">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="P284" s="23">
+        <f t="shared" si="17"/>
+        <v>2.5</v>
+      </c>
+      <c r="R284">
+        <v>20</v>
+      </c>
+      <c r="S284">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B285" s="24">
+        <v>46122</v>
+      </c>
+      <c r="C285">
+        <v>16</v>
+      </c>
+      <c r="D285">
+        <v>16</v>
+      </c>
+      <c r="E285">
+        <v>14</v>
+      </c>
+      <c r="F285">
+        <v>17</v>
+      </c>
+      <c r="G285">
+        <v>18</v>
+      </c>
+      <c r="H285">
+        <v>24</v>
+      </c>
+      <c r="I285">
+        <v>13</v>
+      </c>
+      <c r="J285">
+        <v>15</v>
+      </c>
+      <c r="K285">
+        <v>19</v>
+      </c>
+      <c r="L285">
+        <v>14</v>
+      </c>
+      <c r="M285">
+        <v>15</v>
+      </c>
+      <c r="N285">
+        <v>13</v>
+      </c>
+      <c r="O285" s="23">
+        <f t="shared" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="P285" s="23">
+        <f t="shared" si="17"/>
+        <v>2.81</v>
+      </c>
+      <c r="R285">
+        <v>15</v>
+      </c>
+      <c r="S285">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="286" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B286" s="24">
+        <v>46123</v>
+      </c>
+      <c r="C286">
+        <v>28</v>
+      </c>
+      <c r="D286">
+        <v>34</v>
+      </c>
+      <c r="E286">
+        <v>20</v>
+      </c>
+      <c r="F286">
+        <v>24</v>
+      </c>
+      <c r="G286">
+        <v>17</v>
+      </c>
+      <c r="H286">
+        <v>18</v>
+      </c>
+      <c r="I286">
+        <v>18</v>
+      </c>
+      <c r="J286">
+        <v>38</v>
+      </c>
+      <c r="K286">
+        <v>22</v>
+      </c>
+      <c r="L286">
+        <v>27</v>
+      </c>
+      <c r="M286">
+        <v>24</v>
+      </c>
+      <c r="N286">
+        <v>32</v>
+      </c>
+      <c r="O286" s="23">
+        <f t="shared" si="16"/>
+        <v>26</v>
+      </c>
+      <c r="P286" s="23">
+        <f t="shared" si="17"/>
+        <v>6.09</v>
+      </c>
+      <c r="R286">
+        <v>27</v>
+      </c>
+      <c r="S286">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="287" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B287" s="24">
+        <v>46124</v>
+      </c>
+      <c r="C287">
+        <v>31</v>
+      </c>
+      <c r="D287">
+        <v>34</v>
+      </c>
+      <c r="E287">
+        <v>26</v>
+      </c>
+      <c r="F287">
+        <v>32</v>
+      </c>
+      <c r="G287">
+        <v>37</v>
+      </c>
+      <c r="H287">
+        <v>28</v>
+      </c>
+      <c r="I287">
+        <v>39</v>
+      </c>
+      <c r="J287">
+        <v>33</v>
+      </c>
+      <c r="K287">
+        <v>33</v>
+      </c>
+      <c r="L287">
+        <v>35</v>
+      </c>
+      <c r="M287">
+        <v>28</v>
+      </c>
+      <c r="N287">
+        <v>36</v>
+      </c>
+      <c r="O287" s="23">
+        <f t="shared" si="16"/>
+        <v>33</v>
+      </c>
+      <c r="P287" s="23">
+        <f t="shared" si="17"/>
+        <v>3.66</v>
+      </c>
+      <c r="R287">
+        <v>36</v>
+      </c>
+      <c r="S287">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="288" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B288" s="24">
+        <v>46125</v>
+      </c>
+      <c r="C288">
+        <v>42</v>
+      </c>
+      <c r="D288">
+        <v>25</v>
+      </c>
+      <c r="E288">
+        <v>21</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288">
+        <v>28</v>
+      </c>
+      <c r="H288">
+        <v>26</v>
+      </c>
+      <c r="I288">
+        <v>16</v>
+      </c>
+      <c r="J288">
         <v>30</v>
       </c>
-      <c r="M252" s="32">
-        <v>30.62</v>
-      </c>
-      <c r="N252" s="33">
-        <v>31.05</v>
-      </c>
-      <c r="O252" s="34">
-        <f>ROUND(AVERAGE(C252:N252,R252,S252),2)</f>
-        <v>29.1</v>
-      </c>
-      <c r="P252" s="34">
-        <f>ROUND(_xlfn.STDEV.P(C252:N252,R252,S252),2)</f>
-        <v>3.09</v>
-      </c>
-      <c r="R252">
-        <v>28.34</v>
-      </c>
-      <c r="S252">
-        <v>30.39</v>
-      </c>
-    </row>
-    <row r="253" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B253" s="20" t="s">
+      <c r="K288">
+        <v>41</v>
+      </c>
+      <c r="L288">
+        <v>24</v>
+      </c>
+      <c r="M288">
+        <v>22</v>
+      </c>
+      <c r="N288">
+        <v>25</v>
+      </c>
+      <c r="O288" s="23">
+        <f t="shared" si="16"/>
+        <v>27</v>
+      </c>
+      <c r="P288" s="23">
+        <f t="shared" si="17"/>
+        <v>6.73</v>
+      </c>
+      <c r="R288">
+        <v>27</v>
+      </c>
+      <c r="S288">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B289" s="24">
+        <v>46126</v>
+      </c>
+      <c r="C289">
+        <v>11</v>
+      </c>
+      <c r="D289">
+        <v>9</v>
+      </c>
+      <c r="E289">
+        <v>13</v>
+      </c>
+      <c r="F289">
+        <v>11</v>
+      </c>
+      <c r="G289">
+        <v>15</v>
+      </c>
+      <c r="H289">
+        <v>14</v>
+      </c>
+      <c r="I289">
+        <v>4</v>
+      </c>
+      <c r="J289">
+        <v>10</v>
+      </c>
+      <c r="K289">
+        <v>12</v>
+      </c>
+      <c r="L289">
+        <v>12</v>
+      </c>
+      <c r="M289">
+        <v>10</v>
+      </c>
+      <c r="N289">
+        <v>11</v>
+      </c>
+      <c r="O289" s="23">
+        <f t="shared" si="16"/>
+        <v>11</v>
+      </c>
+      <c r="P289" s="23">
+        <f t="shared" si="17"/>
+        <v>2.5</v>
+      </c>
+      <c r="R289">
+        <v>12</v>
+      </c>
+      <c r="S289">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B290" s="24">
+        <v>46127</v>
+      </c>
+      <c r="C290">
+        <v>17</v>
+      </c>
+      <c r="D290">
+        <v>20</v>
+      </c>
+      <c r="E290">
+        <v>13</v>
+      </c>
+      <c r="F290">
+        <v>16</v>
+      </c>
+      <c r="G290">
+        <v>16</v>
+      </c>
+      <c r="H290">
+        <v>18</v>
+      </c>
+      <c r="I290">
+        <v>12</v>
+      </c>
+      <c r="J290">
+        <v>16</v>
+      </c>
+      <c r="K290">
+        <v>16</v>
+      </c>
+      <c r="L290">
+        <v>16</v>
+      </c>
+      <c r="M290">
+        <v>15</v>
+      </c>
+      <c r="N290">
+        <v>19</v>
+      </c>
+      <c r="O290" s="23">
+        <f t="shared" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="P290" s="23">
+        <f t="shared" si="17"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="R290">
+        <v>13</v>
+      </c>
+      <c r="S290">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B291" s="24">
+        <v>46128</v>
+      </c>
+      <c r="C291">
+        <v>11</v>
+      </c>
+      <c r="D291">
+        <v>13</v>
+      </c>
+      <c r="E291">
+        <v>14</v>
+      </c>
+      <c r="F291">
+        <v>13</v>
+      </c>
+      <c r="G291">
+        <v>13</v>
+      </c>
+      <c r="H291">
+        <v>18</v>
+      </c>
+      <c r="I291">
+        <v>16</v>
+      </c>
+      <c r="J291">
+        <v>13</v>
+      </c>
+      <c r="K291">
+        <v>12</v>
+      </c>
+      <c r="L291">
+        <v>13</v>
+      </c>
+      <c r="M291">
+        <v>15</v>
+      </c>
+      <c r="N291">
+        <v>12</v>
+      </c>
+      <c r="O291" s="23">
+        <f t="shared" si="16"/>
+        <v>14</v>
+      </c>
+      <c r="P291" s="23">
+        <f t="shared" si="17"/>
+        <v>1.76</v>
+      </c>
+      <c r="R291">
+        <v>15</v>
+      </c>
+      <c r="S291">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="292" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B292" s="24">
+        <v>46129</v>
+      </c>
+      <c r="C292">
+        <v>17</v>
+      </c>
+      <c r="D292">
+        <v>13</v>
+      </c>
+      <c r="E292">
+        <v>20</v>
+      </c>
+      <c r="F292">
+        <v>16</v>
+      </c>
+      <c r="G292">
+        <v>16</v>
+      </c>
+      <c r="H292">
+        <v>16</v>
+      </c>
+      <c r="I292">
+        <v>20</v>
+      </c>
+      <c r="J292">
+        <v>15</v>
+      </c>
+      <c r="K292">
+        <v>20</v>
+      </c>
+      <c r="L292">
+        <v>16</v>
+      </c>
+      <c r="M292">
+        <v>17</v>
+      </c>
+      <c r="N292">
+        <v>14</v>
+      </c>
+      <c r="O292" s="23">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="P292" s="23">
+        <f t="shared" si="17"/>
+        <v>3.17</v>
+      </c>
+      <c r="R292">
+        <v>26</v>
+      </c>
+      <c r="S292">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="293" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B293" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C293" s="32">
+        <v>28.3</v>
+      </c>
+      <c r="D293" s="32">
+        <v>27.95</v>
+      </c>
+      <c r="E293" s="32">
+        <v>28.76</v>
+      </c>
+      <c r="F293" s="32">
+        <v>24.98</v>
+      </c>
+      <c r="G293" s="32">
+        <v>22.59</v>
+      </c>
+      <c r="H293" s="32">
+        <v>19.03</v>
+      </c>
+      <c r="I293" s="32">
+        <v>30.36</v>
+      </c>
+      <c r="J293" s="32">
+        <v>28.18</v>
+      </c>
+      <c r="K293" s="32">
+        <v>31.82</v>
+      </c>
+      <c r="L293" s="32">
+        <v>34.909999999999997</v>
+      </c>
+      <c r="M293" s="32">
+        <v>32.5</v>
+      </c>
+      <c r="N293" s="33">
+        <v>31.77</v>
+      </c>
+      <c r="O293" s="34">
+        <f>ROUND(AVERAGE(C293:N293,R293,S293),2)</f>
+        <v>28.41</v>
+      </c>
+      <c r="P293" s="34">
+        <f>ROUND(_xlfn.STDEV.P(C293:N293,R293,S293),2)</f>
+        <v>3.98</v>
+      </c>
+      <c r="R293">
+        <v>29.39</v>
+      </c>
+      <c r="S293">
+        <v>27.22</v>
+      </c>
+    </row>
+    <row r="294" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B294" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C253" s="16">
-        <v>11.84</v>
-      </c>
-      <c r="D253" s="16">
-        <v>13.92</v>
-      </c>
-      <c r="E253" s="16">
-        <v>18.37</v>
-      </c>
-      <c r="F253" s="16">
-        <v>14.94</v>
-      </c>
-      <c r="G253" s="16">
-        <v>14.51</v>
-      </c>
-      <c r="H253" s="16">
-        <v>18.7</v>
-      </c>
-      <c r="I253" s="16">
-        <v>13.99</v>
-      </c>
-      <c r="J253" s="16">
-        <v>14.47</v>
-      </c>
-      <c r="K253" s="16">
-        <v>11.76</v>
-      </c>
-      <c r="L253" s="16">
-        <v>12.07</v>
-      </c>
-      <c r="M253" s="16">
-        <v>12.25</v>
-      </c>
-      <c r="N253" s="17">
-        <v>12.32</v>
-      </c>
-      <c r="O253" s="34">
-        <f>ROUND(AVERAGE(C253:N253,R253,S253),2)</f>
-        <v>14.08</v>
-      </c>
-      <c r="P253" s="34">
-        <f>ROUND(_xlfn.STDEV.P(C253:N253,R253,S253),2)</f>
-        <v>2.1</v>
-      </c>
-      <c r="R253">
-        <v>13.79</v>
-      </c>
-      <c r="S253">
-        <v>14.24</v>
-      </c>
-    </row>
-    <row r="254" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B254" s="24"/>
-      <c r="C254" s="39" t="s">
+      <c r="C294" s="16">
+        <v>13.62</v>
+      </c>
+      <c r="D294" s="16">
+        <v>13.56</v>
+      </c>
+      <c r="E294" s="16">
+        <v>14.55</v>
+      </c>
+      <c r="F294" s="16">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="G294" s="16">
+        <v>17.670000000000002</v>
+      </c>
+      <c r="H294" s="16">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="I294" s="16">
+        <v>14.2</v>
+      </c>
+      <c r="J294" s="16">
+        <v>13.42</v>
+      </c>
+      <c r="K294" s="16">
+        <v>13.15</v>
+      </c>
+      <c r="L294" s="16">
+        <v>11.42</v>
+      </c>
+      <c r="M294" s="16">
+        <v>12.51</v>
+      </c>
+      <c r="N294" s="17">
+        <v>12.85</v>
+      </c>
+      <c r="O294" s="34">
+        <f>ROUND(AVERAGE(C294:N294,R294,S294),2)</f>
+        <v>14.56</v>
+      </c>
+      <c r="P294" s="34">
+        <f>ROUND(_xlfn.STDEV.P(C294:N294,R294,S294),2)</f>
+        <v>2.16</v>
+      </c>
+      <c r="R294">
+        <v>14.17</v>
+      </c>
+      <c r="S294">
+        <v>16.91</v>
+      </c>
+    </row>
+    <row r="295" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B295" s="24"/>
+      <c r="C295" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D254" s="39"/>
-      <c r="E254" s="39" t="s">
+      <c r="D295" s="47"/>
+      <c r="E295" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F254" s="39"/>
-      <c r="G254" s="39" t="s">
+      <c r="F295" s="47"/>
+      <c r="G295" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H254" s="39"/>
-      <c r="I254" s="39" t="s">
+      <c r="H295" s="47"/>
+      <c r="I295" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="J254" s="39"/>
-      <c r="K254" s="43" t="s">
+      <c r="J295" s="47"/>
+      <c r="K295" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="L254" s="43"/>
-      <c r="M254" s="43" t="s">
+      <c r="L295" s="48"/>
+      <c r="M295" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="N254" s="43"/>
-      <c r="R254" s="39" t="s">
+      <c r="N295" s="48"/>
+      <c r="R295" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="S254" s="39"/>
-    </row>
-    <row r="255" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="C255" t="s">
+      <c r="S295" s="47"/>
+    </row>
+    <row r="296" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C296" t="s">
         <v>55</v>
       </c>
-      <c r="D255" t="s">
+      <c r="D296" t="s">
         <v>56</v>
       </c>
-      <c r="E255" t="s">
+      <c r="E296" t="s">
         <v>55</v>
       </c>
-      <c r="F255" t="s">
+      <c r="F296" t="s">
         <v>56</v>
       </c>
-      <c r="G255" t="s">
+      <c r="G296" t="s">
         <v>55</v>
       </c>
-      <c r="H255" t="s">
+      <c r="H296" t="s">
         <v>56</v>
       </c>
-      <c r="I255" t="s">
+      <c r="I296" t="s">
         <v>55</v>
       </c>
-      <c r="J255" t="s">
+      <c r="J296" t="s">
         <v>56</v>
       </c>
-      <c r="K255" t="s">
+      <c r="K296" t="s">
         <v>55</v>
       </c>
-      <c r="L255" t="s">
+      <c r="L296" t="s">
         <v>56</v>
       </c>
-      <c r="M255" t="s">
+      <c r="M296" t="s">
         <v>55</v>
       </c>
-      <c r="N255" t="s">
+      <c r="N296" t="s">
         <v>56</v>
       </c>
-      <c r="R255" t="s">
+      <c r="R296" t="s">
         <v>55</v>
       </c>
-      <c r="S255" t="s">
+      <c r="S296" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="256" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B256" t="s">
+    <row r="297" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
         <v>57</v>
       </c>
-      <c r="C256">
-        <v>72.492999999999995</v>
-      </c>
-      <c r="D256">
-        <v>71.766999999999996</v>
-      </c>
-      <c r="E256">
-        <v>85.573999999999998</v>
-      </c>
-      <c r="F256">
-        <v>73.179000000000002</v>
-      </c>
-      <c r="G256">
-        <v>24.437999999999999</v>
-      </c>
-      <c r="H256">
-        <v>12.88</v>
-      </c>
-      <c r="I256">
-        <v>121.943</v>
-      </c>
-      <c r="J256">
-        <v>124.828</v>
-      </c>
-      <c r="K256">
-        <v>86.710999999999999</v>
-      </c>
-      <c r="L256">
-        <v>89.936999999999998</v>
-      </c>
-      <c r="M256">
-        <v>148.298</v>
-      </c>
-      <c r="N256">
-        <v>146.03</v>
-      </c>
-      <c r="R256">
-        <v>191.82900000000001</v>
-      </c>
-      <c r="S256">
-        <v>183.238</v>
-      </c>
-    </row>
-    <row r="257" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B257" t="s">
+      <c r="C297">
+        <v>75.162000000000006</v>
+      </c>
+      <c r="D297">
+        <v>71.727000000000004</v>
+      </c>
+      <c r="E297">
+        <v>88.418999999999997</v>
+      </c>
+      <c r="F297">
+        <v>89.831999999999994</v>
+      </c>
+      <c r="G297">
+        <v>26.315000000000001</v>
+      </c>
+      <c r="H297">
+        <v>15.343</v>
+      </c>
+      <c r="I297">
+        <v>105.959</v>
+      </c>
+      <c r="J297">
+        <v>114.395</v>
+      </c>
+      <c r="K297">
+        <v>108.185</v>
+      </c>
+      <c r="L297">
+        <v>103.062</v>
+      </c>
+      <c r="M297">
+        <v>164.20099999999999</v>
+      </c>
+      <c r="N297">
+        <v>187.61600000000001</v>
+      </c>
+      <c r="R297">
+        <v>205.511</v>
+      </c>
+      <c r="S297">
+        <v>201.929</v>
+      </c>
+    </row>
+    <row r="298" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B298" t="s">
         <v>58</v>
       </c>
-      <c r="C257" s="38"/>
-      <c r="D257" s="38"/>
-      <c r="E257" s="38"/>
-      <c r="F257" s="38"/>
-      <c r="G257" s="38"/>
-      <c r="H257" s="38"/>
-      <c r="I257" s="45">
-        <v>0.83809999999999996</v>
-      </c>
-      <c r="J257" s="45">
-        <v>0.85819999999999996</v>
-      </c>
-      <c r="K257" s="45">
-        <v>0.79510000000000003</v>
-      </c>
-      <c r="L257" s="45">
-        <v>0.67910000000000004</v>
-      </c>
-      <c r="M257" s="45">
-        <v>0.75929999999999997</v>
-      </c>
-      <c r="N257" s="45">
-        <v>0.75360000000000005</v>
-      </c>
-      <c r="R257" s="45">
-        <v>0.72350000000000003</v>
-      </c>
-      <c r="S257" s="45">
-        <v>0.78800000000000003</v>
+      <c r="C298" s="38"/>
+      <c r="D298" s="38"/>
+      <c r="E298" s="38"/>
+      <c r="F298" s="38"/>
+      <c r="G298" s="38"/>
+      <c r="H298" s="38"/>
+      <c r="I298" s="39">
+        <v>0.67169999999999996</v>
+      </c>
+      <c r="J298" s="39">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="K298" s="39">
+        <v>0.84830000000000005</v>
+      </c>
+      <c r="L298" s="39">
+        <v>0.77790000000000004</v>
+      </c>
+      <c r="M298" s="39">
+        <v>0.76829999999999998</v>
+      </c>
+      <c r="N298" s="39">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="R298" s="39">
+        <v>0.85240000000000005</v>
+      </c>
+      <c r="S298" s="39">
+        <v>0.83450000000000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="R254:S254"/>
+    <mergeCell ref="R295:S295"/>
     <mergeCell ref="C1:N1"/>
-    <mergeCell ref="C254:D254"/>
-    <mergeCell ref="E254:F254"/>
-    <mergeCell ref="G254:H254"/>
-    <mergeCell ref="I254:J254"/>
-    <mergeCell ref="K254:L254"/>
-    <mergeCell ref="M254:N254"/>
+    <mergeCell ref="C295:D295"/>
+    <mergeCell ref="E295:F295"/>
+    <mergeCell ref="G295:H295"/>
+    <mergeCell ref="I295:J295"/>
+    <mergeCell ref="K295:L295"/>
+    <mergeCell ref="M295:N295"/>
   </mergeCells>
-  <conditionalFormatting sqref="C252:N253">
+  <conditionalFormatting sqref="C293:N294">
     <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>20</formula>
     </cfRule>
@@ -31433,7 +34851,7 @@
       <formula>ABS(C116-$A116)&lt;=10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q233">
+  <conditionalFormatting sqref="Q1:Q260">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -31447,7 +34865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2573A6AB-8DBE-4210-8EFE-4E449AA3F45B}">
-  <dimension ref="A1:S252"/>
+  <dimension ref="A1:S293"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
@@ -31458,20 +34876,20 @@
         <v>43</v>
       </c>
       <c r="B1" s="7"/>
-      <c r="C1" s="40">
+      <c r="C1" s="43">
         <v>0.85</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="45"/>
       <c r="O1" s="22" t="s">
         <v>39</v>
       </c>
@@ -39136,7 +42554,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="Q195" t="e">
-        <f t="shared" ref="Q195:Q233" si="12">O195-A195</f>
+        <f t="shared" ref="Q195:Q258" si="12">O195-A195</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -41497,6 +44915,9 @@
       </c>
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A234" s="14">
+        <v>3</v>
+      </c>
       <c r="B234" s="24">
         <v>46071</v>
       </c>
@@ -41504,7 +44925,7 @@
         <v>23</v>
       </c>
       <c r="D234">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E234">
         <v>20</v>
@@ -41516,13 +44937,13 @@
         <v>19</v>
       </c>
       <c r="H234">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I234">
         <v>16</v>
       </c>
       <c r="J234">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K234">
         <v>13</v>
@@ -41534,7 +44955,7 @@
         <v>23</v>
       </c>
       <c r="N234">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O234" s="23">
         <f t="shared" si="13"/>
@@ -41542,16 +44963,23 @@
       </c>
       <c r="P234" s="23">
         <f t="shared" si="14"/>
-        <v>4.8899999999999997</v>
+        <v>3.32</v>
+      </c>
+      <c r="Q234">
+        <f t="shared" si="12"/>
+        <v>15</v>
       </c>
       <c r="R234">
         <v>16</v>
       </c>
       <c r="S234">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A235" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B235" s="24">
         <v>46072</v>
       </c>
@@ -41559,31 +44987,31 @@
         <v>12</v>
       </c>
       <c r="D235">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E235">
         <v>16</v>
       </c>
       <c r="F235">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G235">
         <v>19</v>
       </c>
       <c r="H235">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I235">
         <v>13</v>
       </c>
       <c r="J235">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K235">
         <v>14</v>
       </c>
       <c r="L235">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M235">
         <v>15</v>
@@ -41593,20 +45021,27 @@
       </c>
       <c r="O235" s="23">
         <f t="shared" si="13"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P235" s="23">
         <f t="shared" si="14"/>
-        <v>3.37</v>
+        <v>3.18</v>
+      </c>
+      <c r="Q235">
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="R235">
         <v>18</v>
       </c>
       <c r="S235">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A236" s="14">
+        <v>18</v>
+      </c>
       <c r="B236" s="24">
         <v>46073</v>
       </c>
@@ -41614,54 +45049,61 @@
         <v>10</v>
       </c>
       <c r="D236">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E236">
         <v>17</v>
       </c>
       <c r="F236">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G236">
         <v>19</v>
       </c>
       <c r="H236">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="I236">
         <v>12</v>
       </c>
       <c r="J236">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K236">
         <v>12</v>
       </c>
       <c r="L236">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M236">
         <v>13</v>
       </c>
       <c r="N236">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O236" s="23">
         <f t="shared" si="13"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P236" s="23">
         <f t="shared" si="14"/>
-        <v>4.57</v>
+        <v>7.36</v>
+      </c>
+      <c r="Q236">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="R236">
         <v>17</v>
       </c>
       <c r="S236">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A237" s="14">
+        <v>19</v>
+      </c>
       <c r="B237" s="24">
         <v>46074</v>
       </c>
@@ -41669,54 +45111,61 @@
         <v>44</v>
       </c>
       <c r="D237">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E237">
         <v>26</v>
       </c>
       <c r="F237">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G237">
         <v>19</v>
       </c>
       <c r="H237">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I237">
         <v>15</v>
       </c>
       <c r="J237">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K237">
         <v>15</v>
       </c>
       <c r="L237">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M237">
         <v>46</v>
       </c>
       <c r="N237">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="O237" s="23">
         <f t="shared" si="13"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P237" s="23">
         <f t="shared" si="14"/>
-        <v>9.4</v>
+        <v>10.19</v>
+      </c>
+      <c r="Q237">
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="R237">
         <v>18</v>
       </c>
       <c r="S237">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A238" s="14">
+        <v>29</v>
+      </c>
       <c r="B238" s="24">
         <v>46075</v>
       </c>
@@ -41724,54 +45173,61 @@
         <v>39</v>
       </c>
       <c r="D238">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E238">
         <v>23</v>
       </c>
       <c r="F238">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G238">
         <v>19</v>
       </c>
       <c r="H238">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I238">
         <v>43</v>
       </c>
       <c r="J238">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="K238">
         <v>16</v>
       </c>
       <c r="L238">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="M238">
         <v>26</v>
       </c>
       <c r="N238">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O238" s="23">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P238" s="23">
         <f t="shared" si="14"/>
-        <v>13.77</v>
+        <v>9.15</v>
+      </c>
+      <c r="Q238">
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="R238">
         <v>40</v>
       </c>
       <c r="S238">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A239" s="14">
+        <v>12</v>
+      </c>
       <c r="B239" s="24">
         <v>46076</v>
       </c>
@@ -41779,13 +45235,13 @@
         <v>10</v>
       </c>
       <c r="D239">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E239">
         <v>16</v>
       </c>
       <c r="F239">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G239">
         <v>19</v>
@@ -41797,36 +45253,43 @@
         <v>12</v>
       </c>
       <c r="J239">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K239">
         <v>18</v>
       </c>
       <c r="L239">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M239">
         <v>11</v>
       </c>
       <c r="N239">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O239" s="23">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P239" s="23">
         <f t="shared" si="14"/>
-        <v>3.8</v>
+        <v>3.82</v>
+      </c>
+      <c r="Q239">
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="R239">
         <v>15</v>
       </c>
       <c r="S239">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A240" s="14">
+        <v>8</v>
+      </c>
       <c r="B240" s="24">
         <v>46077</v>
       </c>
@@ -41840,39 +45303,43 @@
         <v>19</v>
       </c>
       <c r="F240">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G240">
         <v>19</v>
       </c>
       <c r="H240">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I240">
         <v>16</v>
       </c>
       <c r="J240">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K240">
         <v>16</v>
       </c>
       <c r="L240">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M240">
         <v>17</v>
       </c>
       <c r="N240">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O240" s="23">
         <f t="shared" si="13"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P240" s="23">
         <f t="shared" si="14"/>
-        <v>4.54</v>
+        <v>4.05</v>
+      </c>
+      <c r="Q240">
+        <f t="shared" si="12"/>
+        <v>6</v>
       </c>
       <c r="R240">
         <v>22</v>
@@ -41881,7 +45348,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A241" s="14">
+        <v>16</v>
+      </c>
       <c r="B241" s="24">
         <v>46078</v>
       </c>
@@ -41889,13 +45359,13 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E241">
         <v>13</v>
       </c>
       <c r="F241">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G241">
         <v>19</v>
@@ -41907,36 +45377,43 @@
         <v>12</v>
       </c>
       <c r="J241">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K241">
         <v>11</v>
       </c>
       <c r="L241">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M241">
         <v>17</v>
       </c>
       <c r="N241">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O241" s="23">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P241" s="23">
         <f t="shared" si="14"/>
-        <v>3.68</v>
+        <v>3.73</v>
+      </c>
+      <c r="Q241">
+        <f t="shared" si="12"/>
+        <v>-3</v>
       </c>
       <c r="R241">
         <v>13</v>
       </c>
       <c r="S241">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="242" spans="2:19" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A242" s="14">
+        <v>15</v>
+      </c>
       <c r="B242" s="24">
         <v>46079</v>
       </c>
@@ -41950,25 +45427,25 @@
         <v>21</v>
       </c>
       <c r="F242">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G242">
         <v>22</v>
       </c>
       <c r="H242">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I242">
         <v>14</v>
       </c>
       <c r="J242">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K242">
         <v>12</v>
       </c>
       <c r="L242">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M242">
         <v>25</v>
@@ -41982,16 +45459,23 @@
       </c>
       <c r="P242" s="23">
         <f t="shared" si="14"/>
-        <v>4.6399999999999997</v>
+        <v>5</v>
+      </c>
+      <c r="Q242">
+        <f t="shared" si="12"/>
+        <v>2</v>
       </c>
       <c r="R242">
         <v>14</v>
       </c>
       <c r="S242">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="243" spans="2:19" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A243" s="14">
+        <v>28</v>
+      </c>
       <c r="B243" s="24">
         <v>46080</v>
       </c>
@@ -41999,54 +45483,61 @@
         <v>16</v>
       </c>
       <c r="D243">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E243">
         <v>22</v>
       </c>
       <c r="F243">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G243">
         <v>19</v>
       </c>
       <c r="H243">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I243">
         <v>14</v>
       </c>
       <c r="J243">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K243">
         <v>15</v>
       </c>
       <c r="L243">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M243">
         <v>20</v>
       </c>
       <c r="N243">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O243" s="23">
         <f t="shared" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P243" s="23">
         <f t="shared" si="14"/>
-        <v>4.34</v>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q243">
+        <f t="shared" si="12"/>
+        <v>-8</v>
       </c>
       <c r="R243">
         <v>19</v>
       </c>
       <c r="S243">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="244" spans="2:19" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A244" s="14">
+        <v>17</v>
+      </c>
       <c r="B244" s="24">
         <v>46081</v>
       </c>
@@ -42054,54 +45545,61 @@
         <v>17</v>
       </c>
       <c r="D244">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E244">
         <v>23</v>
       </c>
       <c r="F244">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G244">
         <v>21</v>
       </c>
       <c r="H244">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I244">
         <v>20</v>
       </c>
       <c r="J244">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K244">
         <v>15</v>
       </c>
       <c r="L244">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="M244">
         <v>16</v>
       </c>
       <c r="N244">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O244" s="23">
         <f t="shared" si="13"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P244" s="23">
         <f t="shared" si="14"/>
-        <v>4.05</v>
+        <v>6</v>
+      </c>
+      <c r="Q244">
+        <f t="shared" si="12"/>
+        <v>7</v>
       </c>
       <c r="R244">
         <v>23</v>
       </c>
       <c r="S244">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="245" spans="2:19" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A245" s="14">
+        <v>70</v>
+      </c>
       <c r="B245" s="24">
         <v>46082</v>
       </c>
@@ -42109,54 +45607,61 @@
         <v>17</v>
       </c>
       <c r="D245">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E245">
         <v>19</v>
       </c>
       <c r="F245">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G245">
         <v>22</v>
       </c>
       <c r="H245">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I245">
         <v>18</v>
       </c>
       <c r="J245">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K245">
         <v>17</v>
       </c>
       <c r="L245">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M245">
         <v>14</v>
       </c>
       <c r="N245">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O245" s="23">
         <f t="shared" si="13"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P245" s="23">
         <f t="shared" si="14"/>
-        <v>7.53</v>
+        <v>6.93</v>
+      </c>
+      <c r="Q245">
+        <f t="shared" si="12"/>
+        <v>-48</v>
       </c>
       <c r="R245">
         <v>41</v>
       </c>
       <c r="S245">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="246" spans="2:19" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A246" s="14">
+        <v>21</v>
+      </c>
       <c r="B246" s="24">
         <v>46083</v>
       </c>
@@ -42164,54 +45669,61 @@
         <v>30</v>
       </c>
       <c r="D246">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E246">
         <v>18</v>
       </c>
       <c r="F246">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G246">
         <v>20</v>
       </c>
       <c r="H246">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I246">
         <v>13</v>
       </c>
       <c r="J246">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K246">
         <v>23</v>
       </c>
       <c r="L246">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M246">
         <v>35</v>
       </c>
       <c r="N246">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O246" s="23">
         <f t="shared" si="13"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P246" s="23">
         <f t="shared" si="14"/>
-        <v>7.41</v>
+        <v>7.12</v>
+      </c>
+      <c r="Q246">
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="R246">
         <v>28</v>
       </c>
       <c r="S246">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="247" spans="2:19" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A247" s="14">
+        <v>9</v>
+      </c>
       <c r="B247" s="24">
         <v>46084</v>
       </c>
@@ -42219,7 +45731,7 @@
         <v>15</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E247">
         <v>18</v>
@@ -42231,42 +45743,49 @@
         <v>19</v>
       </c>
       <c r="H247">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I247">
         <v>12</v>
       </c>
       <c r="J247">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K247">
         <v>13</v>
       </c>
       <c r="L247">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M247">
         <v>12</v>
       </c>
       <c r="N247">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O247" s="23">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P247" s="23">
         <f t="shared" si="14"/>
-        <v>3.11</v>
+        <v>3.13</v>
+      </c>
+      <c r="Q247">
+        <f t="shared" si="12"/>
+        <v>4</v>
       </c>
       <c r="R247">
         <v>14</v>
       </c>
       <c r="S247">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="248" spans="2:19" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A248" s="14">
+        <v>18</v>
+      </c>
       <c r="B248" s="24">
         <v>46085</v>
       </c>
@@ -42274,31 +45793,31 @@
         <v>11</v>
       </c>
       <c r="D248">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E248">
         <v>18</v>
       </c>
       <c r="F248">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G248">
         <v>21</v>
       </c>
       <c r="H248">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I248">
         <v>12</v>
       </c>
       <c r="J248">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K248">
         <v>20</v>
       </c>
       <c r="L248">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M248">
         <v>10</v>
@@ -42308,11 +45827,15 @@
       </c>
       <c r="O248" s="23">
         <f t="shared" si="13"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P248" s="23">
         <f t="shared" si="14"/>
-        <v>5.25</v>
+        <v>4.59</v>
+      </c>
+      <c r="Q248">
+        <f t="shared" si="12"/>
+        <v>-4</v>
       </c>
       <c r="R248">
         <v>21</v>
@@ -42321,7 +45844,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="249" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A249" s="14">
+        <v>7</v>
+      </c>
       <c r="B249" s="24">
         <v>46086</v>
       </c>
@@ -42329,19 +45855,19 @@
         <v>19</v>
       </c>
       <c r="D249">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E249">
         <v>17</v>
       </c>
       <c r="F249">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G249">
         <v>25</v>
       </c>
       <c r="H249">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I249">
         <v>14</v>
@@ -42353,13 +45879,13 @@
         <v>14</v>
       </c>
       <c r="L249">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M249">
         <v>25</v>
       </c>
       <c r="N249">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O249" s="23">
         <f t="shared" si="13"/>
@@ -42367,16 +45893,23 @@
       </c>
       <c r="P249" s="23">
         <f t="shared" si="14"/>
-        <v>3.66</v>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="Q249">
+        <f t="shared" si="12"/>
+        <v>11</v>
       </c>
       <c r="R249">
         <v>20</v>
       </c>
       <c r="S249">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="250" spans="2:19" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A250" s="14">
+        <v>6</v>
+      </c>
       <c r="B250" s="24">
         <v>46087</v>
       </c>
@@ -42384,25 +45917,25 @@
         <v>10</v>
       </c>
       <c r="D250">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E250">
         <v>22</v>
       </c>
       <c r="F250">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G250">
         <v>19</v>
       </c>
       <c r="H250">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I250">
         <v>18</v>
       </c>
       <c r="J250">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K250">
         <v>20</v>
@@ -42422,16 +45955,23 @@
       </c>
       <c r="P250" s="23">
         <f t="shared" si="14"/>
-        <v>4.6399999999999997</v>
+        <v>3.66</v>
+      </c>
+      <c r="Q250">
+        <f t="shared" si="12"/>
+        <v>10</v>
       </c>
       <c r="R250">
         <v>13</v>
       </c>
       <c r="S250">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="251" spans="2:19" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A251" s="14">
+        <v>13</v>
+      </c>
       <c r="B251" s="24">
         <v>46088</v>
       </c>
@@ -42439,31 +45979,31 @@
         <v>34</v>
       </c>
       <c r="D251">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E251">
         <v>27</v>
       </c>
       <c r="F251">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G251">
         <v>26</v>
       </c>
       <c r="H251">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I251">
         <v>18</v>
       </c>
       <c r="J251">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K251">
         <v>30</v>
       </c>
       <c r="L251">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M251">
         <v>32</v>
@@ -42473,63 +46013,2198 @@
       </c>
       <c r="O251" s="23">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P251" s="23">
         <f t="shared" si="14"/>
-        <v>4.55</v>
+        <v>5.24</v>
+      </c>
+      <c r="Q251">
+        <f t="shared" si="12"/>
+        <v>15</v>
       </c>
       <c r="R251">
         <v>32</v>
       </c>
       <c r="S251">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A252" s="14">
+        <v>73</v>
+      </c>
+      <c r="B252" s="24">
+        <v>46089</v>
+      </c>
+      <c r="D252">
+        <v>22</v>
+      </c>
+      <c r="F252">
+        <v>48</v>
+      </c>
+      <c r="H252">
+        <v>82</v>
+      </c>
+      <c r="J252">
+        <v>19</v>
+      </c>
+      <c r="L252">
+        <v>19</v>
+      </c>
+      <c r="N252">
+        <v>27</v>
+      </c>
+      <c r="O252" s="23">
+        <f t="shared" ref="O252:O292" si="15">ROUND(AVERAGE(C252:N252,R252,S252),0)</f>
+        <v>38</v>
+      </c>
+      <c r="P252" s="23">
+        <f t="shared" ref="P252:P292" si="16">ROUND(_xlfn.STDEV.P(C252:N252,R252,S252),2)</f>
+        <v>21.64</v>
+      </c>
+      <c r="Q252">
+        <f t="shared" si="12"/>
+        <v>-35</v>
+      </c>
+      <c r="S252">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A253" s="14">
+        <v>12</v>
+      </c>
+      <c r="B253" s="24">
+        <v>46090</v>
+      </c>
+      <c r="D253">
+        <v>14</v>
+      </c>
+      <c r="F253">
+        <v>11</v>
+      </c>
+      <c r="H253">
+        <v>15</v>
+      </c>
+      <c r="J253">
+        <v>11</v>
+      </c>
+      <c r="L253">
+        <v>15</v>
+      </c>
+      <c r="N253">
+        <v>12</v>
+      </c>
+      <c r="O253" s="23">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="P253" s="23">
+        <f t="shared" si="16"/>
+        <v>1.64</v>
+      </c>
+      <c r="Q253">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="S253">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A254" s="14">
+        <v>27</v>
+      </c>
+      <c r="B254" s="24">
+        <v>46091</v>
+      </c>
+      <c r="D254">
+        <v>17</v>
+      </c>
+      <c r="F254">
+        <v>19</v>
+      </c>
+      <c r="H254">
+        <v>9</v>
+      </c>
+      <c r="J254">
+        <v>16</v>
+      </c>
+      <c r="L254">
+        <v>13</v>
+      </c>
+      <c r="N254">
+        <v>12</v>
+      </c>
+      <c r="O254" s="23">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="P254" s="23">
+        <f t="shared" si="16"/>
+        <v>3.16</v>
+      </c>
+      <c r="Q254">
+        <f t="shared" si="12"/>
+        <v>-12</v>
+      </c>
+      <c r="S254">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A255" s="14">
+        <v>24</v>
+      </c>
+      <c r="B255" s="24">
+        <v>46092</v>
+      </c>
+      <c r="D255">
+        <v>13</v>
+      </c>
+      <c r="F255">
+        <v>11</v>
+      </c>
+      <c r="H255">
+        <v>22</v>
+      </c>
+      <c r="J255">
+        <v>13</v>
+      </c>
+      <c r="L255">
+        <v>12</v>
+      </c>
+      <c r="N255">
+        <v>11</v>
+      </c>
+      <c r="O255" s="23">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="P255" s="23">
+        <f t="shared" si="16"/>
+        <v>3.89</v>
+      </c>
+      <c r="Q255">
+        <f t="shared" si="12"/>
+        <v>-11</v>
+      </c>
+      <c r="S255">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A256" s="14">
+        <v>4</v>
+      </c>
+      <c r="B256" s="24">
+        <v>46093</v>
+      </c>
+      <c r="D256">
+        <v>14</v>
+      </c>
+      <c r="F256">
+        <v>11</v>
+      </c>
+      <c r="H256">
+        <v>7</v>
+      </c>
+      <c r="J256">
+        <v>13</v>
+      </c>
+      <c r="L256">
+        <v>13</v>
+      </c>
+      <c r="N256">
+        <v>13</v>
+      </c>
+      <c r="O256" s="23">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="P256" s="23">
+        <f t="shared" si="16"/>
+        <v>2.19</v>
+      </c>
+      <c r="Q256">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="S256">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A257" s="14">
+        <v>28</v>
+      </c>
+      <c r="B257" s="24">
+        <v>46094</v>
+      </c>
+      <c r="D257">
+        <v>23</v>
+      </c>
+      <c r="F257">
+        <v>21</v>
+      </c>
+      <c r="H257">
+        <v>39</v>
+      </c>
+      <c r="J257">
+        <v>20</v>
+      </c>
+      <c r="L257">
+        <v>25</v>
+      </c>
+      <c r="N257">
+        <v>25</v>
+      </c>
+      <c r="O257" s="23">
+        <f t="shared" si="15"/>
+        <v>26</v>
+      </c>
+      <c r="P257" s="23">
+        <f t="shared" si="16"/>
+        <v>6.16</v>
+      </c>
+      <c r="Q257">
+        <f t="shared" si="12"/>
+        <v>-2</v>
+      </c>
+      <c r="S257">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A258" s="14">
+        <v>17</v>
+      </c>
+      <c r="B258" s="24">
+        <v>46095</v>
+      </c>
+      <c r="D258">
+        <v>23</v>
+      </c>
+      <c r="F258">
+        <v>14</v>
+      </c>
+      <c r="H258">
+        <v>14</v>
+      </c>
+      <c r="J258">
+        <v>30</v>
+      </c>
+      <c r="L258">
+        <v>24</v>
+      </c>
+      <c r="N258">
+        <v>20</v>
+      </c>
+      <c r="O258" s="23">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="P258" s="23">
+        <f t="shared" si="16"/>
+        <v>5.29</v>
+      </c>
+      <c r="Q258">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="S258">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A259" s="14">
+        <v>66</v>
+      </c>
+      <c r="B259" s="24">
+        <v>46096</v>
+      </c>
+      <c r="D259">
+        <v>22</v>
+      </c>
+      <c r="F259">
+        <v>49</v>
+      </c>
+      <c r="H259">
+        <v>72</v>
+      </c>
+      <c r="J259">
+        <v>15</v>
+      </c>
+      <c r="L259">
+        <v>17</v>
+      </c>
+      <c r="N259">
+        <v>27</v>
+      </c>
+      <c r="O259" s="23">
+        <f t="shared" si="15"/>
+        <v>34</v>
+      </c>
+      <c r="P259" s="23">
+        <f t="shared" si="16"/>
+        <v>18.940000000000001</v>
+      </c>
+      <c r="Q259">
+        <f t="shared" ref="Q259:Q260" si="17">O259-A259</f>
+        <v>-32</v>
+      </c>
+      <c r="S259">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A260" s="14">
+        <v>7</v>
+      </c>
+      <c r="B260" s="24">
+        <v>46097</v>
+      </c>
+      <c r="D260">
+        <v>14</v>
+      </c>
+      <c r="F260">
+        <v>10</v>
+      </c>
+      <c r="H260">
+        <v>11</v>
+      </c>
+      <c r="J260">
+        <v>7</v>
+      </c>
+      <c r="L260">
+        <v>13</v>
+      </c>
+      <c r="N260">
+        <v>13</v>
+      </c>
+      <c r="O260" s="23">
+        <f t="shared" si="15"/>
+        <v>11</v>
+      </c>
+      <c r="P260" s="23">
+        <f t="shared" si="16"/>
+        <v>2.23</v>
+      </c>
+      <c r="Q260">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="S260">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A261" s="26"/>
+      <c r="B261" s="27">
+        <v>46098</v>
+      </c>
+      <c r="C261" s="26">
+        <v>11</v>
+      </c>
+      <c r="D261" s="26">
+        <v>16</v>
+      </c>
+      <c r="E261" s="26">
+        <v>14</v>
+      </c>
+      <c r="F261" s="26">
+        <v>11</v>
+      </c>
+      <c r="G261" s="26">
+        <v>13</v>
+      </c>
+      <c r="H261" s="26">
+        <v>7</v>
+      </c>
+      <c r="I261" s="26">
+        <v>14</v>
+      </c>
+      <c r="J261" s="26">
+        <v>8</v>
+      </c>
+      <c r="K261" s="26">
+        <v>11</v>
+      </c>
+      <c r="L261" s="26">
+        <v>14</v>
+      </c>
+      <c r="M261" s="26">
+        <v>15</v>
+      </c>
+      <c r="N261" s="26">
+        <v>12</v>
+      </c>
+      <c r="O261" s="28">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="P261" s="28">
+        <f t="shared" si="16"/>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Q261" s="26"/>
+      <c r="R261" s="26">
+        <v>13</v>
+      </c>
+      <c r="S261" s="26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B262" s="24">
+        <v>46099</v>
+      </c>
+      <c r="C262">
+        <v>20</v>
+      </c>
+      <c r="D262">
+        <v>14</v>
+      </c>
+      <c r="E262">
+        <v>13</v>
+      </c>
+      <c r="F262">
+        <v>12</v>
+      </c>
+      <c r="G262">
+        <v>11</v>
+      </c>
+      <c r="H262">
+        <v>7</v>
+      </c>
+      <c r="I262">
+        <v>14</v>
+      </c>
+      <c r="J262">
+        <v>9</v>
+      </c>
+      <c r="K262">
+        <v>21</v>
+      </c>
+      <c r="L262">
+        <v>14</v>
+      </c>
+      <c r="M262">
+        <v>16</v>
+      </c>
+      <c r="N262">
+        <v>14</v>
+      </c>
+      <c r="O262" s="23">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="P262" s="23">
+        <f t="shared" si="16"/>
+        <v>3.58</v>
+      </c>
+      <c r="R262">
+        <v>12</v>
+      </c>
+      <c r="S262">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B263" s="24">
+        <v>46100</v>
+      </c>
+      <c r="C263">
+        <v>12</v>
+      </c>
+      <c r="D263">
+        <v>11</v>
+      </c>
+      <c r="E263">
+        <v>13</v>
+      </c>
+      <c r="F263">
+        <v>11</v>
+      </c>
+      <c r="G263">
+        <v>10</v>
+      </c>
+      <c r="H263">
+        <v>4</v>
+      </c>
+      <c r="I263">
+        <v>14</v>
+      </c>
+      <c r="J263">
+        <v>11</v>
+      </c>
+      <c r="K263">
+        <v>14</v>
+      </c>
+      <c r="L263">
+        <v>14</v>
+      </c>
+      <c r="M263">
+        <v>15</v>
+      </c>
+      <c r="N263">
+        <v>12</v>
+      </c>
+      <c r="O263" s="23">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="P263" s="23">
+        <f t="shared" si="16"/>
+        <v>2.58</v>
+      </c>
+      <c r="R263">
+        <v>12</v>
+      </c>
+      <c r="S263">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B264" s="24">
+        <v>46101</v>
+      </c>
+      <c r="C264">
+        <v>23</v>
+      </c>
+      <c r="D264">
+        <v>17</v>
+      </c>
+      <c r="E264">
+        <v>27</v>
+      </c>
+      <c r="F264">
+        <v>19</v>
+      </c>
+      <c r="G264">
+        <v>17</v>
+      </c>
+      <c r="H264">
+        <v>19</v>
+      </c>
+      <c r="I264">
+        <v>18</v>
+      </c>
+      <c r="J264">
+        <v>13</v>
+      </c>
+      <c r="K264">
+        <v>30</v>
+      </c>
+      <c r="L264">
+        <v>18</v>
+      </c>
+      <c r="M264">
+        <v>17</v>
+      </c>
+      <c r="N264">
+        <v>16</v>
+      </c>
+      <c r="O264" s="23">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="P264" s="23">
+        <f t="shared" si="16"/>
+        <v>6.67</v>
+      </c>
+      <c r="R264">
+        <v>39</v>
+      </c>
+      <c r="S264">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B265" s="24">
+        <v>46102</v>
+      </c>
+      <c r="C265">
+        <v>43</v>
+      </c>
+      <c r="D265">
+        <v>29</v>
+      </c>
+      <c r="E265">
+        <v>49</v>
+      </c>
+      <c r="F265">
+        <v>22</v>
+      </c>
+      <c r="G265">
+        <v>31</v>
+      </c>
+      <c r="H265">
+        <v>17</v>
+      </c>
+      <c r="I265">
+        <v>26</v>
+      </c>
+      <c r="J265">
+        <v>14</v>
+      </c>
+      <c r="K265">
+        <v>62</v>
+      </c>
+      <c r="L265">
+        <v>24</v>
+      </c>
+      <c r="M265">
+        <v>36</v>
+      </c>
+      <c r="N265">
+        <v>24</v>
+      </c>
+      <c r="O265" s="23">
+        <f t="shared" si="15"/>
+        <v>33</v>
+      </c>
+      <c r="P265" s="23">
+        <f t="shared" si="16"/>
+        <v>14.49</v>
+      </c>
+      <c r="R265">
+        <v>60</v>
+      </c>
+      <c r="S265">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B266" s="24">
+        <v>46103</v>
+      </c>
+      <c r="C266">
+        <v>34</v>
+      </c>
+      <c r="D266">
+        <v>26</v>
+      </c>
+      <c r="E266">
+        <v>35</v>
+      </c>
+      <c r="F266">
+        <v>17</v>
+      </c>
+      <c r="G266">
+        <v>17</v>
+      </c>
+      <c r="H266">
+        <v>16</v>
+      </c>
+      <c r="I266">
+        <v>29</v>
+      </c>
+      <c r="J266">
+        <v>19</v>
+      </c>
+      <c r="K266">
+        <v>27</v>
+      </c>
+      <c r="L266">
+        <v>24</v>
+      </c>
+      <c r="M266">
+        <v>43</v>
+      </c>
+      <c r="N266">
+        <v>26</v>
+      </c>
+      <c r="O266" s="23">
+        <f t="shared" si="15"/>
+        <v>26</v>
+      </c>
+      <c r="P266" s="23">
+        <f t="shared" si="16"/>
+        <v>7.49</v>
+      </c>
+      <c r="R266">
+        <v>21</v>
+      </c>
+      <c r="S266">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B267" s="24">
+        <v>46104</v>
+      </c>
+      <c r="C267">
+        <v>17</v>
+      </c>
+      <c r="D267">
+        <v>19</v>
+      </c>
+      <c r="E267">
+        <v>27</v>
+      </c>
+      <c r="F267">
+        <v>15</v>
+      </c>
+      <c r="G267">
+        <v>20</v>
+      </c>
+      <c r="H267">
+        <v>4</v>
+      </c>
+      <c r="I267">
+        <v>18</v>
+      </c>
+      <c r="J267">
+        <v>8</v>
+      </c>
+      <c r="K267">
+        <v>12</v>
+      </c>
+      <c r="L267">
+        <v>20</v>
+      </c>
+      <c r="M267">
+        <v>28</v>
+      </c>
+      <c r="N267">
+        <v>24</v>
+      </c>
+      <c r="O267" s="23">
+        <f t="shared" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="P267" s="23">
+        <f t="shared" si="16"/>
+        <v>6.92</v>
+      </c>
+      <c r="R267">
+        <v>28</v>
+      </c>
+      <c r="S267">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B268" s="24">
+        <v>46105</v>
+      </c>
+      <c r="C268">
+        <v>16</v>
+      </c>
+      <c r="D268">
+        <v>16</v>
+      </c>
+      <c r="E268">
+        <v>16</v>
+      </c>
+      <c r="F268">
+        <v>15</v>
+      </c>
+      <c r="G268">
+        <v>15</v>
+      </c>
+      <c r="H268">
+        <v>5</v>
+      </c>
+      <c r="I268">
+        <v>14</v>
+      </c>
+      <c r="J268">
+        <v>21</v>
+      </c>
+      <c r="K268">
+        <v>16</v>
+      </c>
+      <c r="L268">
+        <v>15</v>
+      </c>
+      <c r="M268">
+        <v>16</v>
+      </c>
+      <c r="N268">
+        <v>17</v>
+      </c>
+      <c r="O268" s="23">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="P268" s="23">
+        <f t="shared" si="16"/>
+        <v>3.33</v>
+      </c>
+      <c r="R268">
+        <v>18</v>
+      </c>
+      <c r="S268">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B269" s="24">
+        <v>46106</v>
+      </c>
+      <c r="C269">
+        <v>20</v>
+      </c>
+      <c r="D269">
+        <v>20</v>
+      </c>
+      <c r="E269">
+        <v>14</v>
+      </c>
+      <c r="F269">
+        <v>13</v>
+      </c>
+      <c r="G269">
+        <v>13</v>
+      </c>
+      <c r="H269">
+        <v>4</v>
+      </c>
+      <c r="I269">
+        <v>20</v>
+      </c>
+      <c r="J269">
+        <v>15</v>
+      </c>
+      <c r="K269">
+        <v>20</v>
+      </c>
+      <c r="L269">
+        <v>18</v>
+      </c>
+      <c r="M269">
+        <v>25</v>
+      </c>
+      <c r="N269">
+        <v>21</v>
+      </c>
+      <c r="O269" s="23">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="P269" s="23">
+        <f t="shared" si="16"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="R269">
+        <v>15</v>
+      </c>
+      <c r="S269">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B270" s="24">
+        <v>46107</v>
+      </c>
+      <c r="C270">
+        <v>29</v>
+      </c>
+      <c r="D270">
+        <v>17</v>
+      </c>
+      <c r="E270">
+        <v>18</v>
+      </c>
+      <c r="F270">
+        <v>14</v>
+      </c>
+      <c r="G270">
+        <v>14</v>
+      </c>
+      <c r="H270">
+        <v>16</v>
+      </c>
+      <c r="I270">
+        <v>19</v>
+      </c>
+      <c r="J270">
+        <v>13</v>
+      </c>
+      <c r="K270">
+        <v>28</v>
+      </c>
+      <c r="L270">
+        <v>17</v>
+      </c>
+      <c r="M270">
+        <v>27</v>
+      </c>
+      <c r="N270">
+        <v>23</v>
+      </c>
+      <c r="O270" s="23">
+        <f t="shared" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="P270" s="23">
+        <f t="shared" si="16"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R270">
+        <v>19</v>
+      </c>
+      <c r="S270">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B271" s="24">
+        <v>46108</v>
+      </c>
+      <c r="C271">
+        <v>26</v>
+      </c>
+      <c r="D271">
+        <v>18</v>
+      </c>
+      <c r="E271">
+        <v>20</v>
+      </c>
+      <c r="F271">
+        <v>22</v>
+      </c>
+      <c r="G271">
+        <v>22</v>
+      </c>
+      <c r="H271">
+        <v>18</v>
+      </c>
+      <c r="I271">
+        <v>17</v>
+      </c>
+      <c r="J271">
+        <v>18</v>
+      </c>
+      <c r="K271">
+        <v>23</v>
+      </c>
+      <c r="L271">
+        <v>24</v>
+      </c>
+      <c r="M271">
+        <v>24</v>
+      </c>
+      <c r="N271">
+        <v>20</v>
+      </c>
+      <c r="O271" s="23">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="P271" s="23">
+        <f t="shared" si="16"/>
+        <v>2.64</v>
+      </c>
+      <c r="R271">
+        <v>23</v>
+      </c>
+      <c r="S271">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B272" s="24">
+        <v>46109</v>
+      </c>
+      <c r="C272">
+        <v>15</v>
+      </c>
+      <c r="D272">
+        <v>24</v>
+      </c>
+      <c r="E272">
+        <v>31</v>
+      </c>
+      <c r="F272">
+        <v>20</v>
+      </c>
+      <c r="G272">
+        <v>24</v>
+      </c>
+      <c r="H272">
+        <v>4</v>
+      </c>
+      <c r="I272">
+        <v>15</v>
+      </c>
+      <c r="J272">
+        <v>26</v>
+      </c>
+      <c r="K272">
+        <v>11</v>
+      </c>
+      <c r="L272">
+        <v>24</v>
+      </c>
+      <c r="M272">
+        <v>16</v>
+      </c>
+      <c r="N272">
+        <v>18</v>
+      </c>
+      <c r="O272" s="23">
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="P272" s="23">
+        <f t="shared" si="16"/>
+        <v>6.85</v>
+      </c>
+      <c r="R272">
+        <v>26</v>
+      </c>
+      <c r="S272">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="273" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B273" s="24">
+        <v>46110</v>
+      </c>
+      <c r="C273">
+        <v>44</v>
+      </c>
+      <c r="D273">
+        <v>45</v>
+      </c>
+      <c r="E273">
+        <v>31</v>
+      </c>
+      <c r="F273">
+        <v>38</v>
+      </c>
+      <c r="G273">
+        <v>23</v>
+      </c>
+      <c r="H273">
+        <v>37</v>
+      </c>
+      <c r="I273">
+        <v>20</v>
+      </c>
+      <c r="J273">
+        <v>33</v>
+      </c>
+      <c r="K273">
+        <v>37</v>
+      </c>
+      <c r="L273">
+        <v>40</v>
+      </c>
+      <c r="M273">
+        <v>43</v>
+      </c>
+      <c r="N273">
+        <v>41</v>
+      </c>
+      <c r="O273" s="23">
+        <f t="shared" si="15"/>
+        <v>36</v>
+      </c>
+      <c r="P273" s="23">
+        <f t="shared" si="16"/>
+        <v>7.15</v>
+      </c>
+      <c r="R273">
+        <v>33</v>
+      </c>
+      <c r="S273">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="274" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B274" s="24">
+        <v>46111</v>
+      </c>
+      <c r="C274">
+        <v>12</v>
+      </c>
+      <c r="D274">
+        <v>14</v>
+      </c>
+      <c r="E274">
+        <v>22</v>
+      </c>
+      <c r="F274">
+        <v>13</v>
+      </c>
+      <c r="G274">
+        <v>11</v>
+      </c>
+      <c r="H274">
+        <v>9</v>
+      </c>
+      <c r="I274">
+        <v>14</v>
+      </c>
+      <c r="J274">
+        <v>13</v>
+      </c>
+      <c r="K274">
+        <v>12</v>
+      </c>
+      <c r="L274">
+        <v>13</v>
+      </c>
+      <c r="M274">
+        <v>15</v>
+      </c>
+      <c r="N274">
+        <v>15</v>
+      </c>
+      <c r="O274" s="23">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="P274" s="23">
+        <f t="shared" si="16"/>
+        <v>2.87</v>
+      </c>
+      <c r="R274">
+        <v>16</v>
+      </c>
+      <c r="S274">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B275" s="24">
+        <v>46112</v>
+      </c>
+      <c r="C275">
+        <v>11</v>
+      </c>
+      <c r="D275">
+        <v>11</v>
+      </c>
+      <c r="E275">
+        <v>14</v>
+      </c>
+      <c r="F275">
+        <v>12</v>
+      </c>
+      <c r="G275">
+        <v>10</v>
+      </c>
+      <c r="H275">
+        <v>11</v>
+      </c>
+      <c r="I275">
+        <v>12</v>
+      </c>
+      <c r="J275">
+        <v>6</v>
+      </c>
+      <c r="K275">
+        <v>12</v>
+      </c>
+      <c r="L275">
+        <v>12</v>
+      </c>
+      <c r="M275">
+        <v>15</v>
+      </c>
+      <c r="N275">
+        <v>11</v>
+      </c>
+      <c r="O275" s="23">
+        <f t="shared" si="15"/>
+        <v>11</v>
+      </c>
+      <c r="P275" s="23">
+        <f t="shared" si="16"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="R275">
+        <v>12</v>
+      </c>
+      <c r="S275">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B276" s="24">
+        <v>46113</v>
+      </c>
+      <c r="C276">
+        <v>26</v>
+      </c>
+      <c r="D276">
+        <v>15</v>
+      </c>
+      <c r="E276">
+        <v>19</v>
+      </c>
+      <c r="F276">
+        <v>11</v>
+      </c>
+      <c r="G276">
+        <v>15</v>
+      </c>
+      <c r="H276">
+        <v>4</v>
+      </c>
+      <c r="I276">
+        <v>14</v>
+      </c>
+      <c r="J276">
+        <v>10</v>
+      </c>
+      <c r="K276">
+        <v>24</v>
+      </c>
+      <c r="L276">
+        <v>15</v>
+      </c>
+      <c r="M276">
+        <v>16</v>
+      </c>
+      <c r="N276">
+        <v>17</v>
+      </c>
+      <c r="O276" s="23">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="P276" s="23">
+        <f t="shared" si="16"/>
+        <v>5.36</v>
+      </c>
+      <c r="R276">
+        <v>15</v>
+      </c>
+      <c r="S276">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B277" s="24">
+        <v>46114</v>
+      </c>
+      <c r="C277">
+        <v>11</v>
+      </c>
+      <c r="D277">
+        <v>11</v>
+      </c>
+      <c r="E277">
+        <v>13</v>
+      </c>
+      <c r="F277">
+        <v>15</v>
+      </c>
+      <c r="G277">
+        <v>12</v>
+      </c>
+      <c r="H277">
+        <v>33</v>
+      </c>
+      <c r="I277">
+        <v>9</v>
+      </c>
+      <c r="J277">
+        <v>18</v>
+      </c>
+      <c r="K277">
+        <v>14</v>
+      </c>
+      <c r="L277">
+        <v>12</v>
+      </c>
+      <c r="M277">
+        <v>6</v>
+      </c>
+      <c r="N277">
+        <v>11</v>
+      </c>
+      <c r="O277" s="23">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="P277" s="23">
+        <f t="shared" si="16"/>
+        <v>6.01</v>
+      </c>
+      <c r="R277">
+        <v>12</v>
+      </c>
+      <c r="S277">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="278" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B278" s="24">
+        <v>46115</v>
+      </c>
+      <c r="C278">
+        <v>12</v>
+      </c>
+      <c r="D278">
+        <v>13</v>
+      </c>
+      <c r="E278">
+        <v>16</v>
+      </c>
+      <c r="F278">
+        <v>9</v>
+      </c>
+      <c r="G278">
+        <v>13</v>
+      </c>
+      <c r="H278">
+        <v>4</v>
+      </c>
+      <c r="I278">
+        <v>14</v>
+      </c>
+      <c r="J278">
+        <v>6</v>
+      </c>
+      <c r="K278">
+        <v>13</v>
+      </c>
+      <c r="L278">
+        <v>14</v>
+      </c>
+      <c r="M278">
+        <v>22</v>
+      </c>
+      <c r="N278">
+        <v>18</v>
+      </c>
+      <c r="O278" s="23">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="P278" s="23">
+        <f t="shared" si="16"/>
+        <v>4.5</v>
+      </c>
+      <c r="R278">
+        <v>17</v>
+      </c>
+      <c r="S278">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B279" s="24">
+        <v>46116</v>
+      </c>
+      <c r="C279">
+        <v>16</v>
+      </c>
+      <c r="D279">
+        <v>11</v>
+      </c>
+      <c r="E279">
+        <v>20</v>
+      </c>
+      <c r="F279">
+        <v>13</v>
+      </c>
+      <c r="G279">
+        <v>26</v>
+      </c>
+      <c r="H279">
+        <v>6</v>
+      </c>
+      <c r="I279">
+        <v>15</v>
+      </c>
+      <c r="J279">
+        <v>13</v>
+      </c>
+      <c r="K279">
+        <v>13</v>
+      </c>
+      <c r="L279">
+        <v>16</v>
+      </c>
+      <c r="M279">
+        <v>19</v>
+      </c>
+      <c r="N279">
+        <v>13</v>
+      </c>
+      <c r="O279" s="23">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="P279" s="23">
+        <f t="shared" si="16"/>
+        <v>5.87</v>
+      </c>
+      <c r="R279">
+        <v>30</v>
+      </c>
+      <c r="S279">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="280" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B280" s="24">
+        <v>46117</v>
+      </c>
+      <c r="C280">
+        <v>102</v>
+      </c>
+      <c r="D280">
+        <v>95</v>
+      </c>
+      <c r="E280">
+        <v>61</v>
+      </c>
+      <c r="F280">
+        <v>67</v>
+      </c>
+      <c r="G280">
+        <v>34</v>
+      </c>
+      <c r="H280">
+        <v>47</v>
+      </c>
+      <c r="I280">
+        <v>50</v>
+      </c>
+      <c r="J280">
+        <v>50</v>
+      </c>
+      <c r="K280">
+        <v>108</v>
+      </c>
+      <c r="L280">
+        <v>94</v>
+      </c>
+      <c r="M280">
+        <v>95</v>
+      </c>
+      <c r="N280">
+        <v>91</v>
+      </c>
+      <c r="O280" s="23">
+        <f t="shared" si="15"/>
+        <v>73</v>
+      </c>
+      <c r="P280" s="23">
+        <f t="shared" si="16"/>
+        <v>22.99</v>
+      </c>
+      <c r="R280">
+        <v>63</v>
+      </c>
+      <c r="S280">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="281" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B281" s="24">
+        <v>46118</v>
+      </c>
+      <c r="C281">
+        <v>13</v>
+      </c>
+      <c r="D281">
+        <v>13</v>
+      </c>
+      <c r="E281">
+        <v>15</v>
+      </c>
+      <c r="F281">
+        <v>9</v>
+      </c>
+      <c r="G281">
+        <v>10</v>
+      </c>
+      <c r="H281">
+        <v>4</v>
+      </c>
+      <c r="I281">
+        <v>14</v>
+      </c>
+      <c r="J281">
+        <v>7</v>
+      </c>
+      <c r="K281">
+        <v>14</v>
+      </c>
+      <c r="L281">
+        <v>15</v>
+      </c>
+      <c r="M281">
+        <v>14</v>
+      </c>
+      <c r="N281">
+        <v>15</v>
+      </c>
+      <c r="O281" s="23">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="P281" s="23">
+        <f t="shared" si="16"/>
+        <v>3.25</v>
+      </c>
+      <c r="R281">
+        <v>14</v>
+      </c>
+      <c r="S281">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B282" s="24">
+        <v>46119</v>
+      </c>
+      <c r="C282">
+        <v>14</v>
+      </c>
+      <c r="D282">
+        <v>14</v>
+      </c>
+      <c r="E282">
+        <v>13</v>
+      </c>
+      <c r="F282">
+        <v>12</v>
+      </c>
+      <c r="G282">
+        <v>10</v>
+      </c>
+      <c r="H282">
+        <v>7</v>
+      </c>
+      <c r="I282">
+        <v>12</v>
+      </c>
+      <c r="J282">
+        <v>8</v>
+      </c>
+      <c r="K282">
+        <v>12</v>
+      </c>
+      <c r="L282">
+        <v>14</v>
+      </c>
+      <c r="M282">
+        <v>12</v>
+      </c>
+      <c r="N282">
+        <v>12</v>
+      </c>
+      <c r="O282" s="23">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="P282" s="23">
+        <f t="shared" si="16"/>
+        <v>2.04</v>
+      </c>
+      <c r="R282">
+        <v>13</v>
+      </c>
+      <c r="S282">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B283" s="24">
+        <v>46120</v>
+      </c>
+      <c r="C283">
+        <v>19</v>
+      </c>
+      <c r="D283">
+        <v>22</v>
+      </c>
+      <c r="E283">
+        <v>22</v>
+      </c>
+      <c r="F283">
+        <v>15</v>
+      </c>
+      <c r="G283">
+        <v>23</v>
+      </c>
+      <c r="H283">
+        <v>4</v>
+      </c>
+      <c r="I283">
+        <v>18</v>
+      </c>
+      <c r="J283">
+        <v>20</v>
+      </c>
+      <c r="K283">
+        <v>12</v>
+      </c>
+      <c r="L283">
+        <v>13</v>
+      </c>
+      <c r="M283">
+        <v>22</v>
+      </c>
+      <c r="N283">
+        <v>19</v>
+      </c>
+      <c r="O283" s="23">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="P283" s="23">
+        <f t="shared" si="16"/>
+        <v>5.03</v>
+      </c>
+      <c r="R283">
+        <v>19</v>
+      </c>
+      <c r="S283">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="284" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B284" s="24">
+        <v>46121</v>
+      </c>
+      <c r="C284">
+        <v>12</v>
+      </c>
+      <c r="D284">
+        <v>14</v>
+      </c>
+      <c r="E284">
+        <v>16</v>
+      </c>
+      <c r="F284">
+        <v>17</v>
+      </c>
+      <c r="G284">
+        <v>13</v>
+      </c>
+      <c r="H284">
+        <v>4</v>
+      </c>
+      <c r="I284">
+        <v>15</v>
+      </c>
+      <c r="J284">
+        <v>19</v>
+      </c>
+      <c r="K284">
+        <v>12</v>
+      </c>
+      <c r="L284">
+        <v>14</v>
+      </c>
+      <c r="M284">
+        <v>17</v>
+      </c>
+      <c r="N284">
+        <v>14</v>
+      </c>
+      <c r="O284" s="23">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="P284" s="23">
+        <f t="shared" si="16"/>
+        <v>3.76</v>
+      </c>
+      <c r="R284">
+        <v>20</v>
+      </c>
+      <c r="S284">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="285" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B285" s="24">
+        <v>46122</v>
+      </c>
+      <c r="C285">
+        <v>16</v>
+      </c>
+      <c r="D285">
+        <v>16</v>
+      </c>
+      <c r="E285">
+        <v>14</v>
+      </c>
+      <c r="F285">
+        <v>13</v>
+      </c>
+      <c r="G285">
+        <v>20</v>
+      </c>
+      <c r="H285">
+        <v>5</v>
+      </c>
+      <c r="I285">
+        <v>13</v>
+      </c>
+      <c r="J285">
+        <v>10</v>
+      </c>
+      <c r="K285">
+        <v>19</v>
+      </c>
+      <c r="L285">
+        <v>14</v>
+      </c>
+      <c r="M285">
+        <v>14</v>
+      </c>
+      <c r="N285">
+        <v>12</v>
+      </c>
+      <c r="O285" s="23">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="P285" s="23">
+        <f t="shared" si="16"/>
+        <v>3.53</v>
+      </c>
+      <c r="R285">
+        <v>14</v>
+      </c>
+      <c r="S285">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="286" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B286" s="24">
+        <v>46123</v>
+      </c>
+      <c r="C286">
+        <v>27</v>
+      </c>
+      <c r="D286">
+        <v>34</v>
+      </c>
+      <c r="E286">
+        <v>20</v>
+      </c>
+      <c r="F286">
+        <v>20</v>
+      </c>
+      <c r="G286">
+        <v>21</v>
+      </c>
+      <c r="H286">
+        <v>5</v>
+      </c>
+      <c r="I286">
+        <v>15</v>
+      </c>
+      <c r="J286">
+        <v>37</v>
+      </c>
+      <c r="K286">
+        <v>22</v>
+      </c>
+      <c r="L286">
+        <v>27</v>
+      </c>
+      <c r="M286">
+        <v>25</v>
+      </c>
+      <c r="N286">
+        <v>35</v>
+      </c>
+      <c r="O286" s="23">
+        <f t="shared" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="P286" s="23">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="R286">
+        <v>23</v>
+      </c>
+      <c r="S286">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="287" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B287" s="24">
+        <v>46124</v>
+      </c>
+      <c r="C287">
         <v>32</v>
       </c>
-    </row>
-    <row r="252" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B252" s="32"/>
-      <c r="C252" s="44" t="s">
+      <c r="D287">
+        <v>35</v>
+      </c>
+      <c r="E287">
+        <v>24</v>
+      </c>
+      <c r="F287">
+        <v>21</v>
+      </c>
+      <c r="G287">
+        <v>18</v>
+      </c>
+      <c r="H287">
+        <v>4</v>
+      </c>
+      <c r="I287">
+        <v>20</v>
+      </c>
+      <c r="J287">
+        <v>18</v>
+      </c>
+      <c r="K287">
+        <v>33</v>
+      </c>
+      <c r="L287">
+        <v>35</v>
+      </c>
+      <c r="M287">
+        <v>29</v>
+      </c>
+      <c r="N287">
+        <v>38</v>
+      </c>
+      <c r="O287" s="23">
+        <f t="shared" si="15"/>
+        <v>26</v>
+      </c>
+      <c r="P287" s="23">
+        <f t="shared" si="16"/>
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="R287">
+        <v>28</v>
+      </c>
+      <c r="S287">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="288" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B288" s="24">
+        <v>46125</v>
+      </c>
+      <c r="C288">
+        <v>40</v>
+      </c>
+      <c r="D288">
+        <v>25</v>
+      </c>
+      <c r="E288">
+        <v>21</v>
+      </c>
+      <c r="F288">
+        <v>28</v>
+      </c>
+      <c r="G288">
+        <v>17</v>
+      </c>
+      <c r="H288">
+        <v>4</v>
+      </c>
+      <c r="I288">
+        <v>14</v>
+      </c>
+      <c r="J288">
+        <v>45</v>
+      </c>
+      <c r="K288">
+        <v>40</v>
+      </c>
+      <c r="L288">
+        <v>25</v>
+      </c>
+      <c r="M288">
+        <v>21</v>
+      </c>
+      <c r="N288">
+        <v>24</v>
+      </c>
+      <c r="O288" s="23">
+        <f t="shared" si="15"/>
+        <v>25</v>
+      </c>
+      <c r="P288" s="23">
+        <f t="shared" si="16"/>
+        <v>10.55</v>
+      </c>
+      <c r="R288">
+        <v>20</v>
+      </c>
+      <c r="S288">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="289" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B289" s="24">
+        <v>46126</v>
+      </c>
+      <c r="C289">
+        <v>11</v>
+      </c>
+      <c r="D289">
+        <v>10</v>
+      </c>
+      <c r="E289">
+        <v>13</v>
+      </c>
+      <c r="F289">
+        <v>13</v>
+      </c>
+      <c r="G289">
+        <v>10</v>
+      </c>
+      <c r="H289">
+        <v>4</v>
+      </c>
+      <c r="I289">
+        <v>10</v>
+      </c>
+      <c r="J289">
+        <v>7</v>
+      </c>
+      <c r="K289">
+        <v>12</v>
+      </c>
+      <c r="L289">
+        <v>12</v>
+      </c>
+      <c r="M289">
+        <v>7</v>
+      </c>
+      <c r="N289">
+        <v>11</v>
+      </c>
+      <c r="O289" s="23">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="P289" s="23">
+        <f t="shared" si="16"/>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="R289">
+        <v>12</v>
+      </c>
+      <c r="S289">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B290" s="24">
+        <v>46127</v>
+      </c>
+      <c r="C290">
+        <v>17</v>
+      </c>
+      <c r="D290">
+        <v>20</v>
+      </c>
+      <c r="E290">
+        <v>14</v>
+      </c>
+      <c r="F290">
+        <v>12</v>
+      </c>
+      <c r="G290">
+        <v>12</v>
+      </c>
+      <c r="H290">
+        <v>12</v>
+      </c>
+      <c r="I290">
+        <v>13</v>
+      </c>
+      <c r="J290">
+        <v>10</v>
+      </c>
+      <c r="K290">
+        <v>15</v>
+      </c>
+      <c r="L290">
+        <v>16</v>
+      </c>
+      <c r="M290">
+        <v>15</v>
+      </c>
+      <c r="N290">
+        <v>20</v>
+      </c>
+      <c r="O290" s="23">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="P290" s="23">
+        <f t="shared" si="16"/>
+        <v>2.82</v>
+      </c>
+      <c r="R290">
+        <v>14</v>
+      </c>
+      <c r="S290">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B291" s="24">
+        <v>46128</v>
+      </c>
+      <c r="C291">
+        <v>11</v>
+      </c>
+      <c r="D291">
+        <v>13</v>
+      </c>
+      <c r="E291">
+        <v>14</v>
+      </c>
+      <c r="F291">
+        <v>14</v>
+      </c>
+      <c r="G291">
+        <v>11</v>
+      </c>
+      <c r="H291">
+        <v>17</v>
+      </c>
+      <c r="I291">
+        <v>15</v>
+      </c>
+      <c r="J291">
+        <v>13</v>
+      </c>
+      <c r="K291">
+        <v>12</v>
+      </c>
+      <c r="L291">
+        <v>13</v>
+      </c>
+      <c r="M291">
+        <v>15</v>
+      </c>
+      <c r="N291">
+        <v>12</v>
+      </c>
+      <c r="O291" s="23">
+        <f t="shared" si="15"/>
+        <v>14</v>
+      </c>
+      <c r="P291" s="23">
+        <f t="shared" si="16"/>
+        <v>1.72</v>
+      </c>
+      <c r="R291">
+        <v>14</v>
+      </c>
+      <c r="S291">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="292" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B292" s="24">
+        <v>46129</v>
+      </c>
+      <c r="C292">
+        <v>17</v>
+      </c>
+      <c r="D292">
+        <v>13</v>
+      </c>
+      <c r="E292">
+        <v>19</v>
+      </c>
+      <c r="F292">
+        <v>17</v>
+      </c>
+      <c r="G292">
+        <v>14</v>
+      </c>
+      <c r="H292">
+        <v>15</v>
+      </c>
+      <c r="I292">
+        <v>16</v>
+      </c>
+      <c r="J292">
+        <v>15</v>
+      </c>
+      <c r="K292">
+        <v>20</v>
+      </c>
+      <c r="L292">
+        <v>16</v>
+      </c>
+      <c r="M292">
+        <v>16</v>
+      </c>
+      <c r="N292">
+        <v>14</v>
+      </c>
+      <c r="O292" s="23">
+        <f t="shared" si="15"/>
+        <v>16</v>
+      </c>
+      <c r="P292" s="23">
+        <f t="shared" si="16"/>
+        <v>2.09</v>
+      </c>
+      <c r="R292">
+        <v>20</v>
+      </c>
+      <c r="S292">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="293" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B293" s="32"/>
+      <c r="C293" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D252" s="44"/>
-      <c r="E252" s="44" t="s">
+      <c r="D293" s="42"/>
+      <c r="E293" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="F252" s="44"/>
-      <c r="G252" s="44" t="s">
+      <c r="F293" s="41"/>
+      <c r="G293" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H252" s="44"/>
-      <c r="I252" s="44" t="s">
+      <c r="H293" s="42"/>
+      <c r="I293" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="J252" s="44"/>
-      <c r="K252" s="44" t="s">
+      <c r="J293" s="41"/>
+      <c r="K293" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="L252" s="44"/>
-      <c r="M252" s="44" t="s">
+      <c r="L293" s="42"/>
+      <c r="M293" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="N252" s="44"/>
-      <c r="O252" s="32"/>
-      <c r="P252" s="32"/>
-      <c r="Q252" s="32"/>
-      <c r="R252" s="44" t="s">
+      <c r="N293" s="41"/>
+      <c r="O293" s="40"/>
+      <c r="P293" s="40"/>
+      <c r="Q293" s="40"/>
+      <c r="R293" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="S252" s="44"/>
+      <c r="S293" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="R252:S252"/>
-    <mergeCell ref="M252:N252"/>
+    <mergeCell ref="R293:S293"/>
+    <mergeCell ref="M293:N293"/>
     <mergeCell ref="C1:N1"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="E252:F252"/>
-    <mergeCell ref="G252:H252"/>
-    <mergeCell ref="I252:J252"/>
-    <mergeCell ref="K252:L252"/>
+    <mergeCell ref="C293:D293"/>
+    <mergeCell ref="E293:F293"/>
+    <mergeCell ref="G293:H293"/>
+    <mergeCell ref="I293:J293"/>
+    <mergeCell ref="K293:L293"/>
   </mergeCells>
   <conditionalFormatting sqref="C81">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
@@ -42539,7 +48214,7 @@
       <formula>ABS(C116-$A116)&lt;=10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q233">
+  <conditionalFormatting sqref="Q1:Q260">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
